--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21560" activeTab="2"/>
+    <workbookView windowHeight="21560"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>
@@ -8679,7 +8679,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -12088,7 +12088,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -15498,7 +15498,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -18907,7 +18907,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -22317,7 +22317,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -25727,7 +25727,7 @@
     </row>
     <row r="194" ht="24.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -36590,7 +36590,7 @@
     <row r="133" s="238" customFormat="1" ht="20.25" customHeight="1"/>
     <row r="134" s="238" customFormat="1" ht="20.25" customHeight="1"/>
   </sheetData>
-  <sheetProtection formatCells="0"/>
+  <sheetProtection sheet="1" formatCells="0" objects="1"/>
   <mergeCells count="19">
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A5:A6"/>
@@ -39220,7 +39220,7 @@
     </row>
     <row r="204" ht="35" customHeight="1"/>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="170">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="I1:J1"/>
@@ -49705,7 +49705,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -53169,7 +53169,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -56612,7 +56612,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -60040,7 +60040,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>

--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -5802,7 +5802,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -8679,7 +8679,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -9211,7 +9211,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -10937,7 +10937,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -12088,7 +12088,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -12621,7 +12621,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -14231,7 +14231,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -14347,7 +14347,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -15498,7 +15498,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -16030,7 +16030,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -18907,7 +18907,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -19440,7 +19440,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -21050,7 +21050,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -21166,7 +21166,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -22317,7 +22317,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -22849,7 +22849,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -24575,7 +24575,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -25727,7 +25727,7 @@
     </row>
     <row r="194" ht="24.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -26258,7 +26258,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -27826,7 +27826,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -27958,7 +27958,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -29560,7 +29560,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -31243,7 +31243,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -32863,7 +32863,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -34547,7 +34547,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -36590,7 +36590,7 @@
     <row r="133" s="238" customFormat="1" ht="20.25" customHeight="1"/>
     <row r="134" s="238" customFormat="1" ht="20.25" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" objects="1"/>
+  <sheetProtection formatCells="0"/>
   <mergeCells count="19">
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A5:A6"/>
@@ -36714,7 +36714,7 @@
       </c>
       <c r="N3" s="211">
         <f>-C122</f>
-        <v>-24333</v>
+        <v>-350482.51</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:14">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="N4" s="211">
         <f ca="1">'July 2024 - September 2024'!C5</f>
-        <v>-11683</v>
+        <v>-337832.51</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:14">
@@ -36778,7 +36778,7 @@
       </c>
       <c r="N5" s="211">
         <f ca="1">'October 2024 - December 2024'!C5</f>
-        <v>-10683</v>
+        <v>-336832.51</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:14">
@@ -36810,7 +36810,7 @@
       </c>
       <c r="N6" s="211">
         <f ca="1">'January 2025 - March 2025'!C5</f>
-        <v>-6983</v>
+        <v>-333132.51</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:14">
@@ -36842,7 +36842,7 @@
       </c>
       <c r="N7" s="211">
         <f ca="1">'April 2025 - June 2025'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:14">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="N8" s="211">
         <f ca="1">'July 2025 - September 2025'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:14">
@@ -36907,7 +36907,7 @@
       </c>
       <c r="N9" s="221">
         <f ca="1">'October 2025 - December 2025'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:14">
@@ -36939,7 +36939,7 @@
       </c>
       <c r="N10" s="211">
         <f ca="1">'January 2026 - March 2026'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:14">
@@ -36972,7 +36972,7 @@
       </c>
       <c r="N11" s="215">
         <f ca="1">'April 2026 - June 2026'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:14">
@@ -37004,7 +37004,7 @@
       </c>
       <c r="N12" s="215">
         <f ca="1">'July 2026 - September 2026'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:14">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="N13" s="215">
         <f ca="1">'October 2026 - December 2026'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:14">
@@ -37068,7 +37068,7 @@
       </c>
       <c r="N14" s="215">
         <f ca="1">'January 2027 - March 2027'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:14">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="N15" s="215">
         <f ca="1">'April 2027 - June 2027'!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:14">
@@ -37134,7 +37134,7 @@
       </c>
       <c r="N16" s="215">
         <f ca="1">Forecast_14!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="9:14">
@@ -37152,7 +37152,7 @@
       </c>
       <c r="N17" s="215">
         <f ca="1">Forecast_15!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="9:14">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="N18" s="211">
         <f ca="1">Forecast_16!C5</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="9:10">
@@ -38338,7 +38338,7 @@
       </c>
       <c r="B116" s="199"/>
       <c r="C116" s="234">
-        <v>0</v>
+        <v>326149.51</v>
       </c>
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
@@ -38415,7 +38415,7 @@
       </c>
       <c r="C122" s="223">
         <f>SUM(C112:C121)</f>
-        <v>24333</v>
+        <v>350482.51</v>
       </c>
     </row>
     <row r="123" ht="35" customHeight="1" spans="1:3">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="C123" s="36">
         <f>C122+C110</f>
-        <v>25836</v>
+        <v>351985.51</v>
       </c>
     </row>
     <row r="124" ht="35" customHeight="1" spans="5:5">
@@ -39764,7 +39764,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-11683</v>
+        <v>-337832.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -41406,7 +41406,7 @@
       </c>
       <c r="C102" s="108" cm="1">
         <f ca="1" t="array" ref="C102">(((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E135")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E162")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E189")))+SUM(E122+E149+E176))-INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!C116")</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="164"/>
@@ -41522,7 +41522,7 @@
       </c>
       <c r="C108" s="108">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-11683</v>
+        <v>-337832.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -41538,7 +41538,7 @@
       </c>
       <c r="C109" s="108">
         <f ca="1">C108-C96</f>
-        <v>-13711.5</v>
+        <v>-339861.01</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -43214,7 +43214,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-10683</v>
+        <v>-336832.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -44886,7 +44886,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -45002,7 +45002,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-10683</v>
+        <v>-336832.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -45018,7 +45018,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-12052</v>
+        <v>-338201.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -46764,7 +46764,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6983</v>
+        <v>-333132.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -48420,7 +48420,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -48536,7 +48536,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6983</v>
+        <v>-333132.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -48552,7 +48552,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-7380</v>
+        <v>-333529.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -49705,7 +49705,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -50282,7 +50282,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -51896,7 +51896,7 @@
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -52012,7 +52012,7 @@
       </c>
       <c r="C108" s="36">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -52028,7 +52028,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -53169,7 +53169,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -53729,7 +53729,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -55339,7 +55339,7 @@
       </c>
       <c r="C102" s="108" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -55455,7 +55455,7 @@
       </c>
       <c r="C108" s="108">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -55471,7 +55471,7 @@
       </c>
       <c r="C109" s="108">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -56612,7 +56612,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>
@@ -57167,7 +57167,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -58773,7 +58773,7 @@
       </c>
       <c r="C102" s="108" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -58889,7 +58889,7 @@
       </c>
       <c r="C108" s="108">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-6483</v>
+        <v>-332632.51</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -58905,7 +58905,7 @@
       </c>
       <c r="C109" s="108">
         <f ca="1">C108-C96</f>
-        <v>-6880</v>
+        <v>-333029.51</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -60040,7 +60040,7 @@
       <c r="I193" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" objects="1"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="174">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="C2:G2"/>

--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21560"/>
+    <workbookView windowHeight="21560" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="306">
   <si>
     <t>Income Forecast</t>
   </si>
@@ -1212,10 +1212,16 @@
     <t>30th April 2025</t>
   </si>
   <si>
-    <t>Hospital Fees</t>
+    <t>Birdie</t>
   </si>
   <si>
-    <t>Robert Black Hospital Paid in advance</t>
+    <t>Birdie Paid in advance</t>
+  </si>
+  <si>
+    <t>1.  yuu</t>
+  </si>
+  <si>
+    <t>1. Newly added / remain yuu points ~ $1</t>
   </si>
   <si>
     <t>31th May 2025</t>
@@ -1235,7 +1241,13 @@
     - See the psycharitic Doctor ~ $125</t>
   </si>
   <si>
-    <t>2. Food And Transport Expenses</t>
+    <t>2. Food And Transport Expenses
+- Chicken 4 pieces Market ~ $38
+- Rice 5kg Best Mart 360 ~ $49
+- Garden Biscuit (8 packets) x 4 ~ $73 plus Longevity Filled Evaporated
+  3 cans ~ $27~ $90  
+- Oat Meal 1kg Best Mart ~ $20
+- yuu use $10 voucher</t>
   </si>
   <si>
     <t>Payback $1800 to Mom</t>
@@ -2744,7 +2756,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="256">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3373,6 +3385,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3945,1744 +3960,1744 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="17.6"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="253" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="253"/>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
-      <c r="K1" s="253"/>
-      <c r="L1" s="253"/>
-      <c r="M1" s="253"/>
-      <c r="N1" s="253"/>
-      <c r="O1" s="253"/>
-      <c r="P1" s="253"/>
-      <c r="Q1" s="253"/>
-      <c r="R1" s="253"/>
-      <c r="S1" s="253"/>
-      <c r="T1" s="253"/>
-      <c r="U1" s="253"/>
-      <c r="V1" s="253"/>
-      <c r="W1" s="253"/>
-      <c r="X1" s="253"/>
-      <c r="Y1" s="253"/>
-      <c r="Z1" s="253"/>
+      <c r="A1" s="254" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="254"/>
+      <c r="C1" s="254"/>
+      <c r="D1" s="254"/>
+      <c r="E1" s="254"/>
+      <c r="F1" s="254"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="254"/>
+      <c r="N1" s="254"/>
+      <c r="O1" s="254"/>
+      <c r="P1" s="254"/>
+      <c r="Q1" s="254"/>
+      <c r="R1" s="254"/>
+      <c r="S1" s="254"/>
+      <c r="T1" s="254"/>
+      <c r="U1" s="254"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="254"/>
+      <c r="X1" s="254"/>
+      <c r="Y1" s="254"/>
+      <c r="Z1" s="254"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="253"/>
-      <c r="B2" s="253"/>
-      <c r="C2" s="253"/>
-      <c r="D2" s="253"/>
-      <c r="E2" s="253"/>
-      <c r="F2" s="253"/>
-      <c r="G2" s="253"/>
-      <c r="H2" s="253"/>
-      <c r="I2" s="253"/>
-      <c r="J2" s="253"/>
-      <c r="K2" s="253"/>
-      <c r="L2" s="253"/>
-      <c r="M2" s="253"/>
-      <c r="N2" s="253"/>
-      <c r="O2" s="253"/>
-      <c r="P2" s="253"/>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
+      <c r="A2" s="254"/>
+      <c r="B2" s="254"/>
+      <c r="C2" s="254"/>
+      <c r="D2" s="254"/>
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="254"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="254"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="254"/>
+      <c r="P2" s="254"/>
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="253"/>
-      <c r="B3" s="253"/>
-      <c r="C3" s="253"/>
-      <c r="D3" s="253"/>
-      <c r="E3" s="253"/>
-      <c r="F3" s="253"/>
-      <c r="G3" s="253"/>
-      <c r="H3" s="253"/>
-      <c r="I3" s="253"/>
-      <c r="J3" s="253"/>
-      <c r="K3" s="253"/>
-      <c r="L3" s="253"/>
-      <c r="M3" s="253"/>
-      <c r="N3" s="253"/>
-      <c r="O3" s="253"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="A3" s="254"/>
+      <c r="B3" s="254"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="254"/>
+      <c r="I3" s="254"/>
+      <c r="J3" s="254"/>
+      <c r="K3" s="254"/>
+      <c r="L3" s="254"/>
+      <c r="M3" s="254"/>
+      <c r="N3" s="254"/>
+      <c r="O3" s="254"/>
+      <c r="P3" s="254"/>
+      <c r="Q3" s="254"/>
+      <c r="R3" s="254"/>
+      <c r="S3" s="254"/>
+      <c r="T3" s="254"/>
+      <c r="U3" s="254"/>
+      <c r="V3" s="254"/>
+      <c r="W3" s="254"/>
+      <c r="X3" s="254"/>
+      <c r="Y3" s="254"/>
+      <c r="Z3" s="254"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="253"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
-      <c r="E4" s="253"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="253"/>
-      <c r="H4" s="253"/>
-      <c r="I4" s="253"/>
-      <c r="J4" s="253"/>
-      <c r="K4" s="253"/>
-      <c r="L4" s="253"/>
-      <c r="M4" s="253"/>
-      <c r="N4" s="253"/>
-      <c r="O4" s="253"/>
-      <c r="P4" s="253"/>
-      <c r="Q4" s="253"/>
-      <c r="R4" s="253"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="A4" s="254"/>
+      <c r="B4" s="254"/>
+      <c r="C4" s="254"/>
+      <c r="D4" s="254"/>
+      <c r="E4" s="254"/>
+      <c r="F4" s="254"/>
+      <c r="G4" s="254"/>
+      <c r="H4" s="254"/>
+      <c r="I4" s="254"/>
+      <c r="J4" s="254"/>
+      <c r="K4" s="254"/>
+      <c r="L4" s="254"/>
+      <c r="M4" s="254"/>
+      <c r="N4" s="254"/>
+      <c r="O4" s="254"/>
+      <c r="P4" s="254"/>
+      <c r="Q4" s="254"/>
+      <c r="R4" s="254"/>
+      <c r="S4" s="254"/>
+      <c r="T4" s="254"/>
+      <c r="U4" s="254"/>
+      <c r="V4" s="254"/>
+      <c r="W4" s="254"/>
+      <c r="X4" s="254"/>
+      <c r="Y4" s="254"/>
+      <c r="Z4" s="254"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="253"/>
-      <c r="B5" s="253"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="253"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="253"/>
-      <c r="H5" s="253"/>
-      <c r="I5" s="253"/>
-      <c r="J5" s="253"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="253"/>
-      <c r="N5" s="253"/>
-      <c r="O5" s="253"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="A5" s="254"/>
+      <c r="B5" s="254"/>
+      <c r="C5" s="254"/>
+      <c r="D5" s="254"/>
+      <c r="E5" s="254"/>
+      <c r="F5" s="254"/>
+      <c r="G5" s="254"/>
+      <c r="H5" s="254"/>
+      <c r="I5" s="254"/>
+      <c r="J5" s="254"/>
+      <c r="K5" s="254"/>
+      <c r="L5" s="254"/>
+      <c r="M5" s="254"/>
+      <c r="N5" s="254"/>
+      <c r="O5" s="254"/>
+      <c r="P5" s="254"/>
+      <c r="Q5" s="254"/>
+      <c r="R5" s="254"/>
+      <c r="S5" s="254"/>
+      <c r="T5" s="254"/>
+      <c r="U5" s="254"/>
+      <c r="V5" s="254"/>
+      <c r="W5" s="254"/>
+      <c r="X5" s="254"/>
+      <c r="Y5" s="254"/>
+      <c r="Z5" s="254"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="253"/>
-      <c r="B6" s="253"/>
-      <c r="C6" s="253"/>
-      <c r="D6" s="253"/>
-      <c r="E6" s="253"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="253"/>
-      <c r="H6" s="253"/>
-      <c r="I6" s="253"/>
-      <c r="J6" s="253"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="253"/>
-      <c r="M6" s="253"/>
-      <c r="N6" s="253"/>
-      <c r="O6" s="253"/>
-      <c r="P6" s="253"/>
-      <c r="Q6" s="253"/>
-      <c r="R6" s="253"/>
-      <c r="S6" s="253"/>
-      <c r="T6" s="253"/>
-      <c r="U6" s="253"/>
-      <c r="V6" s="253"/>
-      <c r="W6" s="253"/>
-      <c r="X6" s="253"/>
-      <c r="Y6" s="253"/>
-      <c r="Z6" s="253"/>
+      <c r="A6" s="254"/>
+      <c r="B6" s="254"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="254"/>
+      <c r="E6" s="254"/>
+      <c r="F6" s="254"/>
+      <c r="G6" s="254"/>
+      <c r="H6" s="254"/>
+      <c r="I6" s="254"/>
+      <c r="J6" s="254"/>
+      <c r="K6" s="254"/>
+      <c r="L6" s="254"/>
+      <c r="M6" s="254"/>
+      <c r="N6" s="254"/>
+      <c r="O6" s="254"/>
+      <c r="P6" s="254"/>
+      <c r="Q6" s="254"/>
+      <c r="R6" s="254"/>
+      <c r="S6" s="254"/>
+      <c r="T6" s="254"/>
+      <c r="U6" s="254"/>
+      <c r="V6" s="254"/>
+      <c r="W6" s="254"/>
+      <c r="X6" s="254"/>
+      <c r="Y6" s="254"/>
+      <c r="Z6" s="254"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="253"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="253"/>
-      <c r="E7" s="253"/>
-      <c r="F7" s="253"/>
-      <c r="G7" s="253"/>
-      <c r="H7" s="253"/>
-      <c r="I7" s="253"/>
-      <c r="J7" s="253"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="253"/>
-      <c r="M7" s="253"/>
-      <c r="N7" s="253"/>
-      <c r="O7" s="253"/>
-      <c r="P7" s="253"/>
-      <c r="Q7" s="253"/>
-      <c r="R7" s="253"/>
-      <c r="S7" s="253"/>
-      <c r="T7" s="253"/>
-      <c r="U7" s="253"/>
-      <c r="V7" s="253"/>
-      <c r="W7" s="253"/>
-      <c r="X7" s="253"/>
-      <c r="Y7" s="253"/>
-      <c r="Z7" s="253"/>
+      <c r="A7" s="254"/>
+      <c r="B7" s="254"/>
+      <c r="C7" s="254"/>
+      <c r="D7" s="254"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="254"/>
+      <c r="I7" s="254"/>
+      <c r="J7" s="254"/>
+      <c r="K7" s="254"/>
+      <c r="L7" s="254"/>
+      <c r="M7" s="254"/>
+      <c r="N7" s="254"/>
+      <c r="O7" s="254"/>
+      <c r="P7" s="254"/>
+      <c r="Q7" s="254"/>
+      <c r="R7" s="254"/>
+      <c r="S7" s="254"/>
+      <c r="T7" s="254"/>
+      <c r="U7" s="254"/>
+      <c r="V7" s="254"/>
+      <c r="W7" s="254"/>
+      <c r="X7" s="254"/>
+      <c r="Y7" s="254"/>
+      <c r="Z7" s="254"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="253"/>
-      <c r="B8" s="253"/>
-      <c r="C8" s="253"/>
-      <c r="D8" s="253"/>
-      <c r="E8" s="253"/>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253"/>
-      <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
-      <c r="J8" s="253"/>
-      <c r="K8" s="253"/>
-      <c r="L8" s="253"/>
-      <c r="M8" s="253"/>
-      <c r="N8" s="253"/>
-      <c r="O8" s="253"/>
-      <c r="P8" s="253"/>
-      <c r="Q8" s="253"/>
-      <c r="R8" s="253"/>
-      <c r="S8" s="253"/>
-      <c r="T8" s="253"/>
-      <c r="U8" s="253"/>
-      <c r="V8" s="253"/>
-      <c r="W8" s="253"/>
-      <c r="X8" s="253"/>
-      <c r="Y8" s="253"/>
-      <c r="Z8" s="253"/>
+      <c r="A8" s="254"/>
+      <c r="B8" s="254"/>
+      <c r="C8" s="254"/>
+      <c r="D8" s="254"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="254"/>
+      <c r="I8" s="254"/>
+      <c r="J8" s="254"/>
+      <c r="K8" s="254"/>
+      <c r="L8" s="254"/>
+      <c r="M8" s="254"/>
+      <c r="N8" s="254"/>
+      <c r="O8" s="254"/>
+      <c r="P8" s="254"/>
+      <c r="Q8" s="254"/>
+      <c r="R8" s="254"/>
+      <c r="S8" s="254"/>
+      <c r="T8" s="254"/>
+      <c r="U8" s="254"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="254"/>
+      <c r="X8" s="254"/>
+      <c r="Y8" s="254"/>
+      <c r="Z8" s="254"/>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="253"/>
-      <c r="B9" s="253"/>
-      <c r="C9" s="253"/>
-      <c r="D9" s="253"/>
-      <c r="E9" s="253"/>
-      <c r="F9" s="253"/>
-      <c r="G9" s="253"/>
-      <c r="H9" s="253"/>
-      <c r="I9" s="253"/>
-      <c r="J9" s="253"/>
-      <c r="K9" s="253"/>
-      <c r="L9" s="253"/>
-      <c r="M9" s="253"/>
-      <c r="N9" s="253"/>
-      <c r="O9" s="253"/>
-      <c r="P9" s="253"/>
-      <c r="Q9" s="253"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
-      <c r="T9" s="253"/>
-      <c r="U9" s="253"/>
-      <c r="V9" s="253"/>
-      <c r="W9" s="253"/>
-      <c r="X9" s="253"/>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
+      <c r="A9" s="254"/>
+      <c r="B9" s="254"/>
+      <c r="C9" s="254"/>
+      <c r="D9" s="254"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="254"/>
+      <c r="W9" s="254"/>
+      <c r="X9" s="254"/>
+      <c r="Y9" s="254"/>
+      <c r="Z9" s="254"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="253"/>
-      <c r="B10" s="253"/>
-      <c r="C10" s="253"/>
-      <c r="D10" s="253"/>
-      <c r="E10" s="253"/>
-      <c r="F10" s="253"/>
-      <c r="G10" s="253"/>
-      <c r="H10" s="253"/>
-      <c r="I10" s="253"/>
-      <c r="J10" s="253"/>
-      <c r="K10" s="253"/>
-      <c r="L10" s="253"/>
-      <c r="M10" s="253"/>
-      <c r="N10" s="253"/>
-      <c r="O10" s="253"/>
-      <c r="P10" s="253"/>
-      <c r="Q10" s="253"/>
-      <c r="R10" s="253"/>
-      <c r="S10" s="253"/>
-      <c r="T10" s="253"/>
-      <c r="U10" s="253"/>
-      <c r="V10" s="253"/>
-      <c r="W10" s="253"/>
-      <c r="X10" s="253"/>
-      <c r="Y10" s="253"/>
-      <c r="Z10" s="253"/>
+      <c r="A10" s="254"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="254"/>
+      <c r="L10" s="254"/>
+      <c r="M10" s="254"/>
+      <c r="N10" s="254"/>
+      <c r="O10" s="254"/>
+      <c r="P10" s="254"/>
+      <c r="Q10" s="254"/>
+      <c r="R10" s="254"/>
+      <c r="S10" s="254"/>
+      <c r="T10" s="254"/>
+      <c r="U10" s="254"/>
+      <c r="V10" s="254"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="254"/>
+      <c r="Y10" s="254"/>
+      <c r="Z10" s="254"/>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="253"/>
-      <c r="B11" s="253"/>
-      <c r="C11" s="253"/>
-      <c r="D11" s="253"/>
-      <c r="E11" s="253"/>
-      <c r="F11" s="253"/>
-      <c r="G11" s="253"/>
-      <c r="H11" s="253"/>
-      <c r="I11" s="253"/>
-      <c r="J11" s="253"/>
-      <c r="K11" s="253"/>
-      <c r="L11" s="253"/>
-      <c r="M11" s="253"/>
-      <c r="N11" s="253"/>
-      <c r="O11" s="253"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="A11" s="254"/>
+      <c r="B11" s="254"/>
+      <c r="C11" s="254"/>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="254"/>
+      <c r="H11" s="254"/>
+      <c r="I11" s="254"/>
+      <c r="J11" s="254"/>
+      <c r="K11" s="254"/>
+      <c r="L11" s="254"/>
+      <c r="M11" s="254"/>
+      <c r="N11" s="254"/>
+      <c r="O11" s="254"/>
+      <c r="P11" s="254"/>
+      <c r="Q11" s="254"/>
+      <c r="R11" s="254"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
+      <c r="V11" s="254"/>
+      <c r="W11" s="254"/>
+      <c r="X11" s="254"/>
+      <c r="Y11" s="254"/>
+      <c r="Z11" s="254"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="253"/>
-      <c r="B12" s="253"/>
-      <c r="C12" s="253"/>
-      <c r="D12" s="253"/>
-      <c r="E12" s="253"/>
-      <c r="F12" s="253"/>
-      <c r="G12" s="253"/>
-      <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
-      <c r="J12" s="253"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="253"/>
-      <c r="M12" s="253"/>
-      <c r="N12" s="253"/>
-      <c r="O12" s="253"/>
-      <c r="P12" s="253"/>
-      <c r="Q12" s="253"/>
-      <c r="R12" s="253"/>
-      <c r="S12" s="253"/>
-      <c r="T12" s="253"/>
-      <c r="U12" s="253"/>
-      <c r="V12" s="253"/>
-      <c r="W12" s="253"/>
-      <c r="X12" s="253"/>
-      <c r="Y12" s="253"/>
-      <c r="Z12" s="253"/>
+      <c r="A12" s="254"/>
+      <c r="B12" s="254"/>
+      <c r="C12" s="254"/>
+      <c r="D12" s="254"/>
+      <c r="E12" s="254"/>
+      <c r="F12" s="254"/>
+      <c r="G12" s="254"/>
+      <c r="H12" s="254"/>
+      <c r="I12" s="254"/>
+      <c r="J12" s="254"/>
+      <c r="K12" s="254"/>
+      <c r="L12" s="254"/>
+      <c r="M12" s="254"/>
+      <c r="N12" s="254"/>
+      <c r="O12" s="254"/>
+      <c r="P12" s="254"/>
+      <c r="Q12" s="254"/>
+      <c r="R12" s="254"/>
+      <c r="S12" s="254"/>
+      <c r="T12" s="254"/>
+      <c r="U12" s="254"/>
+      <c r="V12" s="254"/>
+      <c r="W12" s="254"/>
+      <c r="X12" s="254"/>
+      <c r="Y12" s="254"/>
+      <c r="Z12" s="254"/>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="253"/>
-      <c r="B13" s="253"/>
-      <c r="C13" s="253"/>
-      <c r="D13" s="253"/>
-      <c r="E13" s="253"/>
-      <c r="F13" s="253"/>
-      <c r="G13" s="253"/>
-      <c r="H13" s="253"/>
-      <c r="I13" s="253"/>
-      <c r="J13" s="253"/>
-      <c r="K13" s="253"/>
-      <c r="L13" s="253"/>
-      <c r="M13" s="253"/>
-      <c r="N13" s="253"/>
-      <c r="O13" s="253"/>
-      <c r="P13" s="253"/>
-      <c r="Q13" s="253"/>
-      <c r="R13" s="253"/>
-      <c r="S13" s="253"/>
-      <c r="T13" s="253"/>
-      <c r="U13" s="253"/>
-      <c r="V13" s="253"/>
-      <c r="W13" s="253"/>
-      <c r="X13" s="253"/>
-      <c r="Y13" s="253"/>
-      <c r="Z13" s="253"/>
+      <c r="A13" s="254"/>
+      <c r="B13" s="254"/>
+      <c r="C13" s="254"/>
+      <c r="D13" s="254"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="254"/>
+      <c r="G13" s="254"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="254"/>
+      <c r="J13" s="254"/>
+      <c r="K13" s="254"/>
+      <c r="L13" s="254"/>
+      <c r="M13" s="254"/>
+      <c r="N13" s="254"/>
+      <c r="O13" s="254"/>
+      <c r="P13" s="254"/>
+      <c r="Q13" s="254"/>
+      <c r="R13" s="254"/>
+      <c r="S13" s="254"/>
+      <c r="T13" s="254"/>
+      <c r="U13" s="254"/>
+      <c r="V13" s="254"/>
+      <c r="W13" s="254"/>
+      <c r="X13" s="254"/>
+      <c r="Y13" s="254"/>
+      <c r="Z13" s="254"/>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="253"/>
-      <c r="B14" s="253"/>
-      <c r="C14" s="253"/>
-      <c r="D14" s="253"/>
-      <c r="E14" s="253"/>
-      <c r="F14" s="253"/>
-      <c r="G14" s="253"/>
-      <c r="H14" s="253"/>
-      <c r="I14" s="253"/>
-      <c r="J14" s="253"/>
-      <c r="K14" s="253"/>
-      <c r="L14" s="253"/>
-      <c r="M14" s="253"/>
-      <c r="N14" s="253"/>
-      <c r="O14" s="253"/>
-      <c r="P14" s="253"/>
-      <c r="Q14" s="253"/>
-      <c r="R14" s="253"/>
-      <c r="S14" s="253"/>
-      <c r="T14" s="253"/>
-      <c r="U14" s="253"/>
-      <c r="V14" s="253"/>
-      <c r="W14" s="253"/>
-      <c r="X14" s="253"/>
-      <c r="Y14" s="253"/>
-      <c r="Z14" s="253"/>
+      <c r="A14" s="254"/>
+      <c r="B14" s="254"/>
+      <c r="C14" s="254"/>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
+      <c r="F14" s="254"/>
+      <c r="G14" s="254"/>
+      <c r="H14" s="254"/>
+      <c r="I14" s="254"/>
+      <c r="J14" s="254"/>
+      <c r="K14" s="254"/>
+      <c r="L14" s="254"/>
+      <c r="M14" s="254"/>
+      <c r="N14" s="254"/>
+      <c r="O14" s="254"/>
+      <c r="P14" s="254"/>
+      <c r="Q14" s="254"/>
+      <c r="R14" s="254"/>
+      <c r="S14" s="254"/>
+      <c r="T14" s="254"/>
+      <c r="U14" s="254"/>
+      <c r="V14" s="254"/>
+      <c r="W14" s="254"/>
+      <c r="X14" s="254"/>
+      <c r="Y14" s="254"/>
+      <c r="Z14" s="254"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="253"/>
-      <c r="B15" s="253"/>
-      <c r="C15" s="253"/>
-      <c r="D15" s="253"/>
-      <c r="E15" s="253"/>
-      <c r="F15" s="253"/>
-      <c r="G15" s="253"/>
-      <c r="H15" s="253"/>
-      <c r="I15" s="253"/>
-      <c r="J15" s="253"/>
-      <c r="K15" s="253"/>
-      <c r="L15" s="253"/>
-      <c r="M15" s="253"/>
-      <c r="N15" s="253"/>
-      <c r="O15" s="253"/>
-      <c r="P15" s="253"/>
-      <c r="Q15" s="253"/>
-      <c r="R15" s="253"/>
-      <c r="S15" s="253"/>
-      <c r="T15" s="253"/>
-      <c r="U15" s="253"/>
-      <c r="V15" s="253"/>
-      <c r="W15" s="253"/>
-      <c r="X15" s="253"/>
-      <c r="Y15" s="253"/>
-      <c r="Z15" s="253"/>
+      <c r="A15" s="254"/>
+      <c r="B15" s="254"/>
+      <c r="C15" s="254"/>
+      <c r="D15" s="254"/>
+      <c r="E15" s="254"/>
+      <c r="F15" s="254"/>
+      <c r="G15" s="254"/>
+      <c r="H15" s="254"/>
+      <c r="I15" s="254"/>
+      <c r="J15" s="254"/>
+      <c r="K15" s="254"/>
+      <c r="L15" s="254"/>
+      <c r="M15" s="254"/>
+      <c r="N15" s="254"/>
+      <c r="O15" s="254"/>
+      <c r="P15" s="254"/>
+      <c r="Q15" s="254"/>
+      <c r="R15" s="254"/>
+      <c r="S15" s="254"/>
+      <c r="T15" s="254"/>
+      <c r="U15" s="254"/>
+      <c r="V15" s="254"/>
+      <c r="W15" s="254"/>
+      <c r="X15" s="254"/>
+      <c r="Y15" s="254"/>
+      <c r="Z15" s="254"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="253"/>
-      <c r="B16" s="253"/>
-      <c r="C16" s="253"/>
-      <c r="D16" s="253"/>
-      <c r="E16" s="253"/>
-      <c r="F16" s="253"/>
-      <c r="G16" s="253"/>
-      <c r="H16" s="253"/>
-      <c r="I16" s="253"/>
-      <c r="J16" s="253"/>
-      <c r="K16" s="253"/>
-      <c r="L16" s="253"/>
-      <c r="M16" s="253"/>
-      <c r="N16" s="253"/>
-      <c r="O16" s="253"/>
-      <c r="P16" s="253"/>
-      <c r="Q16" s="253"/>
-      <c r="R16" s="253"/>
-      <c r="S16" s="253"/>
-      <c r="T16" s="253"/>
-      <c r="U16" s="253"/>
-      <c r="V16" s="253"/>
-      <c r="W16" s="253"/>
-      <c r="X16" s="253"/>
-      <c r="Y16" s="253"/>
-      <c r="Z16" s="253"/>
+      <c r="A16" s="254"/>
+      <c r="B16" s="254"/>
+      <c r="C16" s="254"/>
+      <c r="D16" s="254"/>
+      <c r="E16" s="254"/>
+      <c r="F16" s="254"/>
+      <c r="G16" s="254"/>
+      <c r="H16" s="254"/>
+      <c r="I16" s="254"/>
+      <c r="J16" s="254"/>
+      <c r="K16" s="254"/>
+      <c r="L16" s="254"/>
+      <c r="M16" s="254"/>
+      <c r="N16" s="254"/>
+      <c r="O16" s="254"/>
+      <c r="P16" s="254"/>
+      <c r="Q16" s="254"/>
+      <c r="R16" s="254"/>
+      <c r="S16" s="254"/>
+      <c r="T16" s="254"/>
+      <c r="U16" s="254"/>
+      <c r="V16" s="254"/>
+      <c r="W16" s="254"/>
+      <c r="X16" s="254"/>
+      <c r="Y16" s="254"/>
+      <c r="Z16" s="254"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="253"/>
-      <c r="B17" s="253"/>
-      <c r="C17" s="253"/>
-      <c r="D17" s="253"/>
-      <c r="E17" s="253"/>
-      <c r="F17" s="253"/>
-      <c r="G17" s="253"/>
-      <c r="H17" s="253"/>
-      <c r="I17" s="253"/>
-      <c r="J17" s="253"/>
-      <c r="K17" s="253"/>
-      <c r="L17" s="253"/>
-      <c r="M17" s="253"/>
-      <c r="N17" s="253"/>
-      <c r="O17" s="253"/>
-      <c r="P17" s="253"/>
-      <c r="Q17" s="253"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
-      <c r="T17" s="253"/>
-      <c r="U17" s="253"/>
-      <c r="V17" s="253"/>
-      <c r="W17" s="253"/>
-      <c r="X17" s="253"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
+      <c r="A17" s="254"/>
+      <c r="B17" s="254"/>
+      <c r="C17" s="254"/>
+      <c r="D17" s="254"/>
+      <c r="E17" s="254"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
+      <c r="J17" s="254"/>
+      <c r="K17" s="254"/>
+      <c r="L17" s="254"/>
+      <c r="M17" s="254"/>
+      <c r="N17" s="254"/>
+      <c r="O17" s="254"/>
+      <c r="P17" s="254"/>
+      <c r="Q17" s="254"/>
+      <c r="R17" s="254"/>
+      <c r="S17" s="254"/>
+      <c r="T17" s="254"/>
+      <c r="U17" s="254"/>
+      <c r="V17" s="254"/>
+      <c r="W17" s="254"/>
+      <c r="X17" s="254"/>
+      <c r="Y17" s="254"/>
+      <c r="Z17" s="254"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="253"/>
-      <c r="B18" s="253"/>
-      <c r="C18" s="253"/>
-      <c r="D18" s="253"/>
-      <c r="E18" s="253"/>
-      <c r="F18" s="253"/>
-      <c r="G18" s="253"/>
-      <c r="H18" s="253"/>
-      <c r="I18" s="253"/>
-      <c r="J18" s="253"/>
-      <c r="K18" s="253"/>
-      <c r="L18" s="253"/>
-      <c r="M18" s="253"/>
-      <c r="N18" s="253"/>
-      <c r="O18" s="253"/>
-      <c r="P18" s="253"/>
-      <c r="Q18" s="253"/>
-      <c r="R18" s="253"/>
-      <c r="S18" s="253"/>
-      <c r="T18" s="253"/>
-      <c r="U18" s="253"/>
-      <c r="V18" s="253"/>
-      <c r="W18" s="253"/>
-      <c r="X18" s="253"/>
-      <c r="Y18" s="253"/>
-      <c r="Z18" s="253"/>
+      <c r="A18" s="254"/>
+      <c r="B18" s="254"/>
+      <c r="C18" s="254"/>
+      <c r="D18" s="254"/>
+      <c r="E18" s="254"/>
+      <c r="F18" s="254"/>
+      <c r="G18" s="254"/>
+      <c r="H18" s="254"/>
+      <c r="I18" s="254"/>
+      <c r="J18" s="254"/>
+      <c r="K18" s="254"/>
+      <c r="L18" s="254"/>
+      <c r="M18" s="254"/>
+      <c r="N18" s="254"/>
+      <c r="O18" s="254"/>
+      <c r="P18" s="254"/>
+      <c r="Q18" s="254"/>
+      <c r="R18" s="254"/>
+      <c r="S18" s="254"/>
+      <c r="T18" s="254"/>
+      <c r="U18" s="254"/>
+      <c r="V18" s="254"/>
+      <c r="W18" s="254"/>
+      <c r="X18" s="254"/>
+      <c r="Y18" s="254"/>
+      <c r="Z18" s="254"/>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="253"/>
-      <c r="B19" s="253"/>
-      <c r="C19" s="253"/>
-      <c r="D19" s="253"/>
-      <c r="E19" s="253"/>
-      <c r="F19" s="253"/>
-      <c r="G19" s="253"/>
-      <c r="H19" s="253"/>
-      <c r="I19" s="253"/>
-      <c r="J19" s="253"/>
-      <c r="K19" s="253"/>
-      <c r="L19" s="253"/>
-      <c r="M19" s="253"/>
-      <c r="N19" s="253"/>
-      <c r="O19" s="253"/>
-      <c r="P19" s="253"/>
-      <c r="Q19" s="253"/>
-      <c r="R19" s="253"/>
-      <c r="S19" s="253"/>
-      <c r="T19" s="253"/>
-      <c r="U19" s="253"/>
-      <c r="V19" s="253"/>
-      <c r="W19" s="253"/>
-      <c r="X19" s="253"/>
-      <c r="Y19" s="253"/>
-      <c r="Z19" s="253"/>
+      <c r="A19" s="254"/>
+      <c r="B19" s="254"/>
+      <c r="C19" s="254"/>
+      <c r="D19" s="254"/>
+      <c r="E19" s="254"/>
+      <c r="F19" s="254"/>
+      <c r="G19" s="254"/>
+      <c r="H19" s="254"/>
+      <c r="I19" s="254"/>
+      <c r="J19" s="254"/>
+      <c r="K19" s="254"/>
+      <c r="L19" s="254"/>
+      <c r="M19" s="254"/>
+      <c r="N19" s="254"/>
+      <c r="O19" s="254"/>
+      <c r="P19" s="254"/>
+      <c r="Q19" s="254"/>
+      <c r="R19" s="254"/>
+      <c r="S19" s="254"/>
+      <c r="T19" s="254"/>
+      <c r="U19" s="254"/>
+      <c r="V19" s="254"/>
+      <c r="W19" s="254"/>
+      <c r="X19" s="254"/>
+      <c r="Y19" s="254"/>
+      <c r="Z19" s="254"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="253"/>
-      <c r="B20" s="253"/>
-      <c r="C20" s="253"/>
-      <c r="D20" s="253"/>
-      <c r="E20" s="253"/>
-      <c r="F20" s="253"/>
-      <c r="G20" s="253"/>
-      <c r="H20" s="253"/>
-      <c r="I20" s="253"/>
-      <c r="J20" s="253"/>
-      <c r="K20" s="253"/>
-      <c r="L20" s="253"/>
-      <c r="M20" s="253"/>
-      <c r="N20" s="253"/>
-      <c r="O20" s="253"/>
-      <c r="P20" s="253"/>
-      <c r="Q20" s="253"/>
-      <c r="R20" s="253"/>
-      <c r="S20" s="253"/>
-      <c r="T20" s="253"/>
-      <c r="U20" s="253"/>
-      <c r="V20" s="253"/>
-      <c r="W20" s="253"/>
-      <c r="X20" s="253"/>
-      <c r="Y20" s="253"/>
-      <c r="Z20" s="253"/>
+      <c r="A20" s="254"/>
+      <c r="B20" s="254"/>
+      <c r="C20" s="254"/>
+      <c r="D20" s="254"/>
+      <c r="E20" s="254"/>
+      <c r="F20" s="254"/>
+      <c r="G20" s="254"/>
+      <c r="H20" s="254"/>
+      <c r="I20" s="254"/>
+      <c r="J20" s="254"/>
+      <c r="K20" s="254"/>
+      <c r="L20" s="254"/>
+      <c r="M20" s="254"/>
+      <c r="N20" s="254"/>
+      <c r="O20" s="254"/>
+      <c r="P20" s="254"/>
+      <c r="Q20" s="254"/>
+      <c r="R20" s="254"/>
+      <c r="S20" s="254"/>
+      <c r="T20" s="254"/>
+      <c r="U20" s="254"/>
+      <c r="V20" s="254"/>
+      <c r="W20" s="254"/>
+      <c r="X20" s="254"/>
+      <c r="Y20" s="254"/>
+      <c r="Z20" s="254"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="253"/>
-      <c r="B21" s="253"/>
-      <c r="C21" s="253"/>
-      <c r="D21" s="253"/>
-      <c r="E21" s="253"/>
-      <c r="F21" s="253"/>
-      <c r="G21" s="253"/>
-      <c r="H21" s="253"/>
-      <c r="I21" s="253"/>
-      <c r="J21" s="253"/>
-      <c r="K21" s="253"/>
-      <c r="L21" s="253"/>
-      <c r="M21" s="253"/>
-      <c r="N21" s="253"/>
-      <c r="O21" s="253"/>
-      <c r="P21" s="253"/>
-      <c r="Q21" s="253"/>
-      <c r="R21" s="253"/>
-      <c r="S21" s="253"/>
-      <c r="T21" s="253"/>
-      <c r="U21" s="253"/>
-      <c r="V21" s="253"/>
-      <c r="W21" s="253"/>
-      <c r="X21" s="253"/>
-      <c r="Y21" s="253"/>
-      <c r="Z21" s="253"/>
+      <c r="A21" s="254"/>
+      <c r="B21" s="254"/>
+      <c r="C21" s="254"/>
+      <c r="D21" s="254"/>
+      <c r="E21" s="254"/>
+      <c r="F21" s="254"/>
+      <c r="G21" s="254"/>
+      <c r="H21" s="254"/>
+      <c r="I21" s="254"/>
+      <c r="J21" s="254"/>
+      <c r="K21" s="254"/>
+      <c r="L21" s="254"/>
+      <c r="M21" s="254"/>
+      <c r="N21" s="254"/>
+      <c r="O21" s="254"/>
+      <c r="P21" s="254"/>
+      <c r="Q21" s="254"/>
+      <c r="R21" s="254"/>
+      <c r="S21" s="254"/>
+      <c r="T21" s="254"/>
+      <c r="U21" s="254"/>
+      <c r="V21" s="254"/>
+      <c r="W21" s="254"/>
+      <c r="X21" s="254"/>
+      <c r="Y21" s="254"/>
+      <c r="Z21" s="254"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="253"/>
-      <c r="B22" s="253"/>
-      <c r="C22" s="253"/>
-      <c r="D22" s="253"/>
-      <c r="E22" s="253"/>
-      <c r="F22" s="253"/>
-      <c r="G22" s="253"/>
-      <c r="H22" s="253"/>
-      <c r="I22" s="253"/>
-      <c r="J22" s="253"/>
-      <c r="K22" s="253"/>
-      <c r="L22" s="253"/>
-      <c r="M22" s="253"/>
-      <c r="N22" s="253"/>
-      <c r="O22" s="253"/>
-      <c r="P22" s="253"/>
-      <c r="Q22" s="253"/>
-      <c r="R22" s="253"/>
-      <c r="S22" s="253"/>
-      <c r="T22" s="253"/>
-      <c r="U22" s="253"/>
-      <c r="V22" s="253"/>
-      <c r="W22" s="253"/>
-      <c r="X22" s="253"/>
-      <c r="Y22" s="253"/>
-      <c r="Z22" s="253"/>
+      <c r="A22" s="254"/>
+      <c r="B22" s="254"/>
+      <c r="C22" s="254"/>
+      <c r="D22" s="254"/>
+      <c r="E22" s="254"/>
+      <c r="F22" s="254"/>
+      <c r="G22" s="254"/>
+      <c r="H22" s="254"/>
+      <c r="I22" s="254"/>
+      <c r="J22" s="254"/>
+      <c r="K22" s="254"/>
+      <c r="L22" s="254"/>
+      <c r="M22" s="254"/>
+      <c r="N22" s="254"/>
+      <c r="O22" s="254"/>
+      <c r="P22" s="254"/>
+      <c r="Q22" s="254"/>
+      <c r="R22" s="254"/>
+      <c r="S22" s="254"/>
+      <c r="T22" s="254"/>
+      <c r="U22" s="254"/>
+      <c r="V22" s="254"/>
+      <c r="W22" s="254"/>
+      <c r="X22" s="254"/>
+      <c r="Y22" s="254"/>
+      <c r="Z22" s="254"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="253"/>
-      <c r="B23" s="253"/>
-      <c r="C23" s="253"/>
-      <c r="D23" s="253"/>
-      <c r="E23" s="253"/>
-      <c r="F23" s="253"/>
-      <c r="G23" s="253"/>
-      <c r="H23" s="253"/>
-      <c r="I23" s="253"/>
-      <c r="J23" s="253"/>
-      <c r="K23" s="253"/>
-      <c r="L23" s="253"/>
-      <c r="M23" s="253"/>
-      <c r="N23" s="253"/>
-      <c r="O23" s="253"/>
-      <c r="P23" s="253"/>
-      <c r="Q23" s="253"/>
-      <c r="R23" s="253"/>
-      <c r="S23" s="253"/>
-      <c r="T23" s="253"/>
-      <c r="U23" s="253"/>
-      <c r="V23" s="253"/>
-      <c r="W23" s="253"/>
-      <c r="X23" s="253"/>
-      <c r="Y23" s="253"/>
-      <c r="Z23" s="253"/>
+      <c r="A23" s="254"/>
+      <c r="B23" s="254"/>
+      <c r="C23" s="254"/>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="254"/>
+      <c r="G23" s="254"/>
+      <c r="H23" s="254"/>
+      <c r="I23" s="254"/>
+      <c r="J23" s="254"/>
+      <c r="K23" s="254"/>
+      <c r="L23" s="254"/>
+      <c r="M23" s="254"/>
+      <c r="N23" s="254"/>
+      <c r="O23" s="254"/>
+      <c r="P23" s="254"/>
+      <c r="Q23" s="254"/>
+      <c r="R23" s="254"/>
+      <c r="S23" s="254"/>
+      <c r="T23" s="254"/>
+      <c r="U23" s="254"/>
+      <c r="V23" s="254"/>
+      <c r="W23" s="254"/>
+      <c r="X23" s="254"/>
+      <c r="Y23" s="254"/>
+      <c r="Z23" s="254"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="253"/>
-      <c r="B24" s="253"/>
-      <c r="C24" s="253"/>
-      <c r="D24" s="253"/>
-      <c r="E24" s="253"/>
-      <c r="F24" s="253"/>
-      <c r="G24" s="253"/>
-      <c r="H24" s="253"/>
-      <c r="I24" s="253"/>
-      <c r="J24" s="253"/>
-      <c r="K24" s="253"/>
-      <c r="L24" s="253"/>
-      <c r="M24" s="253"/>
-      <c r="N24" s="253"/>
-      <c r="O24" s="253"/>
-      <c r="P24" s="253"/>
-      <c r="Q24" s="253"/>
-      <c r="R24" s="253"/>
-      <c r="S24" s="253"/>
-      <c r="T24" s="253"/>
-      <c r="U24" s="253"/>
-      <c r="V24" s="253"/>
-      <c r="W24" s="253"/>
-      <c r="X24" s="253"/>
-      <c r="Y24" s="253"/>
-      <c r="Z24" s="253"/>
+      <c r="A24" s="254"/>
+      <c r="B24" s="254"/>
+      <c r="C24" s="254"/>
+      <c r="D24" s="254"/>
+      <c r="E24" s="254"/>
+      <c r="F24" s="254"/>
+      <c r="G24" s="254"/>
+      <c r="H24" s="254"/>
+      <c r="I24" s="254"/>
+      <c r="J24" s="254"/>
+      <c r="K24" s="254"/>
+      <c r="L24" s="254"/>
+      <c r="M24" s="254"/>
+      <c r="N24" s="254"/>
+      <c r="O24" s="254"/>
+      <c r="P24" s="254"/>
+      <c r="Q24" s="254"/>
+      <c r="R24" s="254"/>
+      <c r="S24" s="254"/>
+      <c r="T24" s="254"/>
+      <c r="U24" s="254"/>
+      <c r="V24" s="254"/>
+      <c r="W24" s="254"/>
+      <c r="X24" s="254"/>
+      <c r="Y24" s="254"/>
+      <c r="Z24" s="254"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="253"/>
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
-      <c r="D25" s="253"/>
-      <c r="E25" s="253"/>
-      <c r="F25" s="253"/>
-      <c r="G25" s="253"/>
-      <c r="H25" s="253"/>
-      <c r="I25" s="253"/>
-      <c r="J25" s="253"/>
-      <c r="K25" s="253"/>
-      <c r="L25" s="253"/>
-      <c r="M25" s="253"/>
-      <c r="N25" s="253"/>
-      <c r="O25" s="253"/>
-      <c r="P25" s="253"/>
-      <c r="Q25" s="253"/>
-      <c r="R25" s="253"/>
-      <c r="S25" s="253"/>
-      <c r="T25" s="253"/>
-      <c r="U25" s="253"/>
-      <c r="V25" s="253"/>
-      <c r="W25" s="253"/>
-      <c r="X25" s="253"/>
-      <c r="Y25" s="253"/>
-      <c r="Z25" s="253"/>
+      <c r="A25" s="254"/>
+      <c r="B25" s="254"/>
+      <c r="C25" s="254"/>
+      <c r="D25" s="254"/>
+      <c r="E25" s="254"/>
+      <c r="F25" s="254"/>
+      <c r="G25" s="254"/>
+      <c r="H25" s="254"/>
+      <c r="I25" s="254"/>
+      <c r="J25" s="254"/>
+      <c r="K25" s="254"/>
+      <c r="L25" s="254"/>
+      <c r="M25" s="254"/>
+      <c r="N25" s="254"/>
+      <c r="O25" s="254"/>
+      <c r="P25" s="254"/>
+      <c r="Q25" s="254"/>
+      <c r="R25" s="254"/>
+      <c r="S25" s="254"/>
+      <c r="T25" s="254"/>
+      <c r="U25" s="254"/>
+      <c r="V25" s="254"/>
+      <c r="W25" s="254"/>
+      <c r="X25" s="254"/>
+      <c r="Y25" s="254"/>
+      <c r="Z25" s="254"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="253"/>
-      <c r="B26" s="253"/>
-      <c r="C26" s="253"/>
-      <c r="D26" s="253"/>
-      <c r="E26" s="253"/>
-      <c r="F26" s="253"/>
-      <c r="G26" s="253"/>
-      <c r="H26" s="253"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="253"/>
-      <c r="K26" s="253"/>
-      <c r="L26" s="253"/>
-      <c r="M26" s="253"/>
-      <c r="N26" s="253"/>
-      <c r="O26" s="253"/>
-      <c r="P26" s="253"/>
-      <c r="Q26" s="253"/>
-      <c r="R26" s="253"/>
-      <c r="S26" s="253"/>
-      <c r="T26" s="253"/>
-      <c r="U26" s="253"/>
-      <c r="V26" s="253"/>
-      <c r="W26" s="253"/>
-      <c r="X26" s="253"/>
-      <c r="Y26" s="253"/>
-      <c r="Z26" s="253"/>
+      <c r="A26" s="254"/>
+      <c r="B26" s="254"/>
+      <c r="C26" s="254"/>
+      <c r="D26" s="254"/>
+      <c r="E26" s="254"/>
+      <c r="F26" s="254"/>
+      <c r="G26" s="254"/>
+      <c r="H26" s="254"/>
+      <c r="I26" s="254"/>
+      <c r="J26" s="254"/>
+      <c r="K26" s="254"/>
+      <c r="L26" s="254"/>
+      <c r="M26" s="254"/>
+      <c r="N26" s="254"/>
+      <c r="O26" s="254"/>
+      <c r="P26" s="254"/>
+      <c r="Q26" s="254"/>
+      <c r="R26" s="254"/>
+      <c r="S26" s="254"/>
+      <c r="T26" s="254"/>
+      <c r="U26" s="254"/>
+      <c r="V26" s="254"/>
+      <c r="W26" s="254"/>
+      <c r="X26" s="254"/>
+      <c r="Y26" s="254"/>
+      <c r="Z26" s="254"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="253"/>
-      <c r="B27" s="253"/>
-      <c r="C27" s="253"/>
-      <c r="D27" s="253"/>
-      <c r="E27" s="253"/>
-      <c r="F27" s="253"/>
-      <c r="G27" s="253"/>
-      <c r="H27" s="253"/>
-      <c r="I27" s="253"/>
-      <c r="J27" s="253"/>
-      <c r="K27" s="253"/>
-      <c r="L27" s="253"/>
-      <c r="M27" s="253"/>
-      <c r="N27" s="253"/>
-      <c r="O27" s="253"/>
-      <c r="P27" s="253"/>
-      <c r="Q27" s="253"/>
-      <c r="R27" s="253"/>
-      <c r="S27" s="253"/>
-      <c r="T27" s="253"/>
-      <c r="U27" s="253"/>
-      <c r="V27" s="253"/>
-      <c r="W27" s="253"/>
-      <c r="X27" s="253"/>
-      <c r="Y27" s="253"/>
-      <c r="Z27" s="253"/>
+      <c r="A27" s="254"/>
+      <c r="B27" s="254"/>
+      <c r="C27" s="254"/>
+      <c r="D27" s="254"/>
+      <c r="E27" s="254"/>
+      <c r="F27" s="254"/>
+      <c r="G27" s="254"/>
+      <c r="H27" s="254"/>
+      <c r="I27" s="254"/>
+      <c r="J27" s="254"/>
+      <c r="K27" s="254"/>
+      <c r="L27" s="254"/>
+      <c r="M27" s="254"/>
+      <c r="N27" s="254"/>
+      <c r="O27" s="254"/>
+      <c r="P27" s="254"/>
+      <c r="Q27" s="254"/>
+      <c r="R27" s="254"/>
+      <c r="S27" s="254"/>
+      <c r="T27" s="254"/>
+      <c r="U27" s="254"/>
+      <c r="V27" s="254"/>
+      <c r="W27" s="254"/>
+      <c r="X27" s="254"/>
+      <c r="Y27" s="254"/>
+      <c r="Z27" s="254"/>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="253"/>
-      <c r="B28" s="253"/>
-      <c r="C28" s="253"/>
-      <c r="D28" s="253"/>
-      <c r="E28" s="253"/>
-      <c r="F28" s="253"/>
-      <c r="G28" s="253"/>
-      <c r="H28" s="253"/>
-      <c r="I28" s="253"/>
-      <c r="J28" s="253"/>
-      <c r="K28" s="253"/>
-      <c r="L28" s="253"/>
-      <c r="M28" s="253"/>
-      <c r="N28" s="253"/>
-      <c r="O28" s="253"/>
-      <c r="P28" s="253"/>
-      <c r="Q28" s="253"/>
-      <c r="R28" s="253"/>
-      <c r="S28" s="253"/>
-      <c r="T28" s="253"/>
-      <c r="U28" s="253"/>
-      <c r="V28" s="253"/>
-      <c r="W28" s="253"/>
-      <c r="X28" s="253"/>
-      <c r="Y28" s="253"/>
-      <c r="Z28" s="253"/>
+      <c r="A28" s="254"/>
+      <c r="B28" s="254"/>
+      <c r="C28" s="254"/>
+      <c r="D28" s="254"/>
+      <c r="E28" s="254"/>
+      <c r="F28" s="254"/>
+      <c r="G28" s="254"/>
+      <c r="H28" s="254"/>
+      <c r="I28" s="254"/>
+      <c r="J28" s="254"/>
+      <c r="K28" s="254"/>
+      <c r="L28" s="254"/>
+      <c r="M28" s="254"/>
+      <c r="N28" s="254"/>
+      <c r="O28" s="254"/>
+      <c r="P28" s="254"/>
+      <c r="Q28" s="254"/>
+      <c r="R28" s="254"/>
+      <c r="S28" s="254"/>
+      <c r="T28" s="254"/>
+      <c r="U28" s="254"/>
+      <c r="V28" s="254"/>
+      <c r="W28" s="254"/>
+      <c r="X28" s="254"/>
+      <c r="Y28" s="254"/>
+      <c r="Z28" s="254"/>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="253"/>
-      <c r="B29" s="253"/>
-      <c r="C29" s="253"/>
-      <c r="D29" s="253"/>
-      <c r="E29" s="253"/>
-      <c r="F29" s="253"/>
-      <c r="G29" s="253"/>
-      <c r="H29" s="253"/>
-      <c r="I29" s="253"/>
-      <c r="J29" s="253"/>
-      <c r="K29" s="253"/>
-      <c r="L29" s="253"/>
-      <c r="M29" s="253"/>
-      <c r="N29" s="253"/>
-      <c r="O29" s="253"/>
-      <c r="P29" s="253"/>
-      <c r="Q29" s="253"/>
-      <c r="R29" s="253"/>
-      <c r="S29" s="253"/>
-      <c r="T29" s="253"/>
-      <c r="U29" s="253"/>
-      <c r="V29" s="253"/>
-      <c r="W29" s="253"/>
-      <c r="X29" s="253"/>
-      <c r="Y29" s="253"/>
-      <c r="Z29" s="253"/>
+      <c r="A29" s="254"/>
+      <c r="B29" s="254"/>
+      <c r="C29" s="254"/>
+      <c r="D29" s="254"/>
+      <c r="E29" s="254"/>
+      <c r="F29" s="254"/>
+      <c r="G29" s="254"/>
+      <c r="H29" s="254"/>
+      <c r="I29" s="254"/>
+      <c r="J29" s="254"/>
+      <c r="K29" s="254"/>
+      <c r="L29" s="254"/>
+      <c r="M29" s="254"/>
+      <c r="N29" s="254"/>
+      <c r="O29" s="254"/>
+      <c r="P29" s="254"/>
+      <c r="Q29" s="254"/>
+      <c r="R29" s="254"/>
+      <c r="S29" s="254"/>
+      <c r="T29" s="254"/>
+      <c r="U29" s="254"/>
+      <c r="V29" s="254"/>
+      <c r="W29" s="254"/>
+      <c r="X29" s="254"/>
+      <c r="Y29" s="254"/>
+      <c r="Z29" s="254"/>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="253"/>
-      <c r="B30" s="253"/>
-      <c r="C30" s="253"/>
-      <c r="D30" s="253"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="253"/>
-      <c r="G30" s="253"/>
-      <c r="H30" s="253"/>
-      <c r="I30" s="253"/>
-      <c r="J30" s="253"/>
-      <c r="K30" s="253"/>
-      <c r="L30" s="253"/>
-      <c r="M30" s="253"/>
-      <c r="N30" s="253"/>
-      <c r="O30" s="253"/>
-      <c r="P30" s="253"/>
-      <c r="Q30" s="253"/>
-      <c r="R30" s="253"/>
-      <c r="S30" s="253"/>
-      <c r="T30" s="253"/>
-      <c r="U30" s="253"/>
-      <c r="V30" s="253"/>
-      <c r="W30" s="253"/>
-      <c r="X30" s="253"/>
-      <c r="Y30" s="253"/>
-      <c r="Z30" s="253"/>
+      <c r="A30" s="254"/>
+      <c r="B30" s="254"/>
+      <c r="C30" s="254"/>
+      <c r="D30" s="254"/>
+      <c r="E30" s="254"/>
+      <c r="F30" s="254"/>
+      <c r="G30" s="254"/>
+      <c r="H30" s="254"/>
+      <c r="I30" s="254"/>
+      <c r="J30" s="254"/>
+      <c r="K30" s="254"/>
+      <c r="L30" s="254"/>
+      <c r="M30" s="254"/>
+      <c r="N30" s="254"/>
+      <c r="O30" s="254"/>
+      <c r="P30" s="254"/>
+      <c r="Q30" s="254"/>
+      <c r="R30" s="254"/>
+      <c r="S30" s="254"/>
+      <c r="T30" s="254"/>
+      <c r="U30" s="254"/>
+      <c r="V30" s="254"/>
+      <c r="W30" s="254"/>
+      <c r="X30" s="254"/>
+      <c r="Y30" s="254"/>
+      <c r="Z30" s="254"/>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="253"/>
-      <c r="B31" s="253"/>
-      <c r="C31" s="253"/>
-      <c r="D31" s="253"/>
-      <c r="E31" s="253"/>
-      <c r="F31" s="253"/>
-      <c r="G31" s="253"/>
-      <c r="H31" s="253"/>
-      <c r="I31" s="253"/>
-      <c r="J31" s="253"/>
-      <c r="K31" s="253"/>
-      <c r="L31" s="253"/>
-      <c r="M31" s="253"/>
-      <c r="N31" s="253"/>
-      <c r="O31" s="253"/>
-      <c r="P31" s="253"/>
-      <c r="Q31" s="253"/>
-      <c r="R31" s="253"/>
-      <c r="S31" s="253"/>
-      <c r="T31" s="253"/>
-      <c r="U31" s="253"/>
-      <c r="V31" s="253"/>
-      <c r="W31" s="253"/>
-      <c r="X31" s="253"/>
-      <c r="Y31" s="253"/>
-      <c r="Z31" s="253"/>
+      <c r="A31" s="254"/>
+      <c r="B31" s="254"/>
+      <c r="C31" s="254"/>
+      <c r="D31" s="254"/>
+      <c r="E31" s="254"/>
+      <c r="F31" s="254"/>
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="254"/>
+      <c r="K31" s="254"/>
+      <c r="L31" s="254"/>
+      <c r="M31" s="254"/>
+      <c r="N31" s="254"/>
+      <c r="O31" s="254"/>
+      <c r="P31" s="254"/>
+      <c r="Q31" s="254"/>
+      <c r="R31" s="254"/>
+      <c r="S31" s="254"/>
+      <c r="T31" s="254"/>
+      <c r="U31" s="254"/>
+      <c r="V31" s="254"/>
+      <c r="W31" s="254"/>
+      <c r="X31" s="254"/>
+      <c r="Y31" s="254"/>
+      <c r="Z31" s="254"/>
     </row>
     <row r="32" spans="1:26">
-      <c r="A32" s="254" t="s">
+      <c r="A32" s="255" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="254"/>
-      <c r="C32" s="254"/>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="254"/>
-      <c r="G32" s="254"/>
-      <c r="H32" s="254"/>
-      <c r="I32" s="254"/>
-      <c r="J32" s="254"/>
-      <c r="K32" s="254"/>
-      <c r="L32" s="254"/>
-      <c r="M32" s="254"/>
-      <c r="N32" s="254"/>
-      <c r="O32" s="254"/>
-      <c r="P32" s="254"/>
-      <c r="Q32" s="254"/>
-      <c r="R32" s="254"/>
-      <c r="S32" s="254"/>
-      <c r="T32" s="254"/>
-      <c r="U32" s="254"/>
-      <c r="V32" s="254"/>
-      <c r="W32" s="254"/>
-      <c r="X32" s="254"/>
-      <c r="Y32" s="254"/>
-      <c r="Z32" s="254"/>
+      <c r="B32" s="255"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="255"/>
+      <c r="E32" s="255"/>
+      <c r="F32" s="255"/>
+      <c r="G32" s="255"/>
+      <c r="H32" s="255"/>
+      <c r="I32" s="255"/>
+      <c r="J32" s="255"/>
+      <c r="K32" s="255"/>
+      <c r="L32" s="255"/>
+      <c r="M32" s="255"/>
+      <c r="N32" s="255"/>
+      <c r="O32" s="255"/>
+      <c r="P32" s="255"/>
+      <c r="Q32" s="255"/>
+      <c r="R32" s="255"/>
+      <c r="S32" s="255"/>
+      <c r="T32" s="255"/>
+      <c r="U32" s="255"/>
+      <c r="V32" s="255"/>
+      <c r="W32" s="255"/>
+      <c r="X32" s="255"/>
+      <c r="Y32" s="255"/>
+      <c r="Z32" s="255"/>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="254"/>
-      <c r="B33" s="254"/>
-      <c r="C33" s="254"/>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
-      <c r="F33" s="254"/>
-      <c r="G33" s="254"/>
-      <c r="H33" s="254"/>
-      <c r="I33" s="254"/>
-      <c r="J33" s="254"/>
-      <c r="K33" s="254"/>
-      <c r="L33" s="254"/>
-      <c r="M33" s="254"/>
-      <c r="N33" s="254"/>
-      <c r="O33" s="254"/>
-      <c r="P33" s="254"/>
-      <c r="Q33" s="254"/>
-      <c r="R33" s="254"/>
-      <c r="S33" s="254"/>
-      <c r="T33" s="254"/>
-      <c r="U33" s="254"/>
-      <c r="V33" s="254"/>
-      <c r="W33" s="254"/>
-      <c r="X33" s="254"/>
-      <c r="Y33" s="254"/>
-      <c r="Z33" s="254"/>
+      <c r="A33" s="255"/>
+      <c r="B33" s="255"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
+      <c r="F33" s="255"/>
+      <c r="G33" s="255"/>
+      <c r="H33" s="255"/>
+      <c r="I33" s="255"/>
+      <c r="J33" s="255"/>
+      <c r="K33" s="255"/>
+      <c r="L33" s="255"/>
+      <c r="M33" s="255"/>
+      <c r="N33" s="255"/>
+      <c r="O33" s="255"/>
+      <c r="P33" s="255"/>
+      <c r="Q33" s="255"/>
+      <c r="R33" s="255"/>
+      <c r="S33" s="255"/>
+      <c r="T33" s="255"/>
+      <c r="U33" s="255"/>
+      <c r="V33" s="255"/>
+      <c r="W33" s="255"/>
+      <c r="X33" s="255"/>
+      <c r="Y33" s="255"/>
+      <c r="Z33" s="255"/>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="254"/>
-      <c r="B34" s="254"/>
-      <c r="C34" s="254"/>
-      <c r="D34" s="254"/>
-      <c r="E34" s="254"/>
-      <c r="F34" s="254"/>
-      <c r="G34" s="254"/>
-      <c r="H34" s="254"/>
-      <c r="I34" s="254"/>
-      <c r="J34" s="254"/>
-      <c r="K34" s="254"/>
-      <c r="L34" s="254"/>
-      <c r="M34" s="254"/>
-      <c r="N34" s="254"/>
-      <c r="O34" s="254"/>
-      <c r="P34" s="254"/>
-      <c r="Q34" s="254"/>
-      <c r="R34" s="254"/>
-      <c r="S34" s="254"/>
-      <c r="T34" s="254"/>
-      <c r="U34" s="254"/>
-      <c r="V34" s="254"/>
-      <c r="W34" s="254"/>
-      <c r="X34" s="254"/>
-      <c r="Y34" s="254"/>
-      <c r="Z34" s="254"/>
+      <c r="A34" s="255"/>
+      <c r="B34" s="255"/>
+      <c r="C34" s="255"/>
+      <c r="D34" s="255"/>
+      <c r="E34" s="255"/>
+      <c r="F34" s="255"/>
+      <c r="G34" s="255"/>
+      <c r="H34" s="255"/>
+      <c r="I34" s="255"/>
+      <c r="J34" s="255"/>
+      <c r="K34" s="255"/>
+      <c r="L34" s="255"/>
+      <c r="M34" s="255"/>
+      <c r="N34" s="255"/>
+      <c r="O34" s="255"/>
+      <c r="P34" s="255"/>
+      <c r="Q34" s="255"/>
+      <c r="R34" s="255"/>
+      <c r="S34" s="255"/>
+      <c r="T34" s="255"/>
+      <c r="U34" s="255"/>
+      <c r="V34" s="255"/>
+      <c r="W34" s="255"/>
+      <c r="X34" s="255"/>
+      <c r="Y34" s="255"/>
+      <c r="Z34" s="255"/>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="254"/>
-      <c r="B35" s="254"/>
-      <c r="C35" s="254"/>
-      <c r="D35" s="254"/>
-      <c r="E35" s="254"/>
-      <c r="F35" s="254"/>
-      <c r="G35" s="254"/>
-      <c r="H35" s="254"/>
-      <c r="I35" s="254"/>
-      <c r="J35" s="254"/>
-      <c r="K35" s="254"/>
-      <c r="L35" s="254"/>
-      <c r="M35" s="254"/>
-      <c r="N35" s="254"/>
-      <c r="O35" s="254"/>
-      <c r="P35" s="254"/>
-      <c r="Q35" s="254"/>
-      <c r="R35" s="254"/>
-      <c r="S35" s="254"/>
-      <c r="T35" s="254"/>
-      <c r="U35" s="254"/>
-      <c r="V35" s="254"/>
-      <c r="W35" s="254"/>
-      <c r="X35" s="254"/>
-      <c r="Y35" s="254"/>
-      <c r="Z35" s="254"/>
+      <c r="A35" s="255"/>
+      <c r="B35" s="255"/>
+      <c r="C35" s="255"/>
+      <c r="D35" s="255"/>
+      <c r="E35" s="255"/>
+      <c r="F35" s="255"/>
+      <c r="G35" s="255"/>
+      <c r="H35" s="255"/>
+      <c r="I35" s="255"/>
+      <c r="J35" s="255"/>
+      <c r="K35" s="255"/>
+      <c r="L35" s="255"/>
+      <c r="M35" s="255"/>
+      <c r="N35" s="255"/>
+      <c r="O35" s="255"/>
+      <c r="P35" s="255"/>
+      <c r="Q35" s="255"/>
+      <c r="R35" s="255"/>
+      <c r="S35" s="255"/>
+      <c r="T35" s="255"/>
+      <c r="U35" s="255"/>
+      <c r="V35" s="255"/>
+      <c r="W35" s="255"/>
+      <c r="X35" s="255"/>
+      <c r="Y35" s="255"/>
+      <c r="Z35" s="255"/>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="254"/>
-      <c r="B36" s="254"/>
-      <c r="C36" s="254"/>
-      <c r="D36" s="254"/>
-      <c r="E36" s="254"/>
-      <c r="F36" s="254"/>
-      <c r="G36" s="254"/>
-      <c r="H36" s="254"/>
-      <c r="I36" s="254"/>
-      <c r="J36" s="254"/>
-      <c r="K36" s="254"/>
-      <c r="L36" s="254"/>
-      <c r="M36" s="254"/>
-      <c r="N36" s="254"/>
-      <c r="O36" s="254"/>
-      <c r="P36" s="254"/>
-      <c r="Q36" s="254"/>
-      <c r="R36" s="254"/>
-      <c r="S36" s="254"/>
-      <c r="T36" s="254"/>
-      <c r="U36" s="254"/>
-      <c r="V36" s="254"/>
-      <c r="W36" s="254"/>
-      <c r="X36" s="254"/>
-      <c r="Y36" s="254"/>
-      <c r="Z36" s="254"/>
+      <c r="A36" s="255"/>
+      <c r="B36" s="255"/>
+      <c r="C36" s="255"/>
+      <c r="D36" s="255"/>
+      <c r="E36" s="255"/>
+      <c r="F36" s="255"/>
+      <c r="G36" s="255"/>
+      <c r="H36" s="255"/>
+      <c r="I36" s="255"/>
+      <c r="J36" s="255"/>
+      <c r="K36" s="255"/>
+      <c r="L36" s="255"/>
+      <c r="M36" s="255"/>
+      <c r="N36" s="255"/>
+      <c r="O36" s="255"/>
+      <c r="P36" s="255"/>
+      <c r="Q36" s="255"/>
+      <c r="R36" s="255"/>
+      <c r="S36" s="255"/>
+      <c r="T36" s="255"/>
+      <c r="U36" s="255"/>
+      <c r="V36" s="255"/>
+      <c r="W36" s="255"/>
+      <c r="X36" s="255"/>
+      <c r="Y36" s="255"/>
+      <c r="Z36" s="255"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="254"/>
-      <c r="B37" s="254"/>
-      <c r="C37" s="254"/>
-      <c r="D37" s="254"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="254"/>
-      <c r="G37" s="254"/>
-      <c r="H37" s="254"/>
-      <c r="I37" s="254"/>
-      <c r="J37" s="254"/>
-      <c r="K37" s="254"/>
-      <c r="L37" s="254"/>
-      <c r="M37" s="254"/>
-      <c r="N37" s="254"/>
-      <c r="O37" s="254"/>
-      <c r="P37" s="254"/>
-      <c r="Q37" s="254"/>
-      <c r="R37" s="254"/>
-      <c r="S37" s="254"/>
-      <c r="T37" s="254"/>
-      <c r="U37" s="254"/>
-      <c r="V37" s="254"/>
-      <c r="W37" s="254"/>
-      <c r="X37" s="254"/>
-      <c r="Y37" s="254"/>
-      <c r="Z37" s="254"/>
+      <c r="A37" s="255"/>
+      <c r="B37" s="255"/>
+      <c r="C37" s="255"/>
+      <c r="D37" s="255"/>
+      <c r="E37" s="255"/>
+      <c r="F37" s="255"/>
+      <c r="G37" s="255"/>
+      <c r="H37" s="255"/>
+      <c r="I37" s="255"/>
+      <c r="J37" s="255"/>
+      <c r="K37" s="255"/>
+      <c r="L37" s="255"/>
+      <c r="M37" s="255"/>
+      <c r="N37" s="255"/>
+      <c r="O37" s="255"/>
+      <c r="P37" s="255"/>
+      <c r="Q37" s="255"/>
+      <c r="R37" s="255"/>
+      <c r="S37" s="255"/>
+      <c r="T37" s="255"/>
+      <c r="U37" s="255"/>
+      <c r="V37" s="255"/>
+      <c r="W37" s="255"/>
+      <c r="X37" s="255"/>
+      <c r="Y37" s="255"/>
+      <c r="Z37" s="255"/>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="254"/>
-      <c r="B38" s="254"/>
-      <c r="C38" s="254"/>
-      <c r="D38" s="254"/>
-      <c r="E38" s="254"/>
-      <c r="F38" s="254"/>
-      <c r="G38" s="254"/>
-      <c r="H38" s="254"/>
-      <c r="I38" s="254"/>
-      <c r="J38" s="254"/>
-      <c r="K38" s="254"/>
-      <c r="L38" s="254"/>
-      <c r="M38" s="254"/>
-      <c r="N38" s="254"/>
-      <c r="O38" s="254"/>
-      <c r="P38" s="254"/>
-      <c r="Q38" s="254"/>
-      <c r="R38" s="254"/>
-      <c r="S38" s="254"/>
-      <c r="T38" s="254"/>
-      <c r="U38" s="254"/>
-      <c r="V38" s="254"/>
-      <c r="W38" s="254"/>
-      <c r="X38" s="254"/>
-      <c r="Y38" s="254"/>
-      <c r="Z38" s="254"/>
+      <c r="A38" s="255"/>
+      <c r="B38" s="255"/>
+      <c r="C38" s="255"/>
+      <c r="D38" s="255"/>
+      <c r="E38" s="255"/>
+      <c r="F38" s="255"/>
+      <c r="G38" s="255"/>
+      <c r="H38" s="255"/>
+      <c r="I38" s="255"/>
+      <c r="J38" s="255"/>
+      <c r="K38" s="255"/>
+      <c r="L38" s="255"/>
+      <c r="M38" s="255"/>
+      <c r="N38" s="255"/>
+      <c r="O38" s="255"/>
+      <c r="P38" s="255"/>
+      <c r="Q38" s="255"/>
+      <c r="R38" s="255"/>
+      <c r="S38" s="255"/>
+      <c r="T38" s="255"/>
+      <c r="U38" s="255"/>
+      <c r="V38" s="255"/>
+      <c r="W38" s="255"/>
+      <c r="X38" s="255"/>
+      <c r="Y38" s="255"/>
+      <c r="Z38" s="255"/>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="254"/>
-      <c r="B39" s="254"/>
-      <c r="C39" s="254"/>
-      <c r="D39" s="254"/>
-      <c r="E39" s="254"/>
-      <c r="F39" s="254"/>
-      <c r="G39" s="254"/>
-      <c r="H39" s="254"/>
-      <c r="I39" s="254"/>
-      <c r="J39" s="254"/>
-      <c r="K39" s="254"/>
-      <c r="L39" s="254"/>
-      <c r="M39" s="254"/>
-      <c r="N39" s="254"/>
-      <c r="O39" s="254"/>
-      <c r="P39" s="254"/>
-      <c r="Q39" s="254"/>
-      <c r="R39" s="254"/>
-      <c r="S39" s="254"/>
-      <c r="T39" s="254"/>
-      <c r="U39" s="254"/>
-      <c r="V39" s="254"/>
-      <c r="W39" s="254"/>
-      <c r="X39" s="254"/>
-      <c r="Y39" s="254"/>
-      <c r="Z39" s="254"/>
+      <c r="A39" s="255"/>
+      <c r="B39" s="255"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="255"/>
+      <c r="E39" s="255"/>
+      <c r="F39" s="255"/>
+      <c r="G39" s="255"/>
+      <c r="H39" s="255"/>
+      <c r="I39" s="255"/>
+      <c r="J39" s="255"/>
+      <c r="K39" s="255"/>
+      <c r="L39" s="255"/>
+      <c r="M39" s="255"/>
+      <c r="N39" s="255"/>
+      <c r="O39" s="255"/>
+      <c r="P39" s="255"/>
+      <c r="Q39" s="255"/>
+      <c r="R39" s="255"/>
+      <c r="S39" s="255"/>
+      <c r="T39" s="255"/>
+      <c r="U39" s="255"/>
+      <c r="V39" s="255"/>
+      <c r="W39" s="255"/>
+      <c r="X39" s="255"/>
+      <c r="Y39" s="255"/>
+      <c r="Z39" s="255"/>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="254"/>
-      <c r="B40" s="254"/>
-      <c r="C40" s="254"/>
-      <c r="D40" s="254"/>
-      <c r="E40" s="254"/>
-      <c r="F40" s="254"/>
-      <c r="G40" s="254"/>
-      <c r="H40" s="254"/>
-      <c r="I40" s="254"/>
-      <c r="J40" s="254"/>
-      <c r="K40" s="254"/>
-      <c r="L40" s="254"/>
-      <c r="M40" s="254"/>
-      <c r="N40" s="254"/>
-      <c r="O40" s="254"/>
-      <c r="P40" s="254"/>
-      <c r="Q40" s="254"/>
-      <c r="R40" s="254"/>
-      <c r="S40" s="254"/>
-      <c r="T40" s="254"/>
-      <c r="U40" s="254"/>
-      <c r="V40" s="254"/>
-      <c r="W40" s="254"/>
-      <c r="X40" s="254"/>
-      <c r="Y40" s="254"/>
-      <c r="Z40" s="254"/>
+      <c r="A40" s="255"/>
+      <c r="B40" s="255"/>
+      <c r="C40" s="255"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
+      <c r="F40" s="255"/>
+      <c r="G40" s="255"/>
+      <c r="H40" s="255"/>
+      <c r="I40" s="255"/>
+      <c r="J40" s="255"/>
+      <c r="K40" s="255"/>
+      <c r="L40" s="255"/>
+      <c r="M40" s="255"/>
+      <c r="N40" s="255"/>
+      <c r="O40" s="255"/>
+      <c r="P40" s="255"/>
+      <c r="Q40" s="255"/>
+      <c r="R40" s="255"/>
+      <c r="S40" s="255"/>
+      <c r="T40" s="255"/>
+      <c r="U40" s="255"/>
+      <c r="V40" s="255"/>
+      <c r="W40" s="255"/>
+      <c r="X40" s="255"/>
+      <c r="Y40" s="255"/>
+      <c r="Z40" s="255"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="254"/>
-      <c r="B41" s="254"/>
-      <c r="C41" s="254"/>
-      <c r="D41" s="254"/>
-      <c r="E41" s="254"/>
-      <c r="F41" s="254"/>
-      <c r="G41" s="254"/>
-      <c r="H41" s="254"/>
-      <c r="I41" s="254"/>
-      <c r="J41" s="254"/>
-      <c r="K41" s="254"/>
-      <c r="L41" s="254"/>
-      <c r="M41" s="254"/>
-      <c r="N41" s="254"/>
-      <c r="O41" s="254"/>
-      <c r="P41" s="254"/>
-      <c r="Q41" s="254"/>
-      <c r="R41" s="254"/>
-      <c r="S41" s="254"/>
-      <c r="T41" s="254"/>
-      <c r="U41" s="254"/>
-      <c r="V41" s="254"/>
-      <c r="W41" s="254"/>
-      <c r="X41" s="254"/>
-      <c r="Y41" s="254"/>
-      <c r="Z41" s="254"/>
+      <c r="A41" s="255"/>
+      <c r="B41" s="255"/>
+      <c r="C41" s="255"/>
+      <c r="D41" s="255"/>
+      <c r="E41" s="255"/>
+      <c r="F41" s="255"/>
+      <c r="G41" s="255"/>
+      <c r="H41" s="255"/>
+      <c r="I41" s="255"/>
+      <c r="J41" s="255"/>
+      <c r="K41" s="255"/>
+      <c r="L41" s="255"/>
+      <c r="M41" s="255"/>
+      <c r="N41" s="255"/>
+      <c r="O41" s="255"/>
+      <c r="P41" s="255"/>
+      <c r="Q41" s="255"/>
+      <c r="R41" s="255"/>
+      <c r="S41" s="255"/>
+      <c r="T41" s="255"/>
+      <c r="U41" s="255"/>
+      <c r="V41" s="255"/>
+      <c r="W41" s="255"/>
+      <c r="X41" s="255"/>
+      <c r="Y41" s="255"/>
+      <c r="Z41" s="255"/>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="254"/>
-      <c r="B42" s="254"/>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="254"/>
-      <c r="G42" s="254"/>
-      <c r="H42" s="254"/>
-      <c r="I42" s="254"/>
-      <c r="J42" s="254"/>
-      <c r="K42" s="254"/>
-      <c r="L42" s="254"/>
-      <c r="M42" s="254"/>
-      <c r="N42" s="254"/>
-      <c r="O42" s="254"/>
-      <c r="P42" s="254"/>
-      <c r="Q42" s="254"/>
-      <c r="R42" s="254"/>
-      <c r="S42" s="254"/>
-      <c r="T42" s="254"/>
-      <c r="U42" s="254"/>
-      <c r="V42" s="254"/>
-      <c r="W42" s="254"/>
-      <c r="X42" s="254"/>
-      <c r="Y42" s="254"/>
-      <c r="Z42" s="254"/>
+      <c r="A42" s="255"/>
+      <c r="B42" s="255"/>
+      <c r="C42" s="255"/>
+      <c r="D42" s="255"/>
+      <c r="E42" s="255"/>
+      <c r="F42" s="255"/>
+      <c r="G42" s="255"/>
+      <c r="H42" s="255"/>
+      <c r="I42" s="255"/>
+      <c r="J42" s="255"/>
+      <c r="K42" s="255"/>
+      <c r="L42" s="255"/>
+      <c r="M42" s="255"/>
+      <c r="N42" s="255"/>
+      <c r="O42" s="255"/>
+      <c r="P42" s="255"/>
+      <c r="Q42" s="255"/>
+      <c r="R42" s="255"/>
+      <c r="S42" s="255"/>
+      <c r="T42" s="255"/>
+      <c r="U42" s="255"/>
+      <c r="V42" s="255"/>
+      <c r="W42" s="255"/>
+      <c r="X42" s="255"/>
+      <c r="Y42" s="255"/>
+      <c r="Z42" s="255"/>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="254"/>
-      <c r="B43" s="254"/>
-      <c r="C43" s="254"/>
-      <c r="D43" s="254"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="254"/>
-      <c r="G43" s="254"/>
-      <c r="H43" s="254"/>
-      <c r="I43" s="254"/>
-      <c r="J43" s="254"/>
-      <c r="K43" s="254"/>
-      <c r="L43" s="254"/>
-      <c r="M43" s="254"/>
-      <c r="N43" s="254"/>
-      <c r="O43" s="254"/>
-      <c r="P43" s="254"/>
-      <c r="Q43" s="254"/>
-      <c r="R43" s="254"/>
-      <c r="S43" s="254"/>
-      <c r="T43" s="254"/>
-      <c r="U43" s="254"/>
-      <c r="V43" s="254"/>
-      <c r="W43" s="254"/>
-      <c r="X43" s="254"/>
-      <c r="Y43" s="254"/>
-      <c r="Z43" s="254"/>
+      <c r="A43" s="255"/>
+      <c r="B43" s="255"/>
+      <c r="C43" s="255"/>
+      <c r="D43" s="255"/>
+      <c r="E43" s="255"/>
+      <c r="F43" s="255"/>
+      <c r="G43" s="255"/>
+      <c r="H43" s="255"/>
+      <c r="I43" s="255"/>
+      <c r="J43" s="255"/>
+      <c r="K43" s="255"/>
+      <c r="L43" s="255"/>
+      <c r="M43" s="255"/>
+      <c r="N43" s="255"/>
+      <c r="O43" s="255"/>
+      <c r="P43" s="255"/>
+      <c r="Q43" s="255"/>
+      <c r="R43" s="255"/>
+      <c r="S43" s="255"/>
+      <c r="T43" s="255"/>
+      <c r="U43" s="255"/>
+      <c r="V43" s="255"/>
+      <c r="W43" s="255"/>
+      <c r="X43" s="255"/>
+      <c r="Y43" s="255"/>
+      <c r="Z43" s="255"/>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="254"/>
-      <c r="B44" s="254"/>
-      <c r="C44" s="254"/>
-      <c r="D44" s="254"/>
-      <c r="E44" s="254"/>
-      <c r="F44" s="254"/>
-      <c r="G44" s="254"/>
-      <c r="H44" s="254"/>
-      <c r="I44" s="254"/>
-      <c r="J44" s="254"/>
-      <c r="K44" s="254"/>
-      <c r="L44" s="254"/>
-      <c r="M44" s="254"/>
-      <c r="N44" s="254"/>
-      <c r="O44" s="254"/>
-      <c r="P44" s="254"/>
-      <c r="Q44" s="254"/>
-      <c r="R44" s="254"/>
-      <c r="S44" s="254"/>
-      <c r="T44" s="254"/>
-      <c r="U44" s="254"/>
-      <c r="V44" s="254"/>
-      <c r="W44" s="254"/>
-      <c r="X44" s="254"/>
-      <c r="Y44" s="254"/>
-      <c r="Z44" s="254"/>
+      <c r="A44" s="255"/>
+      <c r="B44" s="255"/>
+      <c r="C44" s="255"/>
+      <c r="D44" s="255"/>
+      <c r="E44" s="255"/>
+      <c r="F44" s="255"/>
+      <c r="G44" s="255"/>
+      <c r="H44" s="255"/>
+      <c r="I44" s="255"/>
+      <c r="J44" s="255"/>
+      <c r="K44" s="255"/>
+      <c r="L44" s="255"/>
+      <c r="M44" s="255"/>
+      <c r="N44" s="255"/>
+      <c r="O44" s="255"/>
+      <c r="P44" s="255"/>
+      <c r="Q44" s="255"/>
+      <c r="R44" s="255"/>
+      <c r="S44" s="255"/>
+      <c r="T44" s="255"/>
+      <c r="U44" s="255"/>
+      <c r="V44" s="255"/>
+      <c r="W44" s="255"/>
+      <c r="X44" s="255"/>
+      <c r="Y44" s="255"/>
+      <c r="Z44" s="255"/>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="254"/>
-      <c r="B45" s="254"/>
-      <c r="C45" s="254"/>
-      <c r="D45" s="254"/>
-      <c r="E45" s="254"/>
-      <c r="F45" s="254"/>
-      <c r="G45" s="254"/>
-      <c r="H45" s="254"/>
-      <c r="I45" s="254"/>
-      <c r="J45" s="254"/>
-      <c r="K45" s="254"/>
-      <c r="L45" s="254"/>
-      <c r="M45" s="254"/>
-      <c r="N45" s="254"/>
-      <c r="O45" s="254"/>
-      <c r="P45" s="254"/>
-      <c r="Q45" s="254"/>
-      <c r="R45" s="254"/>
-      <c r="S45" s="254"/>
-      <c r="T45" s="254"/>
-      <c r="U45" s="254"/>
-      <c r="V45" s="254"/>
-      <c r="W45" s="254"/>
-      <c r="X45" s="254"/>
-      <c r="Y45" s="254"/>
-      <c r="Z45" s="254"/>
+      <c r="A45" s="255"/>
+      <c r="B45" s="255"/>
+      <c r="C45" s="255"/>
+      <c r="D45" s="255"/>
+      <c r="E45" s="255"/>
+      <c r="F45" s="255"/>
+      <c r="G45" s="255"/>
+      <c r="H45" s="255"/>
+      <c r="I45" s="255"/>
+      <c r="J45" s="255"/>
+      <c r="K45" s="255"/>
+      <c r="L45" s="255"/>
+      <c r="M45" s="255"/>
+      <c r="N45" s="255"/>
+      <c r="O45" s="255"/>
+      <c r="P45" s="255"/>
+      <c r="Q45" s="255"/>
+      <c r="R45" s="255"/>
+      <c r="S45" s="255"/>
+      <c r="T45" s="255"/>
+      <c r="U45" s="255"/>
+      <c r="V45" s="255"/>
+      <c r="W45" s="255"/>
+      <c r="X45" s="255"/>
+      <c r="Y45" s="255"/>
+      <c r="Z45" s="255"/>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="254"/>
-      <c r="B46" s="254"/>
-      <c r="C46" s="254"/>
-      <c r="D46" s="254"/>
-      <c r="E46" s="254"/>
-      <c r="F46" s="254"/>
-      <c r="G46" s="254"/>
-      <c r="H46" s="254"/>
-      <c r="I46" s="254"/>
-      <c r="J46" s="254"/>
-      <c r="K46" s="254"/>
-      <c r="L46" s="254"/>
-      <c r="M46" s="254"/>
-      <c r="N46" s="254"/>
-      <c r="O46" s="254"/>
-      <c r="P46" s="254"/>
-      <c r="Q46" s="254"/>
-      <c r="R46" s="254"/>
-      <c r="S46" s="254"/>
-      <c r="T46" s="254"/>
-      <c r="U46" s="254"/>
-      <c r="V46" s="254"/>
-      <c r="W46" s="254"/>
-      <c r="X46" s="254"/>
-      <c r="Y46" s="254"/>
-      <c r="Z46" s="254"/>
+      <c r="A46" s="255"/>
+      <c r="B46" s="255"/>
+      <c r="C46" s="255"/>
+      <c r="D46" s="255"/>
+      <c r="E46" s="255"/>
+      <c r="F46" s="255"/>
+      <c r="G46" s="255"/>
+      <c r="H46" s="255"/>
+      <c r="I46" s="255"/>
+      <c r="J46" s="255"/>
+      <c r="K46" s="255"/>
+      <c r="L46" s="255"/>
+      <c r="M46" s="255"/>
+      <c r="N46" s="255"/>
+      <c r="O46" s="255"/>
+      <c r="P46" s="255"/>
+      <c r="Q46" s="255"/>
+      <c r="R46" s="255"/>
+      <c r="S46" s="255"/>
+      <c r="T46" s="255"/>
+      <c r="U46" s="255"/>
+      <c r="V46" s="255"/>
+      <c r="W46" s="255"/>
+      <c r="X46" s="255"/>
+      <c r="Y46" s="255"/>
+      <c r="Z46" s="255"/>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="254"/>
-      <c r="B47" s="254"/>
-      <c r="C47" s="254"/>
-      <c r="D47" s="254"/>
-      <c r="E47" s="254"/>
-      <c r="F47" s="254"/>
-      <c r="G47" s="254"/>
-      <c r="H47" s="254"/>
-      <c r="I47" s="254"/>
-      <c r="J47" s="254"/>
-      <c r="K47" s="254"/>
-      <c r="L47" s="254"/>
-      <c r="M47" s="254"/>
-      <c r="N47" s="254"/>
-      <c r="O47" s="254"/>
-      <c r="P47" s="254"/>
-      <c r="Q47" s="254"/>
-      <c r="R47" s="254"/>
-      <c r="S47" s="254"/>
-      <c r="T47" s="254"/>
-      <c r="U47" s="254"/>
-      <c r="V47" s="254"/>
-      <c r="W47" s="254"/>
-      <c r="X47" s="254"/>
-      <c r="Y47" s="254"/>
-      <c r="Z47" s="254"/>
+      <c r="A47" s="255"/>
+      <c r="B47" s="255"/>
+      <c r="C47" s="255"/>
+      <c r="D47" s="255"/>
+      <c r="E47" s="255"/>
+      <c r="F47" s="255"/>
+      <c r="G47" s="255"/>
+      <c r="H47" s="255"/>
+      <c r="I47" s="255"/>
+      <c r="J47" s="255"/>
+      <c r="K47" s="255"/>
+      <c r="L47" s="255"/>
+      <c r="M47" s="255"/>
+      <c r="N47" s="255"/>
+      <c r="O47" s="255"/>
+      <c r="P47" s="255"/>
+      <c r="Q47" s="255"/>
+      <c r="R47" s="255"/>
+      <c r="S47" s="255"/>
+      <c r="T47" s="255"/>
+      <c r="U47" s="255"/>
+      <c r="V47" s="255"/>
+      <c r="W47" s="255"/>
+      <c r="X47" s="255"/>
+      <c r="Y47" s="255"/>
+      <c r="Z47" s="255"/>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="254"/>
-      <c r="B48" s="254"/>
-      <c r="C48" s="254"/>
-      <c r="D48" s="254"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="254"/>
-      <c r="G48" s="254"/>
-      <c r="H48" s="254"/>
-      <c r="I48" s="254"/>
-      <c r="J48" s="254"/>
-      <c r="K48" s="254"/>
-      <c r="L48" s="254"/>
-      <c r="M48" s="254"/>
-      <c r="N48" s="254"/>
-      <c r="O48" s="254"/>
-      <c r="P48" s="254"/>
-      <c r="Q48" s="254"/>
-      <c r="R48" s="254"/>
-      <c r="S48" s="254"/>
-      <c r="T48" s="254"/>
-      <c r="U48" s="254"/>
-      <c r="V48" s="254"/>
-      <c r="W48" s="254"/>
-      <c r="X48" s="254"/>
-      <c r="Y48" s="254"/>
-      <c r="Z48" s="254"/>
+      <c r="A48" s="255"/>
+      <c r="B48" s="255"/>
+      <c r="C48" s="255"/>
+      <c r="D48" s="255"/>
+      <c r="E48" s="255"/>
+      <c r="F48" s="255"/>
+      <c r="G48" s="255"/>
+      <c r="H48" s="255"/>
+      <c r="I48" s="255"/>
+      <c r="J48" s="255"/>
+      <c r="K48" s="255"/>
+      <c r="L48" s="255"/>
+      <c r="M48" s="255"/>
+      <c r="N48" s="255"/>
+      <c r="O48" s="255"/>
+      <c r="P48" s="255"/>
+      <c r="Q48" s="255"/>
+      <c r="R48" s="255"/>
+      <c r="S48" s="255"/>
+      <c r="T48" s="255"/>
+      <c r="U48" s="255"/>
+      <c r="V48" s="255"/>
+      <c r="W48" s="255"/>
+      <c r="X48" s="255"/>
+      <c r="Y48" s="255"/>
+      <c r="Z48" s="255"/>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="254"/>
-      <c r="B49" s="254"/>
-      <c r="C49" s="254"/>
-      <c r="D49" s="254"/>
-      <c r="E49" s="254"/>
-      <c r="F49" s="254"/>
-      <c r="G49" s="254"/>
-      <c r="H49" s="254"/>
-      <c r="I49" s="254"/>
-      <c r="J49" s="254"/>
-      <c r="K49" s="254"/>
-      <c r="L49" s="254"/>
-      <c r="M49" s="254"/>
-      <c r="N49" s="254"/>
-      <c r="O49" s="254"/>
-      <c r="P49" s="254"/>
-      <c r="Q49" s="254"/>
-      <c r="R49" s="254"/>
-      <c r="S49" s="254"/>
-      <c r="T49" s="254"/>
-      <c r="U49" s="254"/>
-      <c r="V49" s="254"/>
-      <c r="W49" s="254"/>
-      <c r="X49" s="254"/>
-      <c r="Y49" s="254"/>
-      <c r="Z49" s="254"/>
+      <c r="A49" s="255"/>
+      <c r="B49" s="255"/>
+      <c r="C49" s="255"/>
+      <c r="D49" s="255"/>
+      <c r="E49" s="255"/>
+      <c r="F49" s="255"/>
+      <c r="G49" s="255"/>
+      <c r="H49" s="255"/>
+      <c r="I49" s="255"/>
+      <c r="J49" s="255"/>
+      <c r="K49" s="255"/>
+      <c r="L49" s="255"/>
+      <c r="M49" s="255"/>
+      <c r="N49" s="255"/>
+      <c r="O49" s="255"/>
+      <c r="P49" s="255"/>
+      <c r="Q49" s="255"/>
+      <c r="R49" s="255"/>
+      <c r="S49" s="255"/>
+      <c r="T49" s="255"/>
+      <c r="U49" s="255"/>
+      <c r="V49" s="255"/>
+      <c r="W49" s="255"/>
+      <c r="X49" s="255"/>
+      <c r="Y49" s="255"/>
+      <c r="Z49" s="255"/>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="254"/>
-      <c r="B50" s="254"/>
-      <c r="C50" s="254"/>
-      <c r="D50" s="254"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="254"/>
-      <c r="G50" s="254"/>
-      <c r="H50" s="254"/>
-      <c r="I50" s="254"/>
-      <c r="J50" s="254"/>
-      <c r="K50" s="254"/>
-      <c r="L50" s="254"/>
-      <c r="M50" s="254"/>
-      <c r="N50" s="254"/>
-      <c r="O50" s="254"/>
-      <c r="P50" s="254"/>
-      <c r="Q50" s="254"/>
-      <c r="R50" s="254"/>
-      <c r="S50" s="254"/>
-      <c r="T50" s="254"/>
-      <c r="U50" s="254"/>
-      <c r="V50" s="254"/>
-      <c r="W50" s="254"/>
-      <c r="X50" s="254"/>
-      <c r="Y50" s="254"/>
-      <c r="Z50" s="254"/>
+      <c r="A50" s="255"/>
+      <c r="B50" s="255"/>
+      <c r="C50" s="255"/>
+      <c r="D50" s="255"/>
+      <c r="E50" s="255"/>
+      <c r="F50" s="255"/>
+      <c r="G50" s="255"/>
+      <c r="H50" s="255"/>
+      <c r="I50" s="255"/>
+      <c r="J50" s="255"/>
+      <c r="K50" s="255"/>
+      <c r="L50" s="255"/>
+      <c r="M50" s="255"/>
+      <c r="N50" s="255"/>
+      <c r="O50" s="255"/>
+      <c r="P50" s="255"/>
+      <c r="Q50" s="255"/>
+      <c r="R50" s="255"/>
+      <c r="S50" s="255"/>
+      <c r="T50" s="255"/>
+      <c r="U50" s="255"/>
+      <c r="V50" s="255"/>
+      <c r="W50" s="255"/>
+      <c r="X50" s="255"/>
+      <c r="Y50" s="255"/>
+      <c r="Z50" s="255"/>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="254"/>
-      <c r="B51" s="254"/>
-      <c r="C51" s="254"/>
-      <c r="D51" s="254"/>
-      <c r="E51" s="254"/>
-      <c r="F51" s="254"/>
-      <c r="G51" s="254"/>
-      <c r="H51" s="254"/>
-      <c r="I51" s="254"/>
-      <c r="J51" s="254"/>
-      <c r="K51" s="254"/>
-      <c r="L51" s="254"/>
-      <c r="M51" s="254"/>
-      <c r="N51" s="254"/>
-      <c r="O51" s="254"/>
-      <c r="P51" s="254"/>
-      <c r="Q51" s="254"/>
-      <c r="R51" s="254"/>
-      <c r="S51" s="254"/>
-      <c r="T51" s="254"/>
-      <c r="U51" s="254"/>
-      <c r="V51" s="254"/>
-      <c r="W51" s="254"/>
-      <c r="X51" s="254"/>
-      <c r="Y51" s="254"/>
-      <c r="Z51" s="254"/>
+      <c r="A51" s="255"/>
+      <c r="B51" s="255"/>
+      <c r="C51" s="255"/>
+      <c r="D51" s="255"/>
+      <c r="E51" s="255"/>
+      <c r="F51" s="255"/>
+      <c r="G51" s="255"/>
+      <c r="H51" s="255"/>
+      <c r="I51" s="255"/>
+      <c r="J51" s="255"/>
+      <c r="K51" s="255"/>
+      <c r="L51" s="255"/>
+      <c r="M51" s="255"/>
+      <c r="N51" s="255"/>
+      <c r="O51" s="255"/>
+      <c r="P51" s="255"/>
+      <c r="Q51" s="255"/>
+      <c r="R51" s="255"/>
+      <c r="S51" s="255"/>
+      <c r="T51" s="255"/>
+      <c r="U51" s="255"/>
+      <c r="V51" s="255"/>
+      <c r="W51" s="255"/>
+      <c r="X51" s="255"/>
+      <c r="Y51" s="255"/>
+      <c r="Z51" s="255"/>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="254"/>
-      <c r="B52" s="254"/>
-      <c r="C52" s="254"/>
-      <c r="D52" s="254"/>
-      <c r="E52" s="254"/>
-      <c r="F52" s="254"/>
-      <c r="G52" s="254"/>
-      <c r="H52" s="254"/>
-      <c r="I52" s="254"/>
-      <c r="J52" s="254"/>
-      <c r="K52" s="254"/>
-      <c r="L52" s="254"/>
-      <c r="M52" s="254"/>
-      <c r="N52" s="254"/>
-      <c r="O52" s="254"/>
-      <c r="P52" s="254"/>
-      <c r="Q52" s="254"/>
-      <c r="R52" s="254"/>
-      <c r="S52" s="254"/>
-      <c r="T52" s="254"/>
-      <c r="U52" s="254"/>
-      <c r="V52" s="254"/>
-      <c r="W52" s="254"/>
-      <c r="X52" s="254"/>
-      <c r="Y52" s="254"/>
-      <c r="Z52" s="254"/>
+      <c r="A52" s="255"/>
+      <c r="B52" s="255"/>
+      <c r="C52" s="255"/>
+      <c r="D52" s="255"/>
+      <c r="E52" s="255"/>
+      <c r="F52" s="255"/>
+      <c r="G52" s="255"/>
+      <c r="H52" s="255"/>
+      <c r="I52" s="255"/>
+      <c r="J52" s="255"/>
+      <c r="K52" s="255"/>
+      <c r="L52" s="255"/>
+      <c r="M52" s="255"/>
+      <c r="N52" s="255"/>
+      <c r="O52" s="255"/>
+      <c r="P52" s="255"/>
+      <c r="Q52" s="255"/>
+      <c r="R52" s="255"/>
+      <c r="S52" s="255"/>
+      <c r="T52" s="255"/>
+      <c r="U52" s="255"/>
+      <c r="V52" s="255"/>
+      <c r="W52" s="255"/>
+      <c r="X52" s="255"/>
+      <c r="Y52" s="255"/>
+      <c r="Z52" s="255"/>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="254"/>
-      <c r="B53" s="254"/>
-      <c r="C53" s="254"/>
-      <c r="D53" s="254"/>
-      <c r="E53" s="254"/>
-      <c r="F53" s="254"/>
-      <c r="G53" s="254"/>
-      <c r="H53" s="254"/>
-      <c r="I53" s="254"/>
-      <c r="J53" s="254"/>
-      <c r="K53" s="254"/>
-      <c r="L53" s="254"/>
-      <c r="M53" s="254"/>
-      <c r="N53" s="254"/>
-      <c r="O53" s="254"/>
-      <c r="P53" s="254"/>
-      <c r="Q53" s="254"/>
-      <c r="R53" s="254"/>
-      <c r="S53" s="254"/>
-      <c r="T53" s="254"/>
-      <c r="U53" s="254"/>
-      <c r="V53" s="254"/>
-      <c r="W53" s="254"/>
-      <c r="X53" s="254"/>
-      <c r="Y53" s="254"/>
-      <c r="Z53" s="254"/>
+      <c r="A53" s="255"/>
+      <c r="B53" s="255"/>
+      <c r="C53" s="255"/>
+      <c r="D53" s="255"/>
+      <c r="E53" s="255"/>
+      <c r="F53" s="255"/>
+      <c r="G53" s="255"/>
+      <c r="H53" s="255"/>
+      <c r="I53" s="255"/>
+      <c r="J53" s="255"/>
+      <c r="K53" s="255"/>
+      <c r="L53" s="255"/>
+      <c r="M53" s="255"/>
+      <c r="N53" s="255"/>
+      <c r="O53" s="255"/>
+      <c r="P53" s="255"/>
+      <c r="Q53" s="255"/>
+      <c r="R53" s="255"/>
+      <c r="S53" s="255"/>
+      <c r="T53" s="255"/>
+      <c r="U53" s="255"/>
+      <c r="V53" s="255"/>
+      <c r="W53" s="255"/>
+      <c r="X53" s="255"/>
+      <c r="Y53" s="255"/>
+      <c r="Z53" s="255"/>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="254"/>
-      <c r="B54" s="254"/>
-      <c r="C54" s="254"/>
-      <c r="D54" s="254"/>
-      <c r="E54" s="254"/>
-      <c r="F54" s="254"/>
-      <c r="G54" s="254"/>
-      <c r="H54" s="254"/>
-      <c r="I54" s="254"/>
-      <c r="J54" s="254"/>
-      <c r="K54" s="254"/>
-      <c r="L54" s="254"/>
-      <c r="M54" s="254"/>
-      <c r="N54" s="254"/>
-      <c r="O54" s="254"/>
-      <c r="P54" s="254"/>
-      <c r="Q54" s="254"/>
-      <c r="R54" s="254"/>
-      <c r="S54" s="254"/>
-      <c r="T54" s="254"/>
-      <c r="U54" s="254"/>
-      <c r="V54" s="254"/>
-      <c r="W54" s="254"/>
-      <c r="X54" s="254"/>
-      <c r="Y54" s="254"/>
-      <c r="Z54" s="254"/>
+      <c r="A54" s="255"/>
+      <c r="B54" s="255"/>
+      <c r="C54" s="255"/>
+      <c r="D54" s="255"/>
+      <c r="E54" s="255"/>
+      <c r="F54" s="255"/>
+      <c r="G54" s="255"/>
+      <c r="H54" s="255"/>
+      <c r="I54" s="255"/>
+      <c r="J54" s="255"/>
+      <c r="K54" s="255"/>
+      <c r="L54" s="255"/>
+      <c r="M54" s="255"/>
+      <c r="N54" s="255"/>
+      <c r="O54" s="255"/>
+      <c r="P54" s="255"/>
+      <c r="Q54" s="255"/>
+      <c r="R54" s="255"/>
+      <c r="S54" s="255"/>
+      <c r="T54" s="255"/>
+      <c r="U54" s="255"/>
+      <c r="V54" s="255"/>
+      <c r="W54" s="255"/>
+      <c r="X54" s="255"/>
+      <c r="Y54" s="255"/>
+      <c r="Z54" s="255"/>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="254"/>
-      <c r="B55" s="254"/>
-      <c r="C55" s="254"/>
-      <c r="D55" s="254"/>
-      <c r="E55" s="254"/>
-      <c r="F55" s="254"/>
-      <c r="G55" s="254"/>
-      <c r="H55" s="254"/>
-      <c r="I55" s="254"/>
-      <c r="J55" s="254"/>
-      <c r="K55" s="254"/>
-      <c r="L55" s="254"/>
-      <c r="M55" s="254"/>
-      <c r="N55" s="254"/>
-      <c r="O55" s="254"/>
-      <c r="P55" s="254"/>
-      <c r="Q55" s="254"/>
-      <c r="R55" s="254"/>
-      <c r="S55" s="254"/>
-      <c r="T55" s="254"/>
-      <c r="U55" s="254"/>
-      <c r="V55" s="254"/>
-      <c r="W55" s="254"/>
-      <c r="X55" s="254"/>
-      <c r="Y55" s="254"/>
-      <c r="Z55" s="254"/>
+      <c r="A55" s="255"/>
+      <c r="B55" s="255"/>
+      <c r="C55" s="255"/>
+      <c r="D55" s="255"/>
+      <c r="E55" s="255"/>
+      <c r="F55" s="255"/>
+      <c r="G55" s="255"/>
+      <c r="H55" s="255"/>
+      <c r="I55" s="255"/>
+      <c r="J55" s="255"/>
+      <c r="K55" s="255"/>
+      <c r="L55" s="255"/>
+      <c r="M55" s="255"/>
+      <c r="N55" s="255"/>
+      <c r="O55" s="255"/>
+      <c r="P55" s="255"/>
+      <c r="Q55" s="255"/>
+      <c r="R55" s="255"/>
+      <c r="S55" s="255"/>
+      <c r="T55" s="255"/>
+      <c r="U55" s="255"/>
+      <c r="V55" s="255"/>
+      <c r="W55" s="255"/>
+      <c r="X55" s="255"/>
+      <c r="Y55" s="255"/>
+      <c r="Z55" s="255"/>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="254"/>
-      <c r="B56" s="254"/>
-      <c r="C56" s="254"/>
-      <c r="D56" s="254"/>
-      <c r="E56" s="254"/>
-      <c r="F56" s="254"/>
-      <c r="G56" s="254"/>
-      <c r="H56" s="254"/>
-      <c r="I56" s="254"/>
-      <c r="J56" s="254"/>
-      <c r="K56" s="254"/>
-      <c r="L56" s="254"/>
-      <c r="M56" s="254"/>
-      <c r="N56" s="254"/>
-      <c r="O56" s="254"/>
-      <c r="P56" s="254"/>
-      <c r="Q56" s="254"/>
-      <c r="R56" s="254"/>
-      <c r="S56" s="254"/>
-      <c r="T56" s="254"/>
-      <c r="U56" s="254"/>
-      <c r="V56" s="254"/>
-      <c r="W56" s="254"/>
-      <c r="X56" s="254"/>
-      <c r="Y56" s="254"/>
-      <c r="Z56" s="254"/>
+      <c r="A56" s="255"/>
+      <c r="B56" s="255"/>
+      <c r="C56" s="255"/>
+      <c r="D56" s="255"/>
+      <c r="E56" s="255"/>
+      <c r="F56" s="255"/>
+      <c r="G56" s="255"/>
+      <c r="H56" s="255"/>
+      <c r="I56" s="255"/>
+      <c r="J56" s="255"/>
+      <c r="K56" s="255"/>
+      <c r="L56" s="255"/>
+      <c r="M56" s="255"/>
+      <c r="N56" s="255"/>
+      <c r="O56" s="255"/>
+      <c r="P56" s="255"/>
+      <c r="Q56" s="255"/>
+      <c r="R56" s="255"/>
+      <c r="S56" s="255"/>
+      <c r="T56" s="255"/>
+      <c r="U56" s="255"/>
+      <c r="V56" s="255"/>
+      <c r="W56" s="255"/>
+      <c r="X56" s="255"/>
+      <c r="Y56" s="255"/>
+      <c r="Z56" s="255"/>
     </row>
     <row r="57" spans="1:26">
-      <c r="A57" s="254"/>
-      <c r="B57" s="254"/>
-      <c r="C57" s="254"/>
-      <c r="D57" s="254"/>
-      <c r="E57" s="254"/>
-      <c r="F57" s="254"/>
-      <c r="G57" s="254"/>
-      <c r="H57" s="254"/>
-      <c r="I57" s="254"/>
-      <c r="J57" s="254"/>
-      <c r="K57" s="254"/>
-      <c r="L57" s="254"/>
-      <c r="M57" s="254"/>
-      <c r="N57" s="254"/>
-      <c r="O57" s="254"/>
-      <c r="P57" s="254"/>
-      <c r="Q57" s="254"/>
-      <c r="R57" s="254"/>
-      <c r="S57" s="254"/>
-      <c r="T57" s="254"/>
-      <c r="U57" s="254"/>
-      <c r="V57" s="254"/>
-      <c r="W57" s="254"/>
-      <c r="X57" s="254"/>
-      <c r="Y57" s="254"/>
-      <c r="Z57" s="254"/>
+      <c r="A57" s="255"/>
+      <c r="B57" s="255"/>
+      <c r="C57" s="255"/>
+      <c r="D57" s="255"/>
+      <c r="E57" s="255"/>
+      <c r="F57" s="255"/>
+      <c r="G57" s="255"/>
+      <c r="H57" s="255"/>
+      <c r="I57" s="255"/>
+      <c r="J57" s="255"/>
+      <c r="K57" s="255"/>
+      <c r="L57" s="255"/>
+      <c r="M57" s="255"/>
+      <c r="N57" s="255"/>
+      <c r="O57" s="255"/>
+      <c r="P57" s="255"/>
+      <c r="Q57" s="255"/>
+      <c r="R57" s="255"/>
+      <c r="S57" s="255"/>
+      <c r="T57" s="255"/>
+      <c r="U57" s="255"/>
+      <c r="V57" s="255"/>
+      <c r="W57" s="255"/>
+      <c r="X57" s="255"/>
+      <c r="Y57" s="255"/>
+      <c r="Z57" s="255"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="254"/>
-      <c r="B58" s="254"/>
-      <c r="C58" s="254"/>
-      <c r="D58" s="254"/>
-      <c r="E58" s="254"/>
-      <c r="F58" s="254"/>
-      <c r="G58" s="254"/>
-      <c r="H58" s="254"/>
-      <c r="I58" s="254"/>
-      <c r="J58" s="254"/>
-      <c r="K58" s="254"/>
-      <c r="L58" s="254"/>
-      <c r="M58" s="254"/>
-      <c r="N58" s="254"/>
-      <c r="O58" s="254"/>
-      <c r="P58" s="254"/>
-      <c r="Q58" s="254"/>
-      <c r="R58" s="254"/>
-      <c r="S58" s="254"/>
-      <c r="T58" s="254"/>
-      <c r="U58" s="254"/>
-      <c r="V58" s="254"/>
-      <c r="W58" s="254"/>
-      <c r="X58" s="254"/>
-      <c r="Y58" s="254"/>
-      <c r="Z58" s="254"/>
+      <c r="A58" s="255"/>
+      <c r="B58" s="255"/>
+      <c r="C58" s="255"/>
+      <c r="D58" s="255"/>
+      <c r="E58" s="255"/>
+      <c r="F58" s="255"/>
+      <c r="G58" s="255"/>
+      <c r="H58" s="255"/>
+      <c r="I58" s="255"/>
+      <c r="J58" s="255"/>
+      <c r="K58" s="255"/>
+      <c r="L58" s="255"/>
+      <c r="M58" s="255"/>
+      <c r="N58" s="255"/>
+      <c r="O58" s="255"/>
+      <c r="P58" s="255"/>
+      <c r="Q58" s="255"/>
+      <c r="R58" s="255"/>
+      <c r="S58" s="255"/>
+      <c r="T58" s="255"/>
+      <c r="U58" s="255"/>
+      <c r="V58" s="255"/>
+      <c r="W58" s="255"/>
+      <c r="X58" s="255"/>
+      <c r="Y58" s="255"/>
+      <c r="Z58" s="255"/>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="254"/>
-      <c r="B59" s="254"/>
-      <c r="C59" s="254"/>
-      <c r="D59" s="254"/>
-      <c r="E59" s="254"/>
-      <c r="F59" s="254"/>
-      <c r="G59" s="254"/>
-      <c r="H59" s="254"/>
-      <c r="I59" s="254"/>
-      <c r="J59" s="254"/>
-      <c r="K59" s="254"/>
-      <c r="L59" s="254"/>
-      <c r="M59" s="254"/>
-      <c r="N59" s="254"/>
-      <c r="O59" s="254"/>
-      <c r="P59" s="254"/>
-      <c r="Q59" s="254"/>
-      <c r="R59" s="254"/>
-      <c r="S59" s="254"/>
-      <c r="T59" s="254"/>
-      <c r="U59" s="254"/>
-      <c r="V59" s="254"/>
-      <c r="W59" s="254"/>
-      <c r="X59" s="254"/>
-      <c r="Y59" s="254"/>
-      <c r="Z59" s="254"/>
+      <c r="A59" s="255"/>
+      <c r="B59" s="255"/>
+      <c r="C59" s="255"/>
+      <c r="D59" s="255"/>
+      <c r="E59" s="255"/>
+      <c r="F59" s="255"/>
+      <c r="G59" s="255"/>
+      <c r="H59" s="255"/>
+      <c r="I59" s="255"/>
+      <c r="J59" s="255"/>
+      <c r="K59" s="255"/>
+      <c r="L59" s="255"/>
+      <c r="M59" s="255"/>
+      <c r="N59" s="255"/>
+      <c r="O59" s="255"/>
+      <c r="P59" s="255"/>
+      <c r="Q59" s="255"/>
+      <c r="R59" s="255"/>
+      <c r="S59" s="255"/>
+      <c r="T59" s="255"/>
+      <c r="U59" s="255"/>
+      <c r="V59" s="255"/>
+      <c r="W59" s="255"/>
+      <c r="X59" s="255"/>
+      <c r="Y59" s="255"/>
+      <c r="Z59" s="255"/>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="254"/>
-      <c r="B60" s="254"/>
-      <c r="C60" s="254"/>
-      <c r="D60" s="254"/>
-      <c r="E60" s="254"/>
-      <c r="F60" s="254"/>
-      <c r="G60" s="254"/>
-      <c r="H60" s="254"/>
-      <c r="I60" s="254"/>
-      <c r="J60" s="254"/>
-      <c r="K60" s="254"/>
-      <c r="L60" s="254"/>
-      <c r="M60" s="254"/>
-      <c r="N60" s="254"/>
-      <c r="O60" s="254"/>
-      <c r="P60" s="254"/>
-      <c r="Q60" s="254"/>
-      <c r="R60" s="254"/>
-      <c r="S60" s="254"/>
-      <c r="T60" s="254"/>
-      <c r="U60" s="254"/>
-      <c r="V60" s="254"/>
-      <c r="W60" s="254"/>
-      <c r="X60" s="254"/>
-      <c r="Y60" s="254"/>
-      <c r="Z60" s="254"/>
+      <c r="A60" s="255"/>
+      <c r="B60" s="255"/>
+      <c r="C60" s="255"/>
+      <c r="D60" s="255"/>
+      <c r="E60" s="255"/>
+      <c r="F60" s="255"/>
+      <c r="G60" s="255"/>
+      <c r="H60" s="255"/>
+      <c r="I60" s="255"/>
+      <c r="J60" s="255"/>
+      <c r="K60" s="255"/>
+      <c r="L60" s="255"/>
+      <c r="M60" s="255"/>
+      <c r="N60" s="255"/>
+      <c r="O60" s="255"/>
+      <c r="P60" s="255"/>
+      <c r="Q60" s="255"/>
+      <c r="R60" s="255"/>
+      <c r="S60" s="255"/>
+      <c r="T60" s="255"/>
+      <c r="U60" s="255"/>
+      <c r="V60" s="255"/>
+      <c r="W60" s="255"/>
+      <c r="X60" s="255"/>
+      <c r="Y60" s="255"/>
+      <c r="Z60" s="255"/>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="254"/>
-      <c r="B61" s="254"/>
-      <c r="C61" s="254"/>
-      <c r="D61" s="254"/>
-      <c r="E61" s="254"/>
-      <c r="F61" s="254"/>
-      <c r="G61" s="254"/>
-      <c r="H61" s="254"/>
-      <c r="I61" s="254"/>
-      <c r="J61" s="254"/>
-      <c r="K61" s="254"/>
-      <c r="L61" s="254"/>
-      <c r="M61" s="254"/>
-      <c r="N61" s="254"/>
-      <c r="O61" s="254"/>
-      <c r="P61" s="254"/>
-      <c r="Q61" s="254"/>
-      <c r="R61" s="254"/>
-      <c r="S61" s="254"/>
-      <c r="T61" s="254"/>
-      <c r="U61" s="254"/>
-      <c r="V61" s="254"/>
-      <c r="W61" s="254"/>
-      <c r="X61" s="254"/>
-      <c r="Y61" s="254"/>
-      <c r="Z61" s="254"/>
+      <c r="A61" s="255"/>
+      <c r="B61" s="255"/>
+      <c r="C61" s="255"/>
+      <c r="D61" s="255"/>
+      <c r="E61" s="255"/>
+      <c r="F61" s="255"/>
+      <c r="G61" s="255"/>
+      <c r="H61" s="255"/>
+      <c r="I61" s="255"/>
+      <c r="J61" s="255"/>
+      <c r="K61" s="255"/>
+      <c r="L61" s="255"/>
+      <c r="M61" s="255"/>
+      <c r="N61" s="255"/>
+      <c r="O61" s="255"/>
+      <c r="P61" s="255"/>
+      <c r="Q61" s="255"/>
+      <c r="R61" s="255"/>
+      <c r="S61" s="255"/>
+      <c r="T61" s="255"/>
+      <c r="U61" s="255"/>
+      <c r="V61" s="255"/>
+      <c r="W61" s="255"/>
+      <c r="X61" s="255"/>
+      <c r="Y61" s="255"/>
+      <c r="Z61" s="255"/>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="254"/>
-      <c r="B62" s="254"/>
-      <c r="C62" s="254"/>
-      <c r="D62" s="254"/>
-      <c r="E62" s="254"/>
-      <c r="F62" s="254"/>
-      <c r="G62" s="254"/>
-      <c r="H62" s="254"/>
-      <c r="I62" s="254"/>
-      <c r="J62" s="254"/>
-      <c r="K62" s="254"/>
-      <c r="L62" s="254"/>
-      <c r="M62" s="254"/>
-      <c r="N62" s="254"/>
-      <c r="O62" s="254"/>
-      <c r="P62" s="254"/>
-      <c r="Q62" s="254"/>
-      <c r="R62" s="254"/>
-      <c r="S62" s="254"/>
-      <c r="T62" s="254"/>
-      <c r="U62" s="254"/>
-      <c r="V62" s="254"/>
-      <c r="W62" s="254"/>
-      <c r="X62" s="254"/>
-      <c r="Y62" s="254"/>
-      <c r="Z62" s="254"/>
+      <c r="A62" s="255"/>
+      <c r="B62" s="255"/>
+      <c r="C62" s="255"/>
+      <c r="D62" s="255"/>
+      <c r="E62" s="255"/>
+      <c r="F62" s="255"/>
+      <c r="G62" s="255"/>
+      <c r="H62" s="255"/>
+      <c r="I62" s="255"/>
+      <c r="J62" s="255"/>
+      <c r="K62" s="255"/>
+      <c r="L62" s="255"/>
+      <c r="M62" s="255"/>
+      <c r="N62" s="255"/>
+      <c r="O62" s="255"/>
+      <c r="P62" s="255"/>
+      <c r="Q62" s="255"/>
+      <c r="R62" s="255"/>
+      <c r="S62" s="255"/>
+      <c r="T62" s="255"/>
+      <c r="U62" s="255"/>
+      <c r="V62" s="255"/>
+      <c r="W62" s="255"/>
+      <c r="X62" s="255"/>
+      <c r="Y62" s="255"/>
+      <c r="Z62" s="255"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
@@ -5730,7 +5745,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -5746,7 +5761,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>4063.3</v>
+        <v>4648.7</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -5762,7 +5777,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>4229.8</v>
+        <v>5694.2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -5861,7 +5876,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -6035,7 +6050,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -6209,7 +6224,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -7148,7 +7163,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -7259,7 +7274,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -7275,7 +7290,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -7520,7 +7535,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -7614,7 +7629,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!E190")</f>
-        <v>2165.9</v>
+        <v>2571.6</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -7783,7 +7798,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -7802,7 +7817,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -7870,7 +7885,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -7886,7 +7901,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>2948.7</v>
+        <v>3414.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -7978,7 +7993,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>2948.7</v>
+        <v>3414.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -8147,7 +8162,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D156" s="103"/>
       <c r="E156" s="101">
@@ -8166,7 +8181,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -8234,7 +8249,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -8250,7 +8265,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>3280.5</v>
+        <v>3806</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -8342,7 +8357,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>3280.5</v>
+        <v>3806</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -8511,7 +8526,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D183" s="99"/>
       <c r="E183" s="101">
@@ -8530,7 +8545,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -8598,7 +8613,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -8614,7 +8629,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>4063.3</v>
+        <v>4648.7</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -9139,7 +9154,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -9155,7 +9170,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>5669.7</v>
+        <v>6434.8</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -9171,7 +9186,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>5836.2</v>
+        <v>7480.3</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -9270,7 +9285,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -9444,7 +9459,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -9618,7 +9633,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -10557,7 +10572,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -10668,7 +10683,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -10684,7 +10699,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -10929,7 +10944,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -11023,7 +11038,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!E190")</f>
-        <v>4063.3</v>
+        <v>4648.7</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -11192,7 +11207,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -11211,7 +11226,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -11279,7 +11294,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -11295,7 +11310,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>4555.1</v>
+        <v>5200.4</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -11387,7 +11402,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>4555.1</v>
+        <v>5200.4</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -11556,7 +11571,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D156" s="99"/>
       <c r="E156" s="101">
@@ -11575,7 +11590,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -11643,7 +11658,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -11659,7 +11674,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>5177.9</v>
+        <v>5883.1</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -11751,7 +11766,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>5177.9</v>
+        <v>5883.1</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -11920,7 +11935,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D183" s="103"/>
       <c r="E183" s="101">
@@ -11939,7 +11954,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -12007,7 +12022,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -12023,7 +12038,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>5669.7</v>
+        <v>6434.8</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -12549,7 +12564,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -12565,7 +12580,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>7567.1</v>
+        <v>8449</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -12581,7 +12596,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>7733.6</v>
+        <v>9494.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -12680,7 +12695,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -12854,7 +12869,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -13028,7 +13043,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -13967,7 +13982,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -14078,7 +14093,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -14094,7 +14109,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -14339,7 +14354,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -14433,7 +14448,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!E190")</f>
-        <v>5669.7</v>
+        <v>6434.8</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -14602,7 +14617,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -14621,7 +14636,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -14689,7 +14704,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -14705,7 +14720,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>6452.5</v>
+        <v>7277.5</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -14797,7 +14812,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>6452.5</v>
+        <v>7277.5</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -14966,7 +14981,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D156" s="103"/>
       <c r="E156" s="101">
@@ -14985,7 +15000,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -15053,7 +15068,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -15069,7 +15084,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>6784.3</v>
+        <v>7669.2</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -15161,7 +15176,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>6784.3</v>
+        <v>7669.2</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -15330,7 +15345,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D183" s="99"/>
       <c r="E183" s="101">
@@ -15417,7 +15432,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -15433,7 +15448,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>7567.1</v>
+        <v>8449</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -15958,7 +15973,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -15974,7 +15989,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>9173.5</v>
+        <v>10235.1</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -15990,7 +16005,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>9340</v>
+        <v>11280.6</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -16089,7 +16104,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -16263,7 +16278,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -16437,7 +16452,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -17376,7 +17391,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -17487,7 +17502,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -17503,7 +17518,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -17748,7 +17763,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -17842,7 +17857,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!E190")</f>
-        <v>7567.1</v>
+        <v>8449</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -18011,7 +18026,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -18030,7 +18045,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -18098,7 +18113,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -18114,7 +18129,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>8058.9</v>
+        <v>9000.7</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -18206,7 +18221,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>8058.9</v>
+        <v>9000.7</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -18375,7 +18390,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D156" s="99"/>
       <c r="E156" s="101">
@@ -18394,7 +18409,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -18462,7 +18477,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -18478,7 +18493,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>8681.7</v>
+        <v>9683.4</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -18570,7 +18585,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>8681.7</v>
+        <v>9683.4</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -18739,7 +18754,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D183" s="99"/>
       <c r="E183" s="101">
@@ -18758,7 +18773,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -18826,7 +18841,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -18842,7 +18857,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>9173.5</v>
+        <v>10235.1</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -19368,7 +19383,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -19384,7 +19399,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>11070.9</v>
+        <v>12312.2</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -19400,7 +19415,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>11237.4</v>
+        <v>13357.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -19499,7 +19514,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -19673,7 +19688,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -19847,7 +19862,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -20786,7 +20801,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -20897,7 +20912,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -20913,7 +20928,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -21158,7 +21173,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -21252,7 +21267,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!E190")</f>
-        <v>9173.5</v>
+        <v>10235.1</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -21421,7 +21436,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -21440,7 +21455,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -21508,7 +21523,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -21524,7 +21539,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>9956.3</v>
+        <v>11077.8</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -21616,7 +21631,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>9956.3</v>
+        <v>11077.8</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -21785,7 +21800,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D156" s="99"/>
       <c r="E156" s="101">
@@ -21804,7 +21819,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -21872,7 +21887,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -21888,7 +21903,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>10288.1</v>
+        <v>11469.5</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -21980,7 +21995,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>10288.1</v>
+        <v>11469.5</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -22149,7 +22164,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D183" s="99"/>
       <c r="E183" s="101">
@@ -22168,7 +22183,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -22236,7 +22251,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -22252,7 +22267,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>11070.9</v>
+        <v>12312.2</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -22777,7 +22792,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -22793,7 +22808,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -22809,7 +22824,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>12843.8</v>
+        <v>15143.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -22908,7 +22923,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -23082,7 +23097,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -23256,7 +23271,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -24195,7 +24210,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -24306,7 +24321,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -24322,7 +24337,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -24567,7 +24582,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -24661,7 +24676,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!E190")</f>
-        <v>11070.9</v>
+        <v>12312.2</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -24830,7 +24845,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="99" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D129" s="99"/>
       <c r="E129" s="101">
@@ -24849,7 +24864,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -24917,7 +24932,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -24933,7 +24948,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>11562.7</v>
+        <v>12863.9</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -25025,7 +25040,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>11562.7</v>
+        <v>12863.9</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -25194,7 +25209,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="99" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D156" s="99"/>
       <c r="E156" s="101">
@@ -25213,7 +25228,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -25281,7 +25296,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -25297,7 +25312,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>12185.5</v>
+        <v>13546.6</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -25389,7 +25404,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>12185.5</v>
+        <v>13546.6</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -25558,7 +25573,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="99" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D183" s="99"/>
       <c r="E183" s="101">
@@ -25577,7 +25592,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -25645,7 +25660,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -25661,7 +25676,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -26186,7 +26201,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -26202,7 +26217,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -26218,7 +26233,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>12843.8</v>
+        <v>15143.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -28028,7 +28043,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!E190")</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -28296,7 +28311,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -28388,7 +28403,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -28656,7 +28671,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -28748,7 +28763,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -29016,7 +29031,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -29488,7 +29503,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -29504,7 +29519,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -29520,7 +29535,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>12843.8</v>
+        <v>15143.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -31099,7 +31114,7 @@
         <v>Bankruptcy Department / Bank</v>
       </c>
       <c r="B102" s="37" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C102" s="36" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!C102")+SUM(E122+E149+E176)</f>
@@ -31329,7 +31344,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!E190")</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -31597,7 +31612,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -31689,7 +31704,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -31957,7 +31972,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -32049,7 +32064,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -32317,7 +32332,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -32791,7 +32806,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -32807,7 +32822,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -32823,7 +32838,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>12843.8</v>
+        <v>15143.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -34633,7 +34648,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!E190")</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -34901,7 +34916,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -34993,7 +35008,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -35261,7 +35276,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -35353,7 +35368,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -35621,7 +35636,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -36060,433 +36075,433 @@
   <dimension ref="A1:B134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="43.25" style="233" customWidth="1"/>
-    <col min="2" max="2" width="34.125" style="233" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="233"/>
+    <col min="1" max="1" width="43.25" style="234" customWidth="1"/>
+    <col min="2" max="2" width="34.125" style="234" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="234"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:2">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="235" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="235" t="s">
+      <c r="B1" s="236" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:2">
-      <c r="A2" s="236" t="s">
+      <c r="A2" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="237" t="b">
+      <c r="B2" s="238" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2">
-      <c r="A3" s="238" t="s">
+      <c r="A3" s="239" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="239">
+      <c r="B3" s="240">
         <v>45402</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:2">
-      <c r="A4" s="234" t="s">
+      <c r="A4" s="235" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="240" t="str">
+      <c r="B4" s="241" t="str">
         <f>IF(B2,TEXT(EDATE(B3,1)-1,"dd-mmm-yyyy"),TEXT(EDATE(B3,1)-1,"dd-mmm-yyyy"))</f>
         <v>19-May-2024</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:2">
-      <c r="A5" s="236" t="s">
+      <c r="A5" s="237" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="241">
+      <c r="B5" s="242">
         <v>45777</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:2">
-      <c r="A6" s="236"/>
-      <c r="B6" s="241"/>
+      <c r="A6" s="237"/>
+      <c r="B6" s="242"/>
     </row>
     <row r="7" ht="24.75" customHeight="1" spans="1:2">
-      <c r="A7" s="242"/>
-      <c r="B7" s="243"/>
+      <c r="A7" s="243"/>
+      <c r="B7" s="244"/>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:2">
-      <c r="A8" s="244" t="s">
+      <c r="A8" s="245" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="244"/>
+      <c r="B8" s="245"/>
     </row>
     <row r="9" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A9" s="245" t="str">
+      <c r="A9" s="246" t="str">
         <f>TEXT(B3,"dd mmmm yyyy")&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,1)-1,"dd mmmm yyyy"),TEXT(B3+B5-B3,"dd mmmm yyyy"))</f>
         <v>20 April 2024 - 19 May 2024</v>
       </c>
-      <c r="B9" s="246" t="s">
+      <c r="B9" s="247" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A10" s="237" t="str">
+      <c r="A10" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,1),"dd mmmm yyyy"),TEXT(B3+(B5-B3)+1,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,2)-1,"dd mmmm yyyy"),TEXT(B3+(B5-B3)*2+1,"dd mmmm yyyy"))</f>
         <v>20 May 2024 - 19 June 2024</v>
       </c>
-      <c r="B10" s="246"/>
+      <c r="B10" s="247"/>
     </row>
     <row r="11" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A11" s="237" t="str">
+      <c r="A11" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,2),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*2)+2,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,3)-1,"dd mmmm yyyy"),TEXT(B3+((B5-B3)*3+2),"dd mmmm yyyy"))</f>
         <v>20 June 2024 - 19 July 2024</v>
       </c>
-      <c r="B11" s="247"/>
+      <c r="B11" s="248"/>
     </row>
     <row r="12" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A12" s="248" t="str">
+      <c r="A12" s="249" t="str">
         <f>IF(B2,TEXT(EDATE(B3,3),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*3)+3,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,4)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*4)+3),"dd mmmm yyyy"))</f>
         <v>20 July 2024 - 19 August 2024</v>
       </c>
-      <c r="B12" s="235" t="s">
+      <c r="B12" s="236" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A13" s="248" t="str">
+      <c r="A13" s="249" t="str">
         <f>IF(B2,TEXT(EDATE(B3,4),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*4)+4,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,5)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*5)+4),"dd mmmm yyyy"))</f>
         <v>20 August 2024 - 19 September 2024</v>
       </c>
-      <c r="B13" s="249"/>
+      <c r="B13" s="250"/>
     </row>
     <row r="14" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A14" s="237" t="str">
+      <c r="A14" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,5),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*5)+5,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,6)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*6)+5),"dd mmmm yyyy"))</f>
         <v>20 September 2024 - 19 October 2024</v>
       </c>
-      <c r="B14" s="250"/>
+      <c r="B14" s="251"/>
     </row>
     <row r="15" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A15" s="237" t="str">
+      <c r="A15" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,6),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*6)+6,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,7)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*7)+6),"dd mmmm yyyy"))</f>
         <v>20 October 2024 - 19 November 2024</v>
       </c>
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="236" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A16" s="237" t="str">
+      <c r="A16" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,7),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*7)+7,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,8)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*8)+7),"dd mmmm yyyy"))</f>
         <v>20 November 2024 - 19 December 2024</v>
       </c>
-      <c r="B16" s="249"/>
+      <c r="B16" s="250"/>
     </row>
     <row r="17" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A17" s="237" t="str">
+      <c r="A17" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,8),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*8)+8,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,9)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*9)+8),"dd mmmm yyyy"))</f>
         <v>20 December 2024 - 19 January 2025</v>
       </c>
-      <c r="B17" s="250"/>
+      <c r="B17" s="251"/>
     </row>
     <row r="18" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A18" s="237" t="str">
+      <c r="A18" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,9),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*9)+9,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,10)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*10)+9),"dd mmmm yyyy"))</f>
         <v>20 January 2025 - 19 February 2025</v>
       </c>
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="236" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A19" s="237" t="str">
+      <c r="A19" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,10),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*10)+10,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,11)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*11)+10),"dd mmmm yyyy"))</f>
         <v>20 February 2025 - 19 March 2025</v>
       </c>
-      <c r="B19" s="249"/>
+      <c r="B19" s="250"/>
     </row>
     <row r="20" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A20" s="251" t="str">
+      <c r="A20" s="252" t="str">
         <f>IF(B2,TEXT(EDATE(B3,11),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*11)+11,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,12)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*12)+11),"dd mmmm yyyy"))</f>
         <v>20 March 2025 - 19 April 2025</v>
       </c>
-      <c r="B20" s="250"/>
+      <c r="B20" s="251"/>
     </row>
     <row r="21" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A21" s="252" t="str">
+      <c r="A21" s="253" t="str">
         <f>IF(B2,TEXT(EDATE(B3,12),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*12)+12,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,13)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*13)+12),"dd mmmm yyyy"))</f>
         <v>20 April 2025 - 19 May 2025</v>
       </c>
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="238" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A22" s="252" t="str">
+      <c r="A22" s="253" t="str">
         <f>IF(B2,TEXT(EDATE(B3,13),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*13)+13,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,14)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*14)+13),"dd mmmm yyyy"))</f>
         <v>20 May 2025 - 19 June 2025</v>
       </c>
-      <c r="B22" s="237"/>
+      <c r="B22" s="238"/>
     </row>
     <row r="23" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A23" s="251" t="str">
+      <c r="A23" s="252" t="str">
         <f>IF(B2,TEXT(EDATE(B3,14),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*14)+14,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,15)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*15)+14),"dd mmmm yyyy"))</f>
         <v>20 June 2025 - 19 July 2025</v>
       </c>
-      <c r="B23" s="235"/>
+      <c r="B23" s="236"/>
     </row>
     <row r="24" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A24" s="237" t="str">
+      <c r="A24" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,15),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*15)+15,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,16)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*16)+15),"dd mmmm yyyy"))</f>
         <v>20 July 2025 - 19 August 2025</v>
       </c>
-      <c r="B24" s="237" t="s">
+      <c r="B24" s="238" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A25" s="237" t="str">
+      <c r="A25" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,16),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*16)+16,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,17)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*17)+16),"dd mmmm yyyy"))</f>
         <v>20 August 2025 - 19 September 2025</v>
       </c>
-      <c r="B25" s="237"/>
+      <c r="B25" s="238"/>
     </row>
     <row r="26" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A26" s="235" t="str">
+      <c r="A26" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,17),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*17)+17,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,18)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*18)+17),"dd mmmm yyyy"))</f>
         <v>20 September 2025 - 19 October 2025</v>
       </c>
-      <c r="B26" s="235"/>
+      <c r="B26" s="236"/>
     </row>
     <row r="27" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A27" s="237" t="str">
+      <c r="A27" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,18),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*18)+18,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,19)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*19)+18),"dd mmmm yyyy"))</f>
         <v>20 October 2025 - 19 November 2025</v>
       </c>
-      <c r="B27" s="237" t="s">
+      <c r="B27" s="238" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A28" s="237" t="str">
+      <c r="A28" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,19),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*19)+19,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,20)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*20)+19),"dd mmmm yyyy"))</f>
         <v>20 November 2025 - 19 December 2025</v>
       </c>
-      <c r="B28" s="237"/>
+      <c r="B28" s="238"/>
     </row>
     <row r="29" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A29" s="235" t="str">
+      <c r="A29" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,20),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*20)+20,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,21)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*21)+20),"dd mmmm yyyy"))</f>
         <v>20 December 2025 - 19 January 2026</v>
       </c>
-      <c r="B29" s="235"/>
+      <c r="B29" s="236"/>
     </row>
     <row r="30" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A30" s="237" t="str">
+      <c r="A30" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,21),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*21)+21,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,22)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*22)+21),"dd mmmm yyyy"))</f>
         <v>20 January 2026 - 19 February 2026</v>
       </c>
-      <c r="B30" s="237" t="s">
+      <c r="B30" s="238" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A31" s="237" t="str">
+      <c r="A31" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,22),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*22)+22,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,23)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*23)+22),"dd mmmm yyyy"))</f>
         <v>20 February 2026 - 19 March 2026</v>
       </c>
-      <c r="B31" s="237"/>
+      <c r="B31" s="238"/>
     </row>
     <row r="32" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A32" s="235" t="str">
+      <c r="A32" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,23),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*23)+23,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,24)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*24)+23),"dd mmmm yyyy"))</f>
         <v>20 March 2026 - 19 April 2026</v>
       </c>
-      <c r="B32" s="235"/>
+      <c r="B32" s="236"/>
     </row>
     <row r="33" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A33" s="237" t="str">
+      <c r="A33" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,24),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*24)+24,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,25)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*25)+24),"dd mmmm yyyy"))</f>
         <v>20 April 2026 - 19 May 2026</v>
       </c>
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="238" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="34" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A34" s="237" t="str">
+      <c r="A34" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,25),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*25)+25,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,26)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*26)+25),"dd mmmm yyyy"))</f>
         <v>20 May 2026 - 19 June 2026</v>
       </c>
-      <c r="B34" s="237"/>
+      <c r="B34" s="238"/>
     </row>
     <row r="35" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A35" s="235" t="str">
+      <c r="A35" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,26),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*26)+26,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,27)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*27)+26),"dd mmmm yyyy"))</f>
         <v>20 June 2026 - 19 July 2026</v>
       </c>
-      <c r="B35" s="235"/>
+      <c r="B35" s="236"/>
     </row>
     <row r="36" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A36" s="237" t="str">
+      <c r="A36" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,27),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*27)+27,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,28)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*28)+27),"dd mmmm yyyy"))</f>
         <v>20 July 2026 - 19 August 2026</v>
       </c>
-      <c r="B36" s="237" t="s">
+      <c r="B36" s="238" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="37" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A37" s="237" t="str">
+      <c r="A37" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,28),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*28)+28,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,29)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*29)+28),"dd mmmm yyyy"))</f>
         <v>20 August 2026 - 19 September 2026</v>
       </c>
-      <c r="B37" s="237"/>
+      <c r="B37" s="238"/>
     </row>
     <row r="38" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A38" s="235" t="str">
+      <c r="A38" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,29),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*29)+29,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,30)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*30)+29),"dd mmmm yyyy"))</f>
         <v>20 September 2026 - 19 October 2026</v>
       </c>
-      <c r="B38" s="235"/>
+      <c r="B38" s="236"/>
     </row>
     <row r="39" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A39" s="237" t="str">
+      <c r="A39" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,30),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*30)+30,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,31)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*31)+30),"dd mmmm yyyy"))</f>
         <v>20 October 2026 - 19 November 2026</v>
       </c>
-      <c r="B39" s="237" t="s">
+      <c r="B39" s="238" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A40" s="237" t="str">
+      <c r="A40" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,31),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*31)+31,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,32)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*32)+31),"dd mmmm yyyy"))</f>
         <v>20 November 2026 - 19 December 2026</v>
       </c>
-      <c r="B40" s="237"/>
+      <c r="B40" s="238"/>
     </row>
     <row r="41" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A41" s="235" t="str">
+      <c r="A41" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,32),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*32)+32,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,33)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*33)+32),"dd mmmm yyyy"))</f>
         <v>20 December 2026 - 19 January 2027</v>
       </c>
-      <c r="B41" s="235"/>
+      <c r="B41" s="236"/>
     </row>
     <row r="42" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A42" s="237" t="str">
+      <c r="A42" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,33),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*33)+33,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,34)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*34)+33),"dd mmmm yyyy"))</f>
         <v>20 January 2027 - 19 February 2027</v>
       </c>
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="238" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A43" s="237" t="str">
+      <c r="A43" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,34),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*34)+34,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,35)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*35)+34),"dd mmmm yyyy"))</f>
         <v>20 February 2027 - 19 March 2027</v>
       </c>
-      <c r="B43" s="237"/>
+      <c r="B43" s="238"/>
     </row>
     <row r="44" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A44" s="235" t="str">
+      <c r="A44" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,35),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*35)+35,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,36)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*36)+35),"dd mmmm yyyy"))</f>
         <v>20 March 2027 - 19 April 2027</v>
       </c>
-      <c r="B44" s="235"/>
+      <c r="B44" s="236"/>
     </row>
     <row r="45" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A45" s="237" t="str">
+      <c r="A45" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,36),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*36)+36,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,37)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*37)+36),"dd mmmm yyyy"))</f>
         <v>20 April 2027 - 19 May 2027</v>
       </c>
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="238" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A46" s="237" t="str">
+      <c r="A46" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,37),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*37)+37,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,38)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*38)+37),"dd mmmm yyyy"))</f>
         <v>20 May 2027 - 19 June 2027</v>
       </c>
-      <c r="B46" s="237"/>
+      <c r="B46" s="238"/>
     </row>
     <row r="47" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A47" s="235" t="str">
+      <c r="A47" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,38),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*38)+38,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,39)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*39)+38),"dd mmmm yyyy"))</f>
         <v>20 June 2027 - 19 July 2027</v>
       </c>
-      <c r="B47" s="235"/>
+      <c r="B47" s="236"/>
     </row>
     <row r="48" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A48" s="237" t="str">
+      <c r="A48" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,39),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*39)+39,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,40)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*40)+39),"dd mmmm yyyy"))</f>
         <v>20 July 2027 - 19 August 2027</v>
       </c>
-      <c r="B48" s="237" t="s">
+      <c r="B48" s="238" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A49" s="237" t="str">
+      <c r="A49" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,40),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*40)+40,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,41)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*41)+40),"dd mmmm yyyy"))</f>
         <v>20 August 2027 - 19 September 2027</v>
       </c>
-      <c r="B49" s="237"/>
+      <c r="B49" s="238"/>
     </row>
     <row r="50" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A50" s="235" t="str">
+      <c r="A50" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,41),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*41)+41,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,42)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*42)+41),"dd mmmm yyyy"))</f>
         <v>20 September 2027 - 19 October 2027</v>
       </c>
-      <c r="B50" s="235"/>
+      <c r="B50" s="236"/>
     </row>
     <row r="51" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A51" s="237" t="str">
+      <c r="A51" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,42),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*42)+42,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,43)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*43)+42),"dd mmmm yyyy"))</f>
         <v>20 October 2027 - 19 November 2027</v>
       </c>
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="238" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="52" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A52" s="237" t="str">
+      <c r="A52" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,43),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*43)+43,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,44)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*44)+43),"dd mmmm yyyy"))</f>
         <v>20 November 2027 - 19 December 2027</v>
       </c>
-      <c r="B52" s="237"/>
+      <c r="B52" s="238"/>
     </row>
     <row r="53" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A53" s="235" t="str">
+      <c r="A53" s="236" t="str">
         <f>IF(B2,TEXT(EDATE(B3,44),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*44)+44,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,45)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*45)+44),"dd mmmm yyyy"))</f>
         <v>20 December 2027 - 19 January 2028</v>
       </c>
-      <c r="B53" s="235"/>
+      <c r="B53" s="236"/>
     </row>
     <row r="54" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A54" s="237" t="str">
+      <c r="A54" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,45),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*45)+45,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,46)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*46)+45),"dd mmmm yyyy"))</f>
         <v>20 January 2028 - 19 February 2028</v>
       </c>
-      <c r="B54" s="237" t="s">
+      <c r="B54" s="238" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="55" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A55" s="237" t="str">
+      <c r="A55" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,46),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*46)+46,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,47)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*47)+46),"dd mmmm yyyy"))</f>
         <v>20 February 2028 - 19 March 2028</v>
       </c>
-      <c r="B55" s="237"/>
+      <c r="B55" s="238"/>
     </row>
     <row r="56" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A56" s="237" t="str">
+      <c r="A56" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,47),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*47)+47,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,48)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*48)+47),"dd mmmm yyyy"))</f>
         <v>20 March 2028 - 19 April 2028</v>
       </c>
-      <c r="B56" s="237"/>
+      <c r="B56" s="238"/>
     </row>
     <row r="57" ht="20.25" customHeight="1"/>
     <row r="58" ht="20.25" customHeight="1"/>
@@ -36496,75 +36511,75 @@
     <row r="62" ht="20.25" customHeight="1"/>
     <row r="63" ht="20.25" customHeight="1"/>
     <row r="64" ht="20.25" customHeight="1"/>
-    <row r="65" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="66" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="67" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="68" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="69" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="70" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="71" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="72" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="73" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="74" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="75" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="76" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="77" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="78" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="79" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="80" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="81" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="82" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="83" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="84" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="85" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="86" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="87" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="88" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="89" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="90" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="91" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="92" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="93" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="94" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="95" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="96" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="97" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="98" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="99" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="100" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="101" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="102" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="103" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="104" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="105" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="106" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="107" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="108" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="109" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="110" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="111" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="112" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="113" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="114" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="115" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="116" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="117" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="118" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="119" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="120" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="121" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="122" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="123" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="124" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="125" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="126" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="127" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="129" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="130" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="131" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="132" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="133" s="233" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="134" s="233" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="65" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="66" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="67" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="68" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="69" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="70" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="71" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="72" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="73" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="74" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="75" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="76" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="77" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="78" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="79" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="80" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="81" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="82" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="83" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="84" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="85" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="86" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="87" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="88" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="89" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="90" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="91" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="92" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="93" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="94" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="95" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="96" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="97" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="98" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="99" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="100" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="101" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="102" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="103" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="104" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="105" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="106" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="107" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="108" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="109" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="110" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="111" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="112" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="113" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="114" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="115" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="116" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="117" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="118" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="119" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="120" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="121" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="122" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="123" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="124" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="125" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="126" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="127" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="129" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="130" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="131" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="132" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="133" s="234" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="134" s="234" customFormat="1" ht="20.25" customHeight="1"/>
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="19">
@@ -36650,7 +36665,7 @@
       <c r="J2" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="214" t="s">
+      <c r="M2" s="215" t="s">
         <v>31</v>
       </c>
       <c r="N2" s="204" t="s">
@@ -36665,7 +36680,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="169">
-        <v>12</v>
+        <v>875.3</v>
       </c>
       <c r="D3" s="170" t="s">
         <v>33</v>
@@ -36674,7 +36689,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="197">
-        <v>12</v>
+        <v>1072.1</v>
       </c>
       <c r="I3" s="205" t="str">
         <f>TEXT(Main!B3,"dd mmmm yyyy")&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,1)-1,"dd mmmm yyyy"),TEXT(Main!B3+(Main!B5-Main!B3)*1,"dd mmmm yyyy"))</f>
@@ -36699,14 +36714,14 @@
         <v>35</v>
       </c>
       <c r="C4" s="169">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D4" s="171"/>
       <c r="E4" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F4" s="197">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I4" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,1),"dd mmmm yyyy"),TEXT(Main!B3+(Main!B5-Main!B3)+1,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,2)-1,"dd mmmm yyyy"),TEXT(Main!B3+(Main!B5-Main!B3)*2+1,"dd mmmm yyyy"))</f>
@@ -36795,14 +36810,14 @@
         <v>38</v>
       </c>
       <c r="C7" s="169">
-        <v>40.1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="171"/>
       <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F7" s="197">
-        <v>40.1</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="208" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,4),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*4)+4,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,5)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*5+4),"dd mmmm yyyy"))</f>
@@ -36845,7 +36860,7 @@
         <f ca="1">'July 2024 - September 2024'!E190</f>
         <v>502.71</v>
       </c>
-      <c r="M8" s="215" t="str">
+      <c r="M8" s="216" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,15),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*15+15),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,18)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+17),"dd mmmm yyyy"))</f>
         <v>20 July 2025 - 19 October 2025</v>
       </c>
@@ -36881,7 +36896,7 @@
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,18),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+18),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,21)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+20),"dd mmmm yyyy"))</f>
         <v>20 October 2025 - 19 January 2026</v>
       </c>
-      <c r="N9" s="216">
+      <c r="N9" s="217">
         <f ca="1">'October 2025 - December 2025'!C5</f>
         <v>0</v>
       </c>
@@ -36909,7 +36924,7 @@
         <f ca="1">'October 2024 - December 2024'!E163</f>
         <v>229.400000000001</v>
       </c>
-      <c r="M10" s="217" t="str">
+      <c r="M10" s="218" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,21),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+21),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,24)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*24+23),"dd mmmm yyyy"))</f>
         <v>20 January 2026 - 19 April 2026</v>
       </c>
@@ -36924,14 +36939,14 @@
         <v>42</v>
       </c>
       <c r="C11" s="169">
-        <v>20</v>
+        <v>7.8</v>
       </c>
       <c r="D11" s="171"/>
       <c r="E11" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F11" s="197">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="H11" s="198"/>
       <c r="I11" s="207" t="str">
@@ -36957,14 +36972,14 @@
         <v>43</v>
       </c>
       <c r="C12" s="169">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D12" s="171"/>
       <c r="E12" s="199" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="197">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="I12" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,9),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*9)+9,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,10)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*10+9),"dd mmmm yyyy"))</f>
@@ -36989,14 +37004,14 @@
         <v>44</v>
       </c>
       <c r="C13" s="169">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D13" s="171"/>
       <c r="E13" s="199" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="197">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="209" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,10),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*10)+10,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,11)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*11+10),"dd mmmm yyyy"))</f>
@@ -37021,14 +37036,14 @@
         <v>45</v>
       </c>
       <c r="C14" s="169">
-        <v>-14.6</v>
+        <v>30.4</v>
       </c>
       <c r="D14" s="171"/>
       <c r="E14" s="199" t="s">
         <v>45</v>
       </c>
       <c r="F14" s="197">
-        <v>-14.6</v>
+        <v>30.4</v>
       </c>
       <c r="I14" s="209" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,11),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*11)+11,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,12)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*12+11),"dd mmmm yyyy"))</f>
@@ -37060,7 +37075,7 @@
         <v>46</v>
       </c>
       <c r="F15" s="197">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I15" s="211" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,12),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*12)+12,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,13)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*13+12),"dd mmmm yyyy"))</f>
@@ -37068,7 +37083,7 @@
       </c>
       <c r="J15" s="210">
         <f ca="1">'April 2025 - June 2025'!E136</f>
-        <v>679.500000000001</v>
+        <v>920.500000000001</v>
       </c>
       <c r="M15" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,36),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+36),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,39)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+38),"dd mmmm yyyy"))</f>
@@ -37086,7 +37101,7 @@
       </c>
       <c r="C16" s="175">
         <f>SUM(C3:C15)</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D16" s="176"/>
       <c r="E16" s="174" t="s">
@@ -37094,7 +37109,7 @@
       </c>
       <c r="F16" s="200">
         <f>SUM(F3:F15)</f>
-        <v>191.5</v>
+        <v>1252.5</v>
       </c>
       <c r="I16" s="211" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,13),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*13)+13,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,14)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*14+13),"dd mmmm yyyy"))</f>
@@ -37102,7 +37117,7 @@
       </c>
       <c r="J16" s="210">
         <f ca="1">'April 2025 - June 2025'!E163</f>
-        <v>833.500000000001</v>
+        <v>1071.5</v>
       </c>
       <c r="M16" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,39),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+39),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,42)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+41),"dd mmmm yyyy"))</f>
@@ -37120,7 +37135,7 @@
       </c>
       <c r="J17" s="210">
         <f ca="1">'April 2025 - June 2025'!E190</f>
-        <v>596.500000000001</v>
+        <v>831.500000000001</v>
       </c>
       <c r="M17" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,42),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+42),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,45)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+44),"dd mmmm yyyy"))</f>
@@ -37138,7 +37153,7 @@
       </c>
       <c r="J18" s="210">
         <f ca="1">'July 2025 - September 2025'!E136</f>
-        <v>465.500000000001</v>
+        <v>697.500000000001</v>
       </c>
       <c r="M18" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,45),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+45),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,48)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*48+47),"dd mmmm yyyy"))</f>
@@ -37156,17 +37171,17 @@
       </c>
       <c r="J19" s="210">
         <f ca="1">'July 2025 - September 2025'!E163</f>
-        <v>478.500000000001</v>
+        <v>707.500000000001</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="9:10">
-      <c r="I20" s="211" t="str">
+      <c r="I20" s="212" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,17),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*17)+17,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,18)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+17),"dd mmmm yyyy"))</f>
         <v>20 September 2025 - 19 October 2025</v>
       </c>
       <c r="J20" s="210">
         <f ca="1">'July 2025 - September 2025'!E190</f>
-        <v>413.500000000001</v>
+        <v>639.500000000001</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="9:10">
@@ -37176,7 +37191,7 @@
       </c>
       <c r="J21" s="210">
         <f ca="1">'October 2025 - December 2025'!E136</f>
-        <v>941.300000000001</v>
+        <v>1227.2</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:10">
@@ -37190,13 +37205,13 @@
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="I22" s="212" t="str">
+      <c r="I22" s="213" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,19),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*19)+19,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,20)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*20+19),"dd mmmm yyyy"))</f>
         <v>20 November 2025 - 19 December 2025</v>
       </c>
       <c r="J22" s="210">
         <f ca="1">'October 2025 - December 2025'!E163</f>
-        <v>1674.1</v>
+        <v>2019.9</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:10">
@@ -37215,13 +37230,13 @@
         <v>50</v>
       </c>
       <c r="G23" s="18"/>
-      <c r="I23" s="212" t="str">
+      <c r="I23" s="213" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,20),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*20)+20,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,21)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+20),"dd mmmm yyyy"))</f>
         <v>20 December 2025 - 19 January 2026</v>
       </c>
       <c r="J23" s="210">
         <f ca="1">'October 2025 - December 2025'!E190</f>
-        <v>2165.9</v>
+        <v>2571.6</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:10">
@@ -37246,7 +37261,7 @@
       </c>
       <c r="J24" s="210">
         <f ca="1">'January 2026 - March 2026'!E136</f>
-        <v>2948.7</v>
+        <v>3414.3</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:10">
@@ -37265,7 +37280,7 @@
       </c>
       <c r="J25" s="210">
         <f ca="1">'January 2026 - March 2026'!E163</f>
-        <v>3280.5</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:10">
@@ -37284,7 +37299,7 @@
       </c>
       <c r="J26" s="210">
         <f ca="1">'January 2026 - March 2026'!E190</f>
-        <v>4063.3</v>
+        <v>4648.7</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:10">
@@ -37303,7 +37318,7 @@
       </c>
       <c r="J27" s="210">
         <f ca="1">'April 2026 - June 2026'!E136</f>
-        <v>4555.1</v>
+        <v>5200.4</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:10">
@@ -37322,7 +37337,7 @@
       </c>
       <c r="J28" s="210">
         <f ca="1">'April 2026 - June 2026'!E163</f>
-        <v>5177.9</v>
+        <v>5883.1</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:10">
@@ -37341,7 +37356,7 @@
       </c>
       <c r="J29" s="206">
         <f ca="1">'April 2026 - June 2026'!E190</f>
-        <v>5669.7</v>
+        <v>6434.8</v>
       </c>
     </row>
     <row r="30" ht="35" customHeight="1" spans="1:10">
@@ -37361,9 +37376,9 @@
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,27),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*27)+27,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,28)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*28+27),"dd mmmm yyyy"))</f>
         <v>20 July 2026 - 19 August 2026</v>
       </c>
-      <c r="J30" s="213">
+      <c r="J30" s="214">
         <f ca="1">'July 2026 - September 2026'!E136</f>
-        <v>6452.5</v>
+        <v>7277.5</v>
       </c>
     </row>
     <row r="31" ht="35" customHeight="1" spans="9:10">
@@ -37373,7 +37388,7 @@
       </c>
       <c r="J31" s="210">
         <f ca="1">'July 2026 - September 2026'!E163</f>
-        <v>6784.3</v>
+        <v>7669.2</v>
       </c>
     </row>
     <row r="32" ht="35" customHeight="1" spans="9:10">
@@ -37383,7 +37398,7 @@
       </c>
       <c r="J32" s="210">
         <f ca="1">'July 2026 - September 2026'!E190</f>
-        <v>7567.1</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="33" ht="35" customHeight="1" spans="9:10">
@@ -37393,7 +37408,7 @@
       </c>
       <c r="J33" s="210">
         <f ca="1">'October 2026 - December 2026'!E136</f>
-        <v>8058.9</v>
+        <v>9000.7</v>
       </c>
     </row>
     <row r="34" ht="35" customHeight="1" spans="1:10">
@@ -37413,7 +37428,7 @@
       </c>
       <c r="J34" s="210">
         <f ca="1">'October 2026 - December 2026'!E163</f>
-        <v>8681.7</v>
+        <v>9683.4</v>
       </c>
     </row>
     <row r="35" ht="35" customHeight="1" spans="1:10">
@@ -37438,7 +37453,7 @@
       </c>
       <c r="J35" s="210">
         <f ca="1">'October 2026 - December 2026'!E190</f>
-        <v>9173.5</v>
+        <v>10235.1</v>
       </c>
     </row>
     <row r="36" ht="35" customHeight="1" spans="1:10">
@@ -37463,7 +37478,7 @@
       </c>
       <c r="J36" s="210">
         <f ca="1">'January 2027 - March 2027'!E136</f>
-        <v>9956.3</v>
+        <v>11077.8</v>
       </c>
     </row>
     <row r="37" ht="35" customHeight="1" spans="1:10">
@@ -37488,7 +37503,7 @@
       </c>
       <c r="J37" s="210">
         <f ca="1">'January 2027 - March 2027'!E163</f>
-        <v>10288.1</v>
+        <v>11469.5</v>
       </c>
     </row>
     <row r="38" ht="35" customHeight="1" spans="1:10">
@@ -37513,7 +37528,7 @@
       </c>
       <c r="J38" s="210">
         <f ca="1">'January 2027 - March 2027'!E190</f>
-        <v>11070.9</v>
+        <v>12312.2</v>
       </c>
     </row>
     <row r="39" ht="35" customHeight="1" spans="1:10">
@@ -37532,7 +37547,7 @@
       </c>
       <c r="J39" s="210">
         <f ca="1">'April 2027 - June 2027'!E136</f>
-        <v>11562.7</v>
+        <v>12863.9</v>
       </c>
     </row>
     <row r="40" ht="35" customHeight="1" spans="1:10">
@@ -37551,7 +37566,7 @@
       </c>
       <c r="J40" s="210">
         <f ca="1">'April 2027 - June 2027'!E163</f>
-        <v>12185.5</v>
+        <v>13546.6</v>
       </c>
     </row>
     <row r="41" ht="35" customHeight="1" spans="1:10">
@@ -37570,7 +37585,7 @@
       </c>
       <c r="J41" s="210">
         <f ca="1">'April 2027 - June 2027'!E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="42" ht="35" customHeight="1" spans="1:10">
@@ -37592,7 +37607,7 @@
       </c>
       <c r="J42" s="210">
         <f ca="1">Forecast_14!E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="43" ht="35" customHeight="1" spans="9:10">
@@ -37602,7 +37617,7 @@
       </c>
       <c r="J43" s="210">
         <f ca="1">Forecast_14!E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="44" ht="35" customHeight="1" spans="9:10">
@@ -37612,7 +37627,7 @@
       </c>
       <c r="J44" s="210">
         <f ca="1">Forecast_14!E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="45" ht="35" customHeight="1" spans="9:10">
@@ -37622,7 +37637,7 @@
       </c>
       <c r="J45" s="210">
         <f ca="1">Forecast_15!E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="46" ht="35" customHeight="1" spans="1:10">
@@ -37642,7 +37657,7 @@
       </c>
       <c r="J46" s="210">
         <f ca="1">Forecast_15!E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="47" ht="35" customHeight="1" spans="1:10">
@@ -37667,7 +37682,7 @@
       </c>
       <c r="J47" s="210">
         <f ca="1">Forecast_15!E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="48" ht="35" customHeight="1" spans="1:10">
@@ -37692,7 +37707,7 @@
       </c>
       <c r="J48" s="210">
         <f ca="1">Forecast_16!E136</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="49" ht="35" customHeight="1" spans="1:10">
@@ -37717,7 +37732,7 @@
       </c>
       <c r="J49" s="210">
         <f ca="1">Forecast_16!E163</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="50" ht="35" customHeight="1" spans="1:10">
@@ -37742,7 +37757,7 @@
       </c>
       <c r="J50" s="206">
         <f ca="1">Forecast_16!E190</f>
-        <v>12677.3</v>
+        <v>14098.3</v>
       </c>
     </row>
     <row r="51" ht="35" customHeight="1" spans="1:7">
@@ -37872,28 +37887,28 @@
         <v>77</v>
       </c>
       <c r="B65" s="194"/>
-      <c r="C65" s="218">
+      <c r="C65" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="66" ht="35" customHeight="1" spans="1:3">
       <c r="A66" s="50"/>
       <c r="B66" s="194"/>
-      <c r="C66" s="218">
+      <c r="C66" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="67" ht="35" customHeight="1" spans="1:3">
       <c r="A67" s="50"/>
       <c r="B67" s="194"/>
-      <c r="C67" s="218">
+      <c r="C67" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="68" ht="35" customHeight="1" spans="1:3">
       <c r="A68" s="50"/>
       <c r="B68" s="194"/>
-      <c r="C68" s="218">
+      <c r="C68" s="219">
         <v>0</v>
       </c>
     </row>
@@ -37902,7 +37917,7 @@
       <c r="B69" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C69" s="218">
+      <c r="C69" s="219">
         <f>SUM(C61:C68)</f>
         <v>443</v>
       </c>
@@ -37919,7 +37934,7 @@
         <v>80</v>
       </c>
       <c r="B71" s="194"/>
-      <c r="C71" s="218">
+      <c r="C71" s="219">
         <v>0</v>
       </c>
     </row>
@@ -37928,7 +37943,7 @@
         <v>81</v>
       </c>
       <c r="B72" s="194"/>
-      <c r="C72" s="218">
+      <c r="C72" s="219">
         <v>0</v>
       </c>
     </row>
@@ -37937,7 +37952,7 @@
         <v>82</v>
       </c>
       <c r="B73" s="194"/>
-      <c r="C73" s="218">
+      <c r="C73" s="219">
         <v>0</v>
       </c>
     </row>
@@ -37946,51 +37961,51 @@
         <v>83</v>
       </c>
       <c r="B74" s="194"/>
-      <c r="C74" s="218">
+      <c r="C74" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="75" ht="35" customHeight="1" spans="1:3">
       <c r="A75" s="50"/>
       <c r="B75" s="194"/>
-      <c r="C75" s="218">
+      <c r="C75" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="76" ht="35" customHeight="1" spans="1:3">
       <c r="A76" s="50"/>
       <c r="B76" s="194"/>
-      <c r="C76" s="218">
+      <c r="C76" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="77" ht="35" customHeight="1" spans="1:3">
       <c r="A77" s="50"/>
       <c r="B77" s="194"/>
-      <c r="C77" s="218">
+      <c r="C77" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="78" ht="35" customHeight="1" spans="1:3">
       <c r="A78" s="50"/>
       <c r="B78" s="194"/>
-      <c r="C78" s="218">
+      <c r="C78" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="79" ht="35" customHeight="1" spans="1:3">
       <c r="A79" s="50"/>
       <c r="B79" s="194"/>
-      <c r="C79" s="218">
+      <c r="C79" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="80" ht="35" customHeight="1" spans="1:3">
-      <c r="A80" s="219"/>
-      <c r="B80" s="220" t="s">
+      <c r="A80" s="220"/>
+      <c r="B80" s="221" t="s">
         <v>78</v>
       </c>
-      <c r="C80" s="218">
+      <c r="C80" s="219">
         <f>SUM(C71:C79)</f>
         <v>0</v>
       </c>
@@ -38014,7 +38029,7 @@
       </c>
     </row>
     <row r="83" ht="35" customHeight="1" spans="1:3">
-      <c r="A83" s="221" t="s">
+      <c r="A83" s="222" t="s">
         <v>87</v>
       </c>
       <c r="B83" s="194" t="s">
@@ -38060,8 +38075,8 @@
       </c>
     </row>
     <row r="89" ht="35" customHeight="1" spans="1:3">
-      <c r="A89" s="219"/>
-      <c r="B89" s="220" t="s">
+      <c r="A89" s="220"/>
+      <c r="B89" s="221" t="s">
         <v>78</v>
       </c>
       <c r="C89" s="36">
@@ -38077,60 +38092,60 @@
       <c r="C90" s="193"/>
     </row>
     <row r="91" ht="35" customHeight="1" spans="1:3">
-      <c r="A91" s="222" t="s">
+      <c r="A91" s="223" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="223"/>
-      <c r="C91" s="218">
+      <c r="B91" s="224"/>
+      <c r="C91" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="92" ht="35" customHeight="1" spans="1:3">
       <c r="A92" s="51"/>
       <c r="B92" s="194"/>
-      <c r="C92" s="218">
+      <c r="C92" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="93" ht="35" customHeight="1" spans="1:3">
       <c r="A93" s="51"/>
       <c r="B93" s="194"/>
-      <c r="C93" s="218">
+      <c r="C93" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="94" ht="35" customHeight="1" spans="1:3">
       <c r="A94" s="50"/>
       <c r="B94" s="194"/>
-      <c r="C94" s="218">
+      <c r="C94" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="95" ht="35" customHeight="1" spans="1:3">
       <c r="A95" s="50"/>
       <c r="B95" s="194"/>
-      <c r="C95" s="218">
+      <c r="C95" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="96" ht="35" customHeight="1" spans="1:3">
       <c r="A96" s="50"/>
       <c r="B96" s="194"/>
-      <c r="C96" s="218">
+      <c r="C96" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="97" ht="35" customHeight="1" spans="1:3">
       <c r="A97" s="50"/>
       <c r="B97" s="194"/>
-      <c r="C97" s="218">
+      <c r="C97" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="98" ht="35" customHeight="1" spans="1:3">
       <c r="A98" s="50"/>
       <c r="B98" s="194"/>
-      <c r="C98" s="218">
+      <c r="C98" s="219">
         <v>0</v>
       </c>
     </row>
@@ -38155,7 +38170,7 @@
       <c r="A101" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="B101" s="224" t="s">
+      <c r="B101" s="225" t="s">
         <v>93</v>
       </c>
       <c r="C101" s="98">
@@ -38198,28 +38213,28 @@
     <row r="105" ht="35" customHeight="1" spans="1:3">
       <c r="A105" s="50"/>
       <c r="B105" s="194"/>
-      <c r="C105" s="218">
+      <c r="C105" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="106" ht="35" customHeight="1" spans="1:3">
       <c r="A106" s="50"/>
       <c r="B106" s="194"/>
-      <c r="C106" s="218">
+      <c r="C106" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="107" ht="35" customHeight="1" spans="1:3">
       <c r="A107" s="50"/>
       <c r="B107" s="194"/>
-      <c r="C107" s="218">
+      <c r="C107" s="219">
         <v>0</v>
       </c>
     </row>
     <row r="108" ht="35" customHeight="1" spans="1:3">
       <c r="A108" s="50"/>
       <c r="B108" s="194"/>
-      <c r="C108" s="218">
+      <c r="C108" s="219">
         <v>0</v>
       </c>
     </row>
@@ -38228,7 +38243,7 @@
       <c r="B109" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="C109" s="218">
+      <c r="C109" s="219">
         <f>SUM(C101:C108)</f>
         <v>1060</v>
       </c>
@@ -38238,7 +38253,7 @@
       <c r="B110" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="C110" s="218">
+      <c r="C110" s="219">
         <f>C69+C80+C89+C99+C109</f>
         <v>1503</v>
       </c>
@@ -38251,11 +38266,11 @@
       <c r="C111" s="193"/>
     </row>
     <row r="112" ht="35" customHeight="1" spans="1:8">
-      <c r="A112" s="225" t="s">
+      <c r="A112" s="226" t="s">
         <v>102</v>
       </c>
-      <c r="B112" s="226"/>
-      <c r="C112" s="227">
+      <c r="B112" s="227"/>
+      <c r="C112" s="228">
         <v>14950</v>
       </c>
       <c r="D112" s="14"/>
@@ -38265,11 +38280,11 @@
       <c r="H112" s="14"/>
     </row>
     <row r="113" ht="35" customHeight="1" spans="1:8">
-      <c r="A113" s="225" t="s">
+      <c r="A113" s="226" t="s">
         <v>103</v>
       </c>
       <c r="B113" s="194"/>
-      <c r="C113" s="228">
+      <c r="C113" s="229">
         <f>5000</f>
         <v>5000</v>
       </c>
@@ -38280,11 +38295,11 @@
       <c r="H113" s="14"/>
     </row>
     <row r="114" ht="35" customHeight="1" spans="1:8">
-      <c r="A114" s="225" t="s">
+      <c r="A114" s="226" t="s">
         <v>104</v>
       </c>
       <c r="B114" s="194"/>
-      <c r="C114" s="229">
+      <c r="C114" s="230">
         <f>3300</f>
         <v>3300</v>
       </c>
@@ -38295,11 +38310,11 @@
       <c r="H114" s="14"/>
     </row>
     <row r="115" ht="35" customHeight="1" spans="1:8">
-      <c r="A115" s="230" t="s">
+      <c r="A115" s="231" t="s">
         <v>105</v>
       </c>
       <c r="B115" s="194"/>
-      <c r="C115" s="229">
+      <c r="C115" s="230">
         <v>0</v>
       </c>
       <c r="D115" s="14"/>
@@ -38309,11 +38324,11 @@
       <c r="H115" s="14"/>
     </row>
     <row r="116" ht="35" customHeight="1" spans="1:8">
-      <c r="A116" s="230" t="s">
+      <c r="A116" s="231" t="s">
         <v>106</v>
       </c>
       <c r="B116" s="194"/>
-      <c r="C116" s="229">
+      <c r="C116" s="230">
         <v>0</v>
       </c>
       <c r="D116" s="14"/>
@@ -38385,18 +38400,18 @@
       <c r="H121" s="14"/>
     </row>
     <row r="122" ht="35" customHeight="1" spans="1:3">
-      <c r="A122" s="219"/>
-      <c r="B122" s="220" t="s">
+      <c r="A122" s="220"/>
+      <c r="B122" s="221" t="s">
         <v>108</v>
       </c>
-      <c r="C122" s="218">
+      <c r="C122" s="219">
         <f>SUM(C112:C121)</f>
         <v>24333</v>
       </c>
     </row>
     <row r="123" ht="35" customHeight="1" spans="1:3">
-      <c r="A123" s="219"/>
-      <c r="B123" s="220" t="s">
+      <c r="A123" s="220"/>
+      <c r="B123" s="221" t="s">
         <v>109</v>
       </c>
       <c r="C123" s="36">
@@ -38405,10 +38420,10 @@
       </c>
     </row>
     <row r="124" ht="35" customHeight="1" spans="5:5">
-      <c r="E124" s="231"/>
+      <c r="E124" s="232"/>
     </row>
     <row r="125" ht="35" customHeight="1" spans="5:5">
-      <c r="E125" s="231"/>
+      <c r="E125" s="232"/>
     </row>
     <row r="126" ht="35" customHeight="1"/>
     <row r="127" ht="35" customHeight="1"/>
@@ -38685,8 +38700,8 @@
         <v>Balance Brought Forward From May 2024</v>
       </c>
       <c r="B156" s="56"/>
-      <c r="C156" s="232"/>
-      <c r="D156" s="232"/>
+      <c r="C156" s="233"/>
+      <c r="D156" s="233"/>
       <c r="E156" s="87">
         <f>E149</f>
         <v>0</v>
@@ -38955,8 +38970,8 @@
         <v>Balance Brought Forward From June 2024</v>
       </c>
       <c r="B183" s="56"/>
-      <c r="C183" s="232"/>
-      <c r="D183" s="232"/>
+      <c r="C183" s="233"/>
+      <c r="D183" s="233"/>
       <c r="E183" s="90">
         <f>E176</f>
         <v>-416.68</v>
@@ -39696,7 +39711,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -39724,7 +39739,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>669.21</v>
+        <v>1548.21</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -43146,7 +43161,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -43174,7 +43189,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>339.840000000001</v>
+        <v>1218.84</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -46692,7 +46707,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -46724,7 +46739,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>333.000000000001</v>
+        <v>1212</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -50210,7 +50225,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -50226,7 +50241,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>596.500000000001</v>
+        <v>831.500000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -50242,7 +50257,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>763.000000000001</v>
+        <v>1877</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -50377,29 +50392,33 @@
     </row>
     <row r="13" ht="24.75" customHeight="1" spans="1:9">
       <c r="A13" s="95"/>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="110" t="s">
         <v>253</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97" t="s">
+      <c r="C13" s="111"/>
+      <c r="D13" s="110" t="s">
         <v>254</v>
       </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="7">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="41">
+        <v>50</v>
+      </c>
+      <c r="G13" s="42"/>
       <c r="H13" s="14"/>
       <c r="I13" s="47"/>
     </row>
-    <row r="14" ht="25" customHeight="1" spans="1:9">
+    <row r="14" ht="20" customHeight="1" spans="1:9">
       <c r="A14" s="19"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="22"/>
+      <c r="B14" s="110" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="111"/>
+      <c r="D14" s="110" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="111"/>
       <c r="F14" s="41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="42"/>
       <c r="H14" s="14"/>
@@ -50409,8 +50428,8 @@
       <c r="A15" s="19"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="43"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="41">
         <v>0</v>
       </c>
@@ -50428,7 +50447,7 @@
       <c r="E16" s="44"/>
       <c r="F16" s="45">
         <f>SUM(F10:G15)</f>
-        <v>2435</v>
+        <v>2486</v>
       </c>
       <c r="G16" s="46"/>
       <c r="H16" s="14"/>
@@ -50519,7 +50538,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -50543,7 +50562,7 @@
       </c>
       <c r="C24" s="114"/>
       <c r="D24" s="115" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E24" s="115"/>
       <c r="F24" s="116">
@@ -50693,7 +50712,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -51632,7 +51651,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -51743,7 +51762,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -51759,7 +51778,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -52004,7 +52023,7 @@
       </c>
       <c r="C109" s="36">
         <f ca="1">C108-C96</f>
-        <v>-3480</v>
+        <v>-3483</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -52124,7 +52143,7 @@
       <c r="A118" s="62"/>
       <c r="B118" s="63"/>
       <c r="C118" s="100" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D118" s="100"/>
       <c r="E118" s="36">
@@ -52269,7 +52288,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="100" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D129" s="112"/>
       <c r="E129" s="98">
@@ -52280,15 +52299,15 @@
       <c r="H129" s="14"/>
       <c r="I129" s="47"/>
     </row>
-    <row r="130" ht="40" customHeight="1" spans="1:9">
+    <row r="130" ht="137" customHeight="1" spans="1:9">
       <c r="A130" s="62"/>
       <c r="B130" s="63"/>
       <c r="C130" s="117" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D130" s="118"/>
       <c r="E130" s="98">
-        <v>400</v>
+        <v>207</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -52356,7 +52375,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -52372,7 +52391,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>679.500000000001</v>
+        <v>920.500000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -52464,7 +52483,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>679.500000000001</v>
+        <v>920.500000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -52490,7 +52509,7 @@
       <c r="A145" s="62"/>
       <c r="B145" s="63"/>
       <c r="C145" s="112" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D145" s="112"/>
       <c r="E145" s="36">
@@ -52635,7 +52654,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="100" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D156" s="100"/>
       <c r="E156" s="98">
@@ -52646,11 +52665,11 @@
       <c r="H156" s="14"/>
       <c r="I156" s="47"/>
     </row>
-    <row r="157" ht="20" customHeight="1" spans="1:9">
+    <row r="157" ht="25" customHeight="1" spans="1:9">
       <c r="A157" s="62"/>
       <c r="B157" s="63"/>
       <c r="C157" s="100" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="98">
@@ -52722,7 +52741,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -52738,7 +52757,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>833.500000000001</v>
+        <v>1071.5</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -52830,7 +52849,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>833.500000000001</v>
+        <v>1071.5</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -52856,7 +52875,7 @@
       <c r="A172" s="62"/>
       <c r="B172" s="63"/>
       <c r="C172" s="112" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D172" s="112"/>
       <c r="E172" s="36">
@@ -53001,7 +53020,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="100" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D183" s="100"/>
       <c r="E183" s="98">
@@ -53088,7 +53107,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -53104,7 +53123,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>596.500000000001</v>
+        <v>831.500000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -53657,7 +53676,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -53673,7 +53692,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>413.500000000001</v>
+        <v>639.500000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -53689,7 +53708,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>580.000000000001</v>
+        <v>1685</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -53788,7 +53807,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -53808,11 +53827,11 @@
     <row r="12" ht="24.75" customHeight="1" spans="1:9">
       <c r="A12" s="95"/>
       <c r="B12" s="96" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C12" s="96"/>
       <c r="D12" s="97" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E12" s="97"/>
       <c r="F12" s="7">
@@ -53962,7 +53981,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -54136,7 +54155,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -54156,11 +54175,11 @@
     <row r="36" ht="24.75" customHeight="1" spans="1:9">
       <c r="A36" s="109"/>
       <c r="B36" s="110" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C36" s="111"/>
       <c r="D36" s="110" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E36" s="111"/>
       <c r="F36" s="7">
@@ -54173,7 +54192,7 @@
     <row r="37" ht="24.75" customHeight="1" spans="1:9">
       <c r="A37" s="19"/>
       <c r="B37" s="21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="23"/>
@@ -55077,7 +55096,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -55188,7 +55207,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -55204,7 +55223,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -55449,7 +55468,7 @@
       </c>
       <c r="C109" s="108">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -55543,7 +55562,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!E190")</f>
-        <v>596.500000000001</v>
+        <v>831.500000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -55569,7 +55588,7 @@
       <c r="A118" s="62"/>
       <c r="B118" s="63"/>
       <c r="C118" s="112" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D118" s="112"/>
       <c r="E118" s="98">
@@ -55714,7 +55733,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="100" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D129" s="100"/>
       <c r="E129" s="98">
@@ -55729,7 +55748,7 @@
       <c r="A130" s="62"/>
       <c r="B130" s="63"/>
       <c r="C130" s="100" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="98">
@@ -55801,7 +55820,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -55817,7 +55836,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>465.500000000001</v>
+        <v>697.500000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -55909,7 +55928,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>465.500000000001</v>
+        <v>697.500000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -55935,7 +55954,7 @@
       <c r="A145" s="62"/>
       <c r="B145" s="63"/>
       <c r="C145" s="112" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D145" s="112"/>
       <c r="E145" s="98">
@@ -56080,7 +56099,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="100" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D156" s="100"/>
       <c r="E156" s="98">
@@ -56095,7 +56114,7 @@
       <c r="A157" s="62"/>
       <c r="B157" s="63"/>
       <c r="C157" s="100" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="98">
@@ -56167,7 +56186,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -56183,7 +56202,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>478.500000000001</v>
+        <v>707.500000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -56275,7 +56294,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>478.500000000001</v>
+        <v>707.500000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -56301,7 +56320,7 @@
       <c r="A172" s="62"/>
       <c r="B172" s="63"/>
       <c r="C172" s="112" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D172" s="112"/>
       <c r="E172" s="98">
@@ -56368,7 +56387,7 @@
       <c r="A177" s="62"/>
       <c r="B177" s="63"/>
       <c r="C177" s="112" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D177" s="112"/>
       <c r="E177" s="36">
@@ -56448,7 +56467,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="100" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D183" s="100"/>
       <c r="E183" s="98">
@@ -56463,7 +56482,7 @@
       <c r="A184" s="62"/>
       <c r="B184" s="63"/>
       <c r="C184" s="100" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="98">
@@ -56535,7 +56554,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -56551,7 +56570,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>413.500000000001</v>
+        <v>639.500000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -57104,7 +57123,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>166.5</v>
+        <v>1045.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -57120,7 +57139,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>2165.9</v>
+        <v>2571.6</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -57136,7 +57155,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>2332.4</v>
+        <v>3617.1</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -57235,7 +57254,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B11" s="96" t="s">
         <v>66</v>
@@ -57409,7 +57428,7 @@
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:9">
       <c r="A23" s="95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B23" s="96" t="s">
         <v>66</v>
@@ -57579,7 +57598,7 @@
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:9">
       <c r="A35" s="95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B35" s="96" t="s">
         <v>66</v>
@@ -58518,7 +58537,7 @@
         <v>Hair Cut not Include Color treatment</v>
       </c>
       <c r="C89" s="98">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14"/>
@@ -58629,7 +58648,7 @@
       </c>
       <c r="C95" s="36">
         <f>SUM(C87:C94)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14"/>
@@ -58645,7 +58664,7 @@
       </c>
       <c r="C96" s="36">
         <f>C55+C66+C75+C85+C95</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14"/>
@@ -58890,7 +58909,7 @@
       </c>
       <c r="C109" s="108">
         <f ca="1">C108-C96</f>
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -58984,7 +59003,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!E190")</f>
-        <v>413.500000000001</v>
+        <v>639.500000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -59153,7 +59172,7 @@
       <c r="A129" s="62"/>
       <c r="B129" s="63"/>
       <c r="C129" s="100" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D129" s="100"/>
       <c r="E129" s="98">
@@ -59172,7 +59191,7 @@
       </c>
       <c r="D130" s="100"/>
       <c r="E130" s="98">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -59183,7 +59202,7 @@
       <c r="A131" s="62"/>
       <c r="B131" s="63"/>
       <c r="C131" s="64" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D131" s="65"/>
       <c r="E131" s="86">
@@ -59242,7 +59261,7 @@
       <c r="D135" s="78"/>
       <c r="E135" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F135" s="14"/>
       <c r="G135" s="14"/>
@@ -59258,7 +59277,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>941.300000000001</v>
+        <v>1227.2</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -59350,7 +59369,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>941.300000000001</v>
+        <v>1227.2</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -59519,7 +59538,7 @@
       <c r="A156" s="62"/>
       <c r="B156" s="63"/>
       <c r="C156" s="100" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D156" s="100"/>
       <c r="E156" s="102">
@@ -59538,7 +59557,7 @@
       </c>
       <c r="D157" s="100"/>
       <c r="E157" s="102">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F157" s="14"/>
       <c r="G157" s="14"/>
@@ -59606,7 +59625,7 @@
       <c r="D162" s="78"/>
       <c r="E162" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F162" s="14"/>
       <c r="G162" s="14"/>
@@ -59622,7 +59641,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>1674.1</v>
+        <v>2019.9</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -59714,7 +59733,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>1674.1</v>
+        <v>2019.9</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -59883,7 +59902,7 @@
       <c r="A183" s="62"/>
       <c r="B183" s="63"/>
       <c r="C183" s="100" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D183" s="100"/>
       <c r="E183" s="98">
@@ -59902,7 +59921,7 @@
       </c>
       <c r="D184" s="100"/>
       <c r="E184" s="98">
-        <v>586.2</v>
+        <v>523.3</v>
       </c>
       <c r="F184" s="14"/>
       <c r="G184" s="14"/>
@@ -59970,7 +59989,7 @@
       <c r="D189" s="78"/>
       <c r="E189" s="86">
         <f>C96</f>
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F189" s="14"/>
       <c r="G189" s="14"/>
@@ -59986,7 +60005,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>2165.9</v>
+        <v>2571.6</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>

--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -1218,10 +1218,12 @@
     <t>Birdie Paid in advance</t>
   </si>
   <si>
-    <t>1.  yuu</t>
+    <t>1.  yuu
+2. Google Play</t>
   </si>
   <si>
-    <t>1. Newly added / remain yuu points ~ $1</t>
+    <t>1. Newly added / remain yuu points ~ $1
+2. Google Play Newly top up $136</t>
   </si>
   <si>
     <t>31th May 2025</t>
@@ -5745,7 +5747,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -5761,7 +5763,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>4648.7</v>
+        <v>4784.7</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -5777,7 +5779,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>5694.2</v>
+        <v>5966.2</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7629,7 +7631,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!E190")</f>
-        <v>2571.6</v>
+        <v>2707.6</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -7901,7 +7903,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>3414.3</v>
+        <v>3550.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -7993,7 +7995,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>3414.3</v>
+        <v>3550.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -8265,7 +8267,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>3806</v>
+        <v>3942</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -8357,7 +8359,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>3806</v>
+        <v>3942</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -8629,7 +8631,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>4648.7</v>
+        <v>4784.7</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -9154,7 +9156,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -9170,7 +9172,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>6434.8</v>
+        <v>6570.8</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -9186,7 +9188,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>7480.3</v>
+        <v>7752.3</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -11038,7 +11040,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!E190")</f>
-        <v>4648.7</v>
+        <v>4784.7</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -11310,7 +11312,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>5200.4</v>
+        <v>5336.4</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -11402,7 +11404,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>5200.4</v>
+        <v>5336.4</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -11674,7 +11676,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>5883.1</v>
+        <v>6019.1</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -11766,7 +11768,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>5883.1</v>
+        <v>6019.1</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -12038,7 +12040,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>6434.8</v>
+        <v>6570.8</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -12564,7 +12566,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -12580,7 +12582,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>8449</v>
+        <v>8585</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -12596,7 +12598,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>9494.5</v>
+        <v>9766.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -14448,7 +14450,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!E190")</f>
-        <v>6434.8</v>
+        <v>6570.8</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -14720,7 +14722,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>7277.5</v>
+        <v>7413.5</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -14812,7 +14814,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>7277.5</v>
+        <v>7413.5</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -15084,7 +15086,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>7669.2</v>
+        <v>7805.2</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -15176,7 +15178,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>7669.2</v>
+        <v>7805.2</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -15448,7 +15450,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>8449</v>
+        <v>8585</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -15973,7 +15975,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -15989,7 +15991,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>10235.1</v>
+        <v>10371.1</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -16005,7 +16007,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>11280.6</v>
+        <v>11552.6</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -17857,7 +17859,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!E190")</f>
-        <v>8449</v>
+        <v>8585</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -18129,7 +18131,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>9000.7</v>
+        <v>9136.7</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -18221,7 +18223,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>9000.7</v>
+        <v>9136.7</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -18493,7 +18495,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>9683.4</v>
+        <v>9819.4</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -18585,7 +18587,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>9683.4</v>
+        <v>9819.4</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -18857,7 +18859,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>10235.1</v>
+        <v>10371.1</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -19383,7 +19385,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -19399,7 +19401,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>12312.2</v>
+        <v>12448.2</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -19415,7 +19417,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>13357.7</v>
+        <v>13629.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -21267,7 +21269,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!E190")</f>
-        <v>10235.1</v>
+        <v>10371.1</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -21539,7 +21541,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>11077.8</v>
+        <v>11213.8</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -21631,7 +21633,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>11077.8</v>
+        <v>11213.8</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -21903,7 +21905,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>11469.5</v>
+        <v>11605.5</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -21995,7 +21997,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>11469.5</v>
+        <v>11605.5</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -22267,7 +22269,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>12312.2</v>
+        <v>12448.2</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -22792,7 +22794,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -22808,7 +22810,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -22824,7 +22826,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>15143.8</v>
+        <v>15415.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -24676,7 +24678,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!E190")</f>
-        <v>12312.2</v>
+        <v>12448.2</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -24948,7 +24950,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>12863.9</v>
+        <v>12999.9</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -25040,7 +25042,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>12863.9</v>
+        <v>12999.9</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -25312,7 +25314,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>13546.6</v>
+        <v>13682.6</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -25404,7 +25406,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>13546.6</v>
+        <v>13682.6</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -25676,7 +25678,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -26201,7 +26203,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -26217,7 +26219,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -26233,7 +26235,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>15143.8</v>
+        <v>15415.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -28043,7 +28045,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!E190")</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -28311,7 +28313,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -28403,7 +28405,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -28671,7 +28673,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -28763,7 +28765,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -29031,7 +29033,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -29503,7 +29505,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -29519,7 +29521,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -29535,7 +29537,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>15143.8</v>
+        <v>15415.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -31344,7 +31346,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!E190")</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -31612,7 +31614,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -31704,7 +31706,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -31972,7 +31974,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -32064,7 +32066,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -32332,7 +32334,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -32806,7 +32808,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -32822,7 +32824,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -32838,7 +32840,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>15143.8</v>
+        <v>15415.8</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -34648,7 +34650,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!E190")</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -34916,7 +34918,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -35008,7 +35010,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -35276,7 +35278,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -35368,7 +35370,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -35636,7 +35638,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -36689,7 +36691,7 @@
         <v>34</v>
       </c>
       <c r="F3" s="197">
-        <v>1072.1</v>
+        <v>875.3</v>
       </c>
       <c r="I3" s="205" t="str">
         <f>TEXT(Main!B3,"dd mmmm yyyy")&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,1)-1,"dd mmmm yyyy"),TEXT(Main!B3+(Main!B5-Main!B3)*1,"dd mmmm yyyy"))</f>
@@ -36817,7 +36819,7 @@
         <v>38</v>
       </c>
       <c r="F7" s="197">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I7" s="208" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,4),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*4)+4,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,5)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*5+4),"dd mmmm yyyy"))</f>
@@ -36972,7 +36974,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="169">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="D12" s="171"/>
       <c r="E12" s="199" t="s">
@@ -37011,7 +37013,7 @@
         <v>44</v>
       </c>
       <c r="F13" s="197">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I13" s="209" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,10),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*10)+10,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,11)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*11+10),"dd mmmm yyyy"))</f>
@@ -37083,7 +37085,7 @@
       </c>
       <c r="J15" s="210">
         <f ca="1">'April 2025 - June 2025'!E136</f>
-        <v>920.500000000001</v>
+        <v>1056.5</v>
       </c>
       <c r="M15" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,36),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+36),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,39)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+38),"dd mmmm yyyy"))</f>
@@ -37101,7 +37103,7 @@
       </c>
       <c r="C16" s="175">
         <f>SUM(C3:C15)</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D16" s="176"/>
       <c r="E16" s="174" t="s">
@@ -37109,7 +37111,7 @@
       </c>
       <c r="F16" s="200">
         <f>SUM(F3:F15)</f>
-        <v>1252.5</v>
+        <v>1045.5</v>
       </c>
       <c r="I16" s="211" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,13),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*13)+13,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,14)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*14+13),"dd mmmm yyyy"))</f>
@@ -37117,7 +37119,7 @@
       </c>
       <c r="J16" s="210">
         <f ca="1">'April 2025 - June 2025'!E163</f>
-        <v>1071.5</v>
+        <v>1207.5</v>
       </c>
       <c r="M16" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,39),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+39),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,42)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+41),"dd mmmm yyyy"))</f>
@@ -37135,7 +37137,7 @@
       </c>
       <c r="J17" s="210">
         <f ca="1">'April 2025 - June 2025'!E190</f>
-        <v>831.500000000001</v>
+        <v>967.500000000001</v>
       </c>
       <c r="M17" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,42),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+42),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,45)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+44),"dd mmmm yyyy"))</f>
@@ -37153,7 +37155,7 @@
       </c>
       <c r="J18" s="210">
         <f ca="1">'July 2025 - September 2025'!E136</f>
-        <v>697.500000000001</v>
+        <v>833.500000000001</v>
       </c>
       <c r="M18" s="207" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,45),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+45),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,48)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*48+47),"dd mmmm yyyy"))</f>
@@ -37171,7 +37173,7 @@
       </c>
       <c r="J19" s="210">
         <f ca="1">'July 2025 - September 2025'!E163</f>
-        <v>707.500000000001</v>
+        <v>843.500000000001</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="9:10">
@@ -37181,7 +37183,7 @@
       </c>
       <c r="J20" s="210">
         <f ca="1">'July 2025 - September 2025'!E190</f>
-        <v>639.500000000001</v>
+        <v>775.500000000001</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="9:10">
@@ -37191,7 +37193,7 @@
       </c>
       <c r="J21" s="210">
         <f ca="1">'October 2025 - December 2025'!E136</f>
-        <v>1227.2</v>
+        <v>1363.2</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:10">
@@ -37211,7 +37213,7 @@
       </c>
       <c r="J22" s="210">
         <f ca="1">'October 2025 - December 2025'!E163</f>
-        <v>2019.9</v>
+        <v>2155.9</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:10">
@@ -37236,7 +37238,7 @@
       </c>
       <c r="J23" s="210">
         <f ca="1">'October 2025 - December 2025'!E190</f>
-        <v>2571.6</v>
+        <v>2707.6</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:10">
@@ -37261,7 +37263,7 @@
       </c>
       <c r="J24" s="210">
         <f ca="1">'January 2026 - March 2026'!E136</f>
-        <v>3414.3</v>
+        <v>3550.3</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:10">
@@ -37280,7 +37282,7 @@
       </c>
       <c r="J25" s="210">
         <f ca="1">'January 2026 - March 2026'!E163</f>
-        <v>3806</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:10">
@@ -37299,7 +37301,7 @@
       </c>
       <c r="J26" s="210">
         <f ca="1">'January 2026 - March 2026'!E190</f>
-        <v>4648.7</v>
+        <v>4784.7</v>
       </c>
     </row>
     <row r="27" ht="35" customHeight="1" spans="1:10">
@@ -37318,7 +37320,7 @@
       </c>
       <c r="J27" s="210">
         <f ca="1">'April 2026 - June 2026'!E136</f>
-        <v>5200.4</v>
+        <v>5336.4</v>
       </c>
     </row>
     <row r="28" ht="35" customHeight="1" spans="1:10">
@@ -37337,7 +37339,7 @@
       </c>
       <c r="J28" s="210">
         <f ca="1">'April 2026 - June 2026'!E163</f>
-        <v>5883.1</v>
+        <v>6019.1</v>
       </c>
     </row>
     <row r="29" ht="35" customHeight="1" spans="1:10">
@@ -37356,7 +37358,7 @@
       </c>
       <c r="J29" s="206">
         <f ca="1">'April 2026 - June 2026'!E190</f>
-        <v>6434.8</v>
+        <v>6570.8</v>
       </c>
     </row>
     <row r="30" ht="35" customHeight="1" spans="1:10">
@@ -37378,7 +37380,7 @@
       </c>
       <c r="J30" s="214">
         <f ca="1">'July 2026 - September 2026'!E136</f>
-        <v>7277.5</v>
+        <v>7413.5</v>
       </c>
     </row>
     <row r="31" ht="35" customHeight="1" spans="9:10">
@@ -37388,7 +37390,7 @@
       </c>
       <c r="J31" s="210">
         <f ca="1">'July 2026 - September 2026'!E163</f>
-        <v>7669.2</v>
+        <v>7805.2</v>
       </c>
     </row>
     <row r="32" ht="35" customHeight="1" spans="9:10">
@@ -37398,7 +37400,7 @@
       </c>
       <c r="J32" s="210">
         <f ca="1">'July 2026 - September 2026'!E190</f>
-        <v>8449</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="33" ht="35" customHeight="1" spans="9:10">
@@ -37408,7 +37410,7 @@
       </c>
       <c r="J33" s="210">
         <f ca="1">'October 2026 - December 2026'!E136</f>
-        <v>9000.7</v>
+        <v>9136.7</v>
       </c>
     </row>
     <row r="34" ht="35" customHeight="1" spans="1:10">
@@ -37428,7 +37430,7 @@
       </c>
       <c r="J34" s="210">
         <f ca="1">'October 2026 - December 2026'!E163</f>
-        <v>9683.4</v>
+        <v>9819.4</v>
       </c>
     </row>
     <row r="35" ht="35" customHeight="1" spans="1:10">
@@ -37453,7 +37455,7 @@
       </c>
       <c r="J35" s="210">
         <f ca="1">'October 2026 - December 2026'!E190</f>
-        <v>10235.1</v>
+        <v>10371.1</v>
       </c>
     </row>
     <row r="36" ht="35" customHeight="1" spans="1:10">
@@ -37478,7 +37480,7 @@
       </c>
       <c r="J36" s="210">
         <f ca="1">'January 2027 - March 2027'!E136</f>
-        <v>11077.8</v>
+        <v>11213.8</v>
       </c>
     </row>
     <row r="37" ht="35" customHeight="1" spans="1:10">
@@ -37503,7 +37505,7 @@
       </c>
       <c r="J37" s="210">
         <f ca="1">'January 2027 - March 2027'!E163</f>
-        <v>11469.5</v>
+        <v>11605.5</v>
       </c>
     </row>
     <row r="38" ht="35" customHeight="1" spans="1:10">
@@ -37528,7 +37530,7 @@
       </c>
       <c r="J38" s="210">
         <f ca="1">'January 2027 - March 2027'!E190</f>
-        <v>12312.2</v>
+        <v>12448.2</v>
       </c>
     </row>
     <row r="39" ht="35" customHeight="1" spans="1:10">
@@ -37547,7 +37549,7 @@
       </c>
       <c r="J39" s="210">
         <f ca="1">'April 2027 - June 2027'!E136</f>
-        <v>12863.9</v>
+        <v>12999.9</v>
       </c>
     </row>
     <row r="40" ht="35" customHeight="1" spans="1:10">
@@ -37566,7 +37568,7 @@
       </c>
       <c r="J40" s="210">
         <f ca="1">'April 2027 - June 2027'!E163</f>
-        <v>13546.6</v>
+        <v>13682.6</v>
       </c>
     </row>
     <row r="41" ht="35" customHeight="1" spans="1:10">
@@ -37585,7 +37587,7 @@
       </c>
       <c r="J41" s="210">
         <f ca="1">'April 2027 - June 2027'!E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="42" ht="35" customHeight="1" spans="1:10">
@@ -37607,7 +37609,7 @@
       </c>
       <c r="J42" s="210">
         <f ca="1">Forecast_14!E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="43" ht="35" customHeight="1" spans="9:10">
@@ -37617,7 +37619,7 @@
       </c>
       <c r="J43" s="210">
         <f ca="1">Forecast_14!E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="44" ht="35" customHeight="1" spans="9:10">
@@ -37627,7 +37629,7 @@
       </c>
       <c r="J44" s="210">
         <f ca="1">Forecast_14!E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="45" ht="35" customHeight="1" spans="9:10">
@@ -37637,7 +37639,7 @@
       </c>
       <c r="J45" s="210">
         <f ca="1">Forecast_15!E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="46" ht="35" customHeight="1" spans="1:10">
@@ -37657,7 +37659,7 @@
       </c>
       <c r="J46" s="210">
         <f ca="1">Forecast_15!E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="47" ht="35" customHeight="1" spans="1:10">
@@ -37682,7 +37684,7 @@
       </c>
       <c r="J47" s="210">
         <f ca="1">Forecast_15!E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="48" ht="35" customHeight="1" spans="1:10">
@@ -37707,7 +37709,7 @@
       </c>
       <c r="J48" s="210">
         <f ca="1">Forecast_16!E136</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="49" ht="35" customHeight="1" spans="1:10">
@@ -37732,7 +37734,7 @@
       </c>
       <c r="J49" s="210">
         <f ca="1">Forecast_16!E163</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="50" ht="35" customHeight="1" spans="1:10">
@@ -37757,7 +37759,7 @@
       </c>
       <c r="J50" s="206">
         <f ca="1">Forecast_16!E190</f>
-        <v>14098.3</v>
+        <v>14234.3</v>
       </c>
     </row>
     <row r="51" ht="35" customHeight="1" spans="1:7">
@@ -39711,7 +39713,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -39739,7 +39741,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1548.21</v>
+        <v>1684.21</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -43161,7 +43163,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -43189,7 +43191,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1218.84</v>
+        <v>1354.84</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -46707,7 +46709,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -46739,7 +46741,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1212</v>
+        <v>1348</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -50225,7 +50227,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -50241,7 +50243,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>831.500000000001</v>
+        <v>967.500000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -50257,7 +50259,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1877</v>
+        <v>2149</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -50407,7 +50409,7 @@
       <c r="H13" s="14"/>
       <c r="I13" s="47"/>
     </row>
-    <row r="14" ht="20" customHeight="1" spans="1:9">
+    <row r="14" ht="49" customHeight="1" spans="1:9">
       <c r="A14" s="19"/>
       <c r="B14" s="110" t="s">
         <v>255</v>
@@ -50418,7 +50420,7 @@
       </c>
       <c r="E14" s="111"/>
       <c r="F14" s="41">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="G14" s="42"/>
       <c r="H14" s="14"/>
@@ -50447,7 +50449,7 @@
       <c r="E16" s="44"/>
       <c r="F16" s="45">
         <f>SUM(F10:G15)</f>
-        <v>2486</v>
+        <v>2622</v>
       </c>
       <c r="G16" s="46"/>
       <c r="H16" s="14"/>
@@ -52391,7 +52393,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>920.500000000001</v>
+        <v>1056.5</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -52483,7 +52485,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>920.500000000001</v>
+        <v>1056.5</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -52757,7 +52759,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>1071.5</v>
+        <v>1207.5</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -52849,7 +52851,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>1071.5</v>
+        <v>1207.5</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -53123,7 +53125,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>831.500000000001</v>
+        <v>967.500000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -53676,7 +53678,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -53692,7 +53694,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>639.500000000001</v>
+        <v>775.500000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -53708,7 +53710,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1685</v>
+        <v>1957</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -55562,7 +55564,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!E190")</f>
-        <v>831.500000000001</v>
+        <v>967.500000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -55836,7 +55838,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>697.500000000001</v>
+        <v>833.500000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -55928,7 +55930,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>697.500000000001</v>
+        <v>833.500000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -56202,7 +56204,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>707.500000000001</v>
+        <v>843.500000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -56294,7 +56296,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>707.500000000001</v>
+        <v>843.500000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -56570,7 +56572,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>639.500000000001</v>
+        <v>775.500000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -57123,7 +57125,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>1045.5</v>
+        <v>1181.5</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -57139,7 +57141,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>2571.6</v>
+        <v>2707.6</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -57155,7 +57157,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>3617.1</v>
+        <v>3889.1</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -59003,7 +59005,7 @@
       <c r="D116" s="57"/>
       <c r="E116" s="70" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!E190")</f>
-        <v>639.500000000001</v>
+        <v>775.500000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -59277,7 +59279,7 @@
       <c r="D136" s="81"/>
       <c r="E136" s="87">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>1227.2</v>
+        <v>1363.2</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -59369,7 +59371,7 @@
       <c r="D143" s="57"/>
       <c r="E143" s="87">
         <f ca="1">E136</f>
-        <v>1227.2</v>
+        <v>1363.2</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -59641,7 +59643,7 @@
       <c r="D163" s="81"/>
       <c r="E163" s="90">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>2019.9</v>
+        <v>2155.9</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -59733,7 +59735,7 @@
       <c r="D170" s="57"/>
       <c r="E170" s="90">
         <f ca="1">E163</f>
-        <v>2019.9</v>
+        <v>2155.9</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -60005,7 +60007,7 @@
       <c r="D190" s="81"/>
       <c r="E190" s="90">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>2571.6</v>
+        <v>2707.6</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>

--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21560" activeTab="2"/>
+    <workbookView windowHeight="21560"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>

--- a/Income And Expenses Forecast.xlsx
+++ b/Income And Expenses Forecast.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="21560"/>
+    <workbookView windowHeight="21560" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>
